--- a/Statistik_Jassen.xlsx
+++ b/Statistik_Jassen.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/75d543417bde3c84/Jassen/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meine Ablage\Jassen Wädi\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="8_{15F6BD30-91D7-45BC-ABFA-B44D2DB75B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B42F4B3-0815-496A-AA57-809C06B6739F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01BDF821-44C1-4732-9B17-81D672D3C08B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A8FCF452-0EF5-42A7-A382-1701488C7232}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="74">
   <si>
     <t>Fuchs</t>
   </si>
@@ -230,6 +230,40 @@
   </si>
   <si>
     <t>05.06.</t>
+  </si>
+  <si>
+    <t>Teamkostellationen</t>
+  </si>
+  <si>
+    <t>Gesamt-
+Anteil</t>
+  </si>
+  <si>
+    <t>Gesamt-
+Anzahl</t>
+  </si>
+  <si>
+    <t>Win-
+Rate</t>
+  </si>
+  <si>
+    <t>*Win-
+Anteil</t>
+  </si>
+  <si>
+    <t>Schlagi</t>
+  </si>
+  <si>
+    <t>Zolli</t>
+  </si>
+  <si>
+    <t>Disti</t>
+  </si>
+  <si>
+    <t>* Unentschieden wird als Sieg gewertet</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -707,7 +741,7 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -869,6 +903,24 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5556,10 +5608,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7171,12 +7219,10 @@
       <c r="F8" s="19">
         <v>1</v>
       </c>
-      <c r="G8" s="2" t="str">
-        <f>IFERROR(VLOOKUP(F8,$A$110:$B$118,2,0),"DOPPEL")</f>
-        <v>Küng</v>
+      <c r="G8" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="H8" s="42">
-        <f>SUMIFS($C$111:$C$118,$B$111:$B$118,G8)</f>
         <v>16</v>
       </c>
       <c r="I8" s="64"/>
@@ -7198,12 +7244,10 @@
       <c r="F9" s="19">
         <v>2</v>
       </c>
-      <c r="G9" s="2" t="str">
-        <f>IFERROR(VLOOKUP(F9,$A$110:$B$118,2,0),"DOPPEL")</f>
-        <v>Chäli</v>
+      <c r="G9" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="H9" s="42">
-        <f>SUMIFS($C$111:$C$118,$B$111:$B$118,G9)</f>
         <v>14</v>
       </c>
       <c r="I9" s="64"/>
@@ -7225,12 +7269,10 @@
       <c r="F10" s="19">
         <v>3</v>
       </c>
-      <c r="G10" s="2" t="str">
-        <f>IFERROR(VLOOKUP(F10,$A$110:$B$118,2,0),"DOPPEL")</f>
-        <v>Goonse</v>
+      <c r="G10" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="H10" s="42">
-        <f>SUMIFS($C$111:$C$118,$B$111:$B$118,G10)</f>
         <v>6</v>
       </c>
       <c r="I10" s="64"/>
@@ -7252,12 +7294,10 @@
       <c r="F11" s="21">
         <v>4</v>
       </c>
-      <c r="G11" s="6" t="str">
-        <f>IFERROR(VLOOKUP(F11,$A$110:$B$118,2,0),"DOPPEL")</f>
-        <v>Fuchs</v>
+      <c r="G11" s="6" t="s">
+        <v>0</v>
       </c>
       <c r="H11" s="66">
-        <f>SUMIFS($C$111:$C$118,$B$111:$B$118,G11)</f>
         <v>2</v>
       </c>
       <c r="I11" s="67"/>
@@ -9922,7 +9962,7 @@
       <c r="P93" s="8"/>
       <c r="Q93" s="60"/>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A94" s="10"/>
       <c r="B94" s="8"/>
       <c r="C94" s="8"/>
@@ -9933,12 +9973,22 @@
       <c r="H94" s="8"/>
       <c r="I94" s="8"/>
       <c r="J94" s="8"/>
-      <c r="K94" s="8"/>
-      <c r="L94" s="8"/>
-      <c r="M94" s="8"/>
-      <c r="N94" s="8"/>
-      <c r="O94" s="8"/>
-      <c r="P94" s="8"/>
+      <c r="K94" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="L94" s="68"/>
+      <c r="M94" s="69" t="s">
+        <v>65</v>
+      </c>
+      <c r="N94" s="69" t="s">
+        <v>66</v>
+      </c>
+      <c r="O94" s="69" t="s">
+        <v>67</v>
+      </c>
+      <c r="P94" s="69" t="s">
+        <v>68</v>
+      </c>
       <c r="Q94" s="60"/>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
@@ -9952,12 +10002,24 @@
       <c r="H95" s="8"/>
       <c r="I95" s="8"/>
       <c r="J95" s="8"/>
-      <c r="K95" s="8"/>
-      <c r="L95" s="8"/>
-      <c r="M95" s="8"/>
-      <c r="N95" s="8"/>
-      <c r="O95" s="8"/>
-      <c r="P95" s="8"/>
+      <c r="K95" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L95" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M95" s="70">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="N95" s="71">
+        <v>2</v>
+      </c>
+      <c r="O95" s="70">
+        <v>0</v>
+      </c>
+      <c r="P95" s="70">
+        <v>0</v>
+      </c>
       <c r="Q95" s="60"/>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
@@ -9973,12 +10035,24 @@
       <c r="H96" s="8"/>
       <c r="I96" s="8"/>
       <c r="J96" s="8"/>
-      <c r="K96" s="8"/>
-      <c r="L96" s="8"/>
-      <c r="M96" s="8"/>
-      <c r="N96" s="8"/>
-      <c r="O96" s="8"/>
-      <c r="P96" s="8"/>
+      <c r="K96" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L96" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M96" s="72">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="N96" s="73">
+        <v>3</v>
+      </c>
+      <c r="O96" s="70">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="P96" s="72">
+        <v>0.14285714285714285</v>
+      </c>
       <c r="Q96" s="60"/>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.25">
@@ -9992,12 +10066,24 @@
       <c r="H97" s="8"/>
       <c r="I97" s="8"/>
       <c r="J97" s="8"/>
-      <c r="K97" s="8"/>
-      <c r="L97" s="8"/>
-      <c r="M97" s="8"/>
-      <c r="N97" s="8"/>
-      <c r="O97" s="8"/>
-      <c r="P97" s="8"/>
+      <c r="K97" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L97" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M97" s="72" t="s">
+        <v>73</v>
+      </c>
+      <c r="N97" s="73">
+        <v>0</v>
+      </c>
+      <c r="O97" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="P97" s="72" t="s">
+        <v>73</v>
+      </c>
       <c r="Q97" s="60"/>
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.25">
@@ -10011,12 +10097,24 @@
       <c r="H98" s="8"/>
       <c r="I98" s="8"/>
       <c r="J98" s="8"/>
-      <c r="K98" s="8"/>
-      <c r="L98" s="8"/>
-      <c r="M98" s="8"/>
-      <c r="N98" s="8"/>
-      <c r="O98" s="8"/>
-      <c r="P98" s="8"/>
+      <c r="K98" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L98" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M98" s="72">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="N98" s="73">
+        <v>2</v>
+      </c>
+      <c r="O98" s="70">
+        <v>0.5</v>
+      </c>
+      <c r="P98" s="72">
+        <v>0.14285714285714285</v>
+      </c>
       <c r="Q98" s="60"/>
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.25">
@@ -10032,12 +10130,24 @@
       <c r="H99" s="8"/>
       <c r="I99" s="8"/>
       <c r="J99" s="8"/>
-      <c r="K99" s="8"/>
-      <c r="L99" s="8"/>
-      <c r="M99" s="8"/>
-      <c r="N99" s="8"/>
-      <c r="O99" s="8"/>
-      <c r="P99" s="8"/>
+      <c r="K99" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M99" s="72" t="s">
+        <v>73</v>
+      </c>
+      <c r="N99" s="73">
+        <v>0</v>
+      </c>
+      <c r="O99" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="P99" s="72" t="s">
+        <v>73</v>
+      </c>
       <c r="Q99" s="60"/>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.25">
@@ -10051,12 +10161,24 @@
       <c r="H100" s="8"/>
       <c r="I100" s="8"/>
       <c r="J100" s="8"/>
-      <c r="K100" s="8"/>
-      <c r="L100" s="8"/>
-      <c r="M100" s="8"/>
-      <c r="N100" s="8"/>
-      <c r="O100" s="8"/>
-      <c r="P100" s="8"/>
+      <c r="K100" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L100" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M100" s="72" t="s">
+        <v>73</v>
+      </c>
+      <c r="N100" s="73">
+        <v>0</v>
+      </c>
+      <c r="O100" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="P100" s="72" t="s">
+        <v>73</v>
+      </c>
       <c r="Q100" s="60"/>
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.25">
@@ -10070,12 +10192,24 @@
       <c r="H101" s="8"/>
       <c r="I101" s="8"/>
       <c r="J101" s="8"/>
-      <c r="K101" s="8"/>
-      <c r="L101" s="8"/>
-      <c r="M101" s="8"/>
-      <c r="N101" s="8"/>
-      <c r="O101" s="8"/>
-      <c r="P101" s="8"/>
+      <c r="K101" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M101" s="72">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="N101" s="73">
+        <v>2</v>
+      </c>
+      <c r="O101" s="70">
+        <v>0.5</v>
+      </c>
+      <c r="P101" s="72">
+        <v>0.14285714285714285</v>
+      </c>
       <c r="Q101" s="60"/>
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.25">
@@ -10091,12 +10225,24 @@
       <c r="H102" s="8"/>
       <c r="I102" s="8"/>
       <c r="J102" s="8"/>
-      <c r="K102" s="8"/>
-      <c r="L102" s="8"/>
-      <c r="M102" s="8"/>
-      <c r="N102" s="8"/>
-      <c r="O102" s="8"/>
-      <c r="P102" s="8"/>
+      <c r="K102" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M102" s="72" t="s">
+        <v>73</v>
+      </c>
+      <c r="N102" s="73">
+        <v>0</v>
+      </c>
+      <c r="O102" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="P102" s="72" t="s">
+        <v>73</v>
+      </c>
       <c r="Q102" s="60"/>
     </row>
     <row r="103" spans="1:19" x14ac:dyDescent="0.25">
@@ -10110,12 +10256,24 @@
       <c r="H103" s="8"/>
       <c r="I103" s="8"/>
       <c r="J103" s="8"/>
-      <c r="K103" s="8"/>
-      <c r="L103" s="8"/>
-      <c r="M103" s="8"/>
-      <c r="N103" s="8"/>
-      <c r="O103" s="8"/>
-      <c r="P103" s="8"/>
+      <c r="K103" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L103" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M103" s="72">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="N103" s="73">
+        <v>3</v>
+      </c>
+      <c r="O103" s="70">
+        <v>1</v>
+      </c>
+      <c r="P103" s="72">
+        <v>0.42857142857142855</v>
+      </c>
       <c r="Q103" s="60"/>
     </row>
     <row r="104" spans="1:19" x14ac:dyDescent="0.25">
@@ -10129,12 +10287,24 @@
       <c r="H104" s="8"/>
       <c r="I104" s="8"/>
       <c r="J104" s="8"/>
-      <c r="K104" s="8"/>
-      <c r="L104" s="8"/>
-      <c r="M104" s="8"/>
-      <c r="N104" s="8"/>
-      <c r="O104" s="8"/>
-      <c r="P104" s="8"/>
+      <c r="K104" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L104" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M104" s="72" t="s">
+        <v>73</v>
+      </c>
+      <c r="N104" s="73">
+        <v>0</v>
+      </c>
+      <c r="O104" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="P104" s="72" t="s">
+        <v>73</v>
+      </c>
       <c r="Q104" s="60"/>
     </row>
     <row r="105" spans="1:19" x14ac:dyDescent="0.25">
@@ -10150,12 +10320,24 @@
       <c r="H105" s="8"/>
       <c r="I105" s="8"/>
       <c r="J105" s="8"/>
-      <c r="K105" s="8"/>
-      <c r="L105" s="8"/>
-      <c r="M105" s="8"/>
-      <c r="N105" s="8"/>
-      <c r="O105" s="8"/>
-      <c r="P105" s="8"/>
+      <c r="K105" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L105" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M105" s="72" t="s">
+        <v>73</v>
+      </c>
+      <c r="N105" s="73">
+        <v>0</v>
+      </c>
+      <c r="O105" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="P105" s="72" t="s">
+        <v>73</v>
+      </c>
       <c r="Q105" s="60"/>
     </row>
     <row r="106" spans="1:19" x14ac:dyDescent="0.25">
@@ -10169,12 +10351,24 @@
       <c r="H106" s="8"/>
       <c r="I106" s="8"/>
       <c r="J106" s="8"/>
-      <c r="K106" s="8"/>
-      <c r="L106" s="8"/>
-      <c r="M106" s="8"/>
-      <c r="N106" s="8"/>
-      <c r="O106" s="8"/>
-      <c r="P106" s="8"/>
+      <c r="K106" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L106" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M106" s="72">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="N106" s="73">
+        <v>2</v>
+      </c>
+      <c r="O106" s="70">
+        <v>1</v>
+      </c>
+      <c r="P106" s="72">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="Q106" s="60"/>
     </row>
     <row r="107" spans="1:19" x14ac:dyDescent="0.25">
@@ -10188,12 +10382,24 @@
       <c r="H107" s="8"/>
       <c r="I107" s="8"/>
       <c r="J107" s="8"/>
-      <c r="K107" s="8"/>
-      <c r="L107" s="8"/>
-      <c r="M107" s="8"/>
-      <c r="N107" s="8"/>
-      <c r="O107" s="8"/>
-      <c r="P107" s="8"/>
+      <c r="K107" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L107" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M107" s="72" t="s">
+        <v>73</v>
+      </c>
+      <c r="N107" s="73">
+        <v>0</v>
+      </c>
+      <c r="O107" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="P107" s="72" t="s">
+        <v>73</v>
+      </c>
       <c r="Q107" s="60"/>
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.25">
@@ -10207,12 +10413,24 @@
       <c r="H108" s="8"/>
       <c r="I108" s="8"/>
       <c r="J108" s="8"/>
-      <c r="K108" s="8"/>
-      <c r="L108" s="8"/>
-      <c r="M108" s="8"/>
-      <c r="N108" s="8"/>
-      <c r="O108" s="8"/>
-      <c r="P108" s="8"/>
+      <c r="K108" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L108" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M108" s="72" t="s">
+        <v>73</v>
+      </c>
+      <c r="N108" s="73">
+        <v>0</v>
+      </c>
+      <c r="O108" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="P108" s="72" t="s">
+        <v>73</v>
+      </c>
       <c r="Q108" s="8"/>
     </row>
     <row r="109" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10243,7 +10461,9 @@
       </c>
       <c r="K110" s="8"/>
       <c r="L110" s="8"/>
-      <c r="M110" s="8"/>
+      <c r="M110" s="8" t="s">
+        <v>72</v>
+      </c>
       <c r="N110" s="8"/>
       <c r="O110" s="8"/>
       <c r="P110" s="8"/>
@@ -10252,14 +10472,12 @@
     </row>
     <row r="111" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A111" s="46">
-        <f t="shared" ref="A111:A114" si="0">_xlfn.RANK.EQ(C111,$C$111:$C$118,0)</f>
         <v>4</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C111" s="20">
-        <f>SUMIFS($D$17:$D$91,$B$17:$B$91,B111)+SUMIFS($I$17:$I$91,$G$17:$G$91,B111)+SUMIFS($N$17:$N$91,$L$17:$L$91,B111)</f>
         <v>2</v>
       </c>
       <c r="K111" s="8"/>
@@ -10272,14 +10490,12 @@
     </row>
     <row r="112" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A112" s="46">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C112" s="20">
-        <f>SUMIFS($D$17:$D$91,$B$17:$B$91,B112)+SUMIFS($I$17:$I$91,$G$17:$G$91,B112)+SUMIFS($N$17:$N$91,$L$17:$L$91,B112)</f>
         <v>16</v>
       </c>
       <c r="K112" s="8"/>
@@ -10292,27 +10508,23 @@
     </row>
     <row r="113" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A113" s="46">
-        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C113" s="20">
-        <f>SUMIFS($D$17:$D$91,$B$17:$B$91,B113)+SUMIFS($I$17:$I$91,$G$17:$G$91,B113)+SUMIFS($N$17:$N$91,$L$17:$L$91,B113)</f>
         <v>6</v>
       </c>
     </row>
     <row r="114" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A114" s="46">
-        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C114" s="20">
-        <f>SUMIFS($D$17:$D$91,$B$17:$B$91,B114)+SUMIFS($I$17:$I$91,$G$17:$G$91,B114)+SUMIFS($N$17:$N$91,$L$17:$L$91,B114)</f>
         <v>14</v>
       </c>
     </row>

--- a/Statistik_Jassen.xlsx
+++ b/Statistik_Jassen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meine Ablage\Jassen Wädi\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01BDF821-44C1-4732-9B17-81D672D3C08B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D22B551-4071-4744-BEDA-CB3161019211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A8FCF452-0EF5-42A7-A382-1701488C7232}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="71">
   <si>
     <t>Fuchs</t>
   </si>
@@ -251,19 +251,10 @@
 Anteil</t>
   </si>
   <si>
-    <t>Schlagi</t>
-  </si>
-  <si>
-    <t>Zolli</t>
-  </si>
-  <si>
-    <t>Disti</t>
-  </si>
-  <si>
     <t>* Unentschieden wird als Sieg gewertet</t>
   </si>
   <si>
-    <t/>
+    <t>15.06.</t>
   </si>
 </sst>
 </file>
@@ -928,7 +919,17 @@
     <cellStyle name="Prozent" xfId="1" builtinId="5"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="35">
+  <dxfs count="36">
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color auto="1"/>
@@ -1486,7 +1487,7 @@
             <c:strRef>
               <c:f>'Gesamtranking Print'!$B$131:$AH$131</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>21.03.</c:v>
                 </c:pt>
@@ -1507,6 +1508,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>08.06.</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>15.06.</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1537,6 +1541,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1640,7 +1647,7 @@
             <c:strRef>
               <c:f>'Gesamtranking Print'!$B$131:$AH$131</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>21.03.</c:v>
                 </c:pt>
@@ -1661,6 +1668,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>08.06.</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>15.06.</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1691,6 +1701,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1794,7 +1807,7 @@
             <c:strRef>
               <c:f>'Gesamtranking Print'!$B$131:$AH$131</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>21.03.</c:v>
                 </c:pt>
@@ -1815,6 +1828,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>08.06.</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>15.06.</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1844,6 +1860,9 @@
                   <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
@@ -1948,7 +1967,7 @@
             <c:strRef>
               <c:f>'Gesamtranking Print'!$B$131:$AH$131</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>21.03.</c:v>
                 </c:pt>
@@ -1969,6 +1988,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>08.06.</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>15.06.</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1999,6 +2021,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>27</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2168,7 +2193,7 @@
                       </c:ext>
                     </c:extLst>
                     <c:strCache>
-                      <c:ptCount val="7"/>
+                      <c:ptCount val="8"/>
                       <c:pt idx="0">
                         <c:v>21.03.</c:v>
                       </c:pt>
@@ -2189,6 +2214,9 @@
                       </c:pt>
                       <c:pt idx="6">
                         <c:v>08.06.</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>15.06.</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -2360,7 +2388,7 @@
                       </c:ext>
                     </c:extLst>
                     <c:strCache>
-                      <c:ptCount val="7"/>
+                      <c:ptCount val="8"/>
                       <c:pt idx="0">
                         <c:v>21.03.</c:v>
                       </c:pt>
@@ -2381,6 +2409,9 @@
                       </c:pt>
                       <c:pt idx="6">
                         <c:v>08.06.</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>15.06.</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -2559,7 +2590,7 @@
                       </c:ext>
                     </c:extLst>
                     <c:strCache>
-                      <c:ptCount val="7"/>
+                      <c:ptCount val="8"/>
                       <c:pt idx="0">
                         <c:v>21.03.</c:v>
                       </c:pt>
@@ -2580,6 +2611,9 @@
                       </c:pt>
                       <c:pt idx="6">
                         <c:v>08.06.</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>15.06.</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -2981,6 +3015,9 @@
                 <c:pt idx="6">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="7">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3148,6 +3185,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -3481,6 +3521,9 @@
                 <c:pt idx="6">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="7">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3648,6 +3691,9 @@
                   <c:v>-1</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -3979,6 +4025,9 @@
                 <c:pt idx="6">
                   <c:v>-1</c:v>
                 </c:pt>
+                <c:pt idx="7">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4147,6 +4196,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4470,6 +4522,9 @@
                 <c:pt idx="6">
                   <c:v>-1</c:v>
                 </c:pt>
+                <c:pt idx="7">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4631,6 +4686,9 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7223,7 +7281,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="42">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="I8" s="64"/>
       <c r="J8" s="9"/>
@@ -7439,7 +7497,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="42">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D17" s="42">
         <v>1</v>
@@ -7452,7 +7510,7 @@
         <v>2</v>
       </c>
       <c r="H17" s="42">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I17" s="42">
         <v>1</v>
@@ -7482,9 +7540,11 @@
         <v>2</v>
       </c>
       <c r="C18" s="42">
-        <v>43</v>
-      </c>
-      <c r="D18" s="42"/>
+        <v>50</v>
+      </c>
+      <c r="D18" s="42">
+        <v>1</v>
+      </c>
       <c r="E18" s="24"/>
       <c r="F18" s="5">
         <v>2</v>
@@ -8175,9 +8235,15 @@
       <c r="K39" s="5">
         <v>1</v>
       </c>
-      <c r="L39" s="2"/>
-      <c r="M39" s="42"/>
-      <c r="N39" s="42"/>
+      <c r="L39" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M39" s="42">
+        <v>1</v>
+      </c>
+      <c r="N39" s="42">
+        <v>1</v>
+      </c>
       <c r="O39" s="8"/>
       <c r="P39" s="8"/>
       <c r="Q39" s="8"/>
@@ -8208,9 +8274,15 @@
       <c r="K40" s="5">
         <v>2</v>
       </c>
-      <c r="L40" s="2"/>
-      <c r="M40" s="42"/>
-      <c r="N40" s="42"/>
+      <c r="L40" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M40" s="42">
+        <v>1</v>
+      </c>
+      <c r="N40" s="42">
+        <v>1</v>
+      </c>
       <c r="O40" s="8"/>
       <c r="P40" s="8"/>
       <c r="Q40" s="8"/>
@@ -8241,8 +8313,12 @@
       <c r="K41" s="5">
         <v>3</v>
       </c>
-      <c r="L41" s="2"/>
-      <c r="M41" s="42"/>
+      <c r="L41" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M41" s="42">
+        <v>0</v>
+      </c>
       <c r="N41" s="42"/>
       <c r="O41" s="8"/>
       <c r="P41" s="8"/>
@@ -8274,8 +8350,12 @@
       <c r="K42" s="5">
         <v>4</v>
       </c>
-      <c r="L42" s="2"/>
-      <c r="M42" s="42"/>
+      <c r="L42" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="M42" s="42">
+        <v>0</v>
+      </c>
       <c r="N42" s="42"/>
       <c r="O42" s="8"/>
       <c r="P42" s="8"/>
@@ -10015,7 +10095,7 @@
         <v>2</v>
       </c>
       <c r="O95" s="70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P95" s="70">
         <v>0</v>
@@ -10035,24 +10115,12 @@
       <c r="H96" s="8"/>
       <c r="I96" s="8"/>
       <c r="J96" s="8"/>
-      <c r="K96" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L96" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M96" s="72">
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="N96" s="73">
-        <v>3</v>
-      </c>
-      <c r="O96" s="70">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="P96" s="72">
-        <v>0.14285714285714285</v>
-      </c>
+      <c r="K96" s="2"/>
+      <c r="L96" s="2"/>
+      <c r="M96" s="72"/>
+      <c r="N96" s="73"/>
+      <c r="O96" s="70"/>
+      <c r="P96" s="72"/>
       <c r="Q96" s="60"/>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.25">
@@ -10066,24 +10134,12 @@
       <c r="H97" s="8"/>
       <c r="I97" s="8"/>
       <c r="J97" s="8"/>
-      <c r="K97" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L97" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M97" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="N97" s="73">
-        <v>0</v>
-      </c>
-      <c r="O97" s="70" t="s">
-        <v>73</v>
-      </c>
-      <c r="P97" s="72" t="s">
-        <v>73</v>
-      </c>
+      <c r="K97" s="2"/>
+      <c r="L97" s="2"/>
+      <c r="M97" s="72"/>
+      <c r="N97" s="73"/>
+      <c r="O97" s="70"/>
+      <c r="P97" s="72"/>
       <c r="Q97" s="60"/>
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.25">
@@ -10097,24 +10153,12 @@
       <c r="H98" s="8"/>
       <c r="I98" s="8"/>
       <c r="J98" s="8"/>
-      <c r="K98" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L98" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="M98" s="72">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="N98" s="73">
-        <v>2</v>
-      </c>
-      <c r="O98" s="70">
-        <v>0.5</v>
-      </c>
-      <c r="P98" s="72">
-        <v>0.14285714285714285</v>
-      </c>
+      <c r="K98" s="2"/>
+      <c r="L98" s="2"/>
+      <c r="M98" s="72"/>
+      <c r="N98" s="73"/>
+      <c r="O98" s="70"/>
+      <c r="P98" s="72"/>
       <c r="Q98" s="60"/>
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.25">
@@ -10130,24 +10174,12 @@
       <c r="H99" s="8"/>
       <c r="I99" s="8"/>
       <c r="J99" s="8"/>
-      <c r="K99" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L99" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="M99" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="N99" s="73">
-        <v>0</v>
-      </c>
-      <c r="O99" s="70" t="s">
-        <v>73</v>
-      </c>
-      <c r="P99" s="72" t="s">
-        <v>73</v>
-      </c>
+      <c r="K99" s="2"/>
+      <c r="L99" s="2"/>
+      <c r="M99" s="72"/>
+      <c r="N99" s="73"/>
+      <c r="O99" s="70"/>
+      <c r="P99" s="72"/>
       <c r="Q99" s="60"/>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.25">
@@ -10161,24 +10193,12 @@
       <c r="H100" s="8"/>
       <c r="I100" s="8"/>
       <c r="J100" s="8"/>
-      <c r="K100" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L100" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="M100" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="N100" s="73">
-        <v>0</v>
-      </c>
-      <c r="O100" s="70" t="s">
-        <v>73</v>
-      </c>
-      <c r="P100" s="72" t="s">
-        <v>73</v>
-      </c>
+      <c r="K100" s="2"/>
+      <c r="L100" s="2"/>
+      <c r="M100" s="72"/>
+      <c r="N100" s="73"/>
+      <c r="O100" s="70"/>
+      <c r="P100" s="72"/>
       <c r="Q100" s="60"/>
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.25">
@@ -10192,24 +10212,12 @@
       <c r="H101" s="8"/>
       <c r="I101" s="8"/>
       <c r="J101" s="8"/>
-      <c r="K101" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M101" s="72">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="N101" s="73">
-        <v>2</v>
-      </c>
-      <c r="O101" s="70">
-        <v>0.5</v>
-      </c>
-      <c r="P101" s="72">
-        <v>0.14285714285714285</v>
-      </c>
+      <c r="K101" s="2"/>
+      <c r="L101" s="2"/>
+      <c r="M101" s="72"/>
+      <c r="N101" s="73"/>
+      <c r="O101" s="70"/>
+      <c r="P101" s="72"/>
       <c r="Q101" s="60"/>
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.25">
@@ -10225,24 +10233,12 @@
       <c r="H102" s="8"/>
       <c r="I102" s="8"/>
       <c r="J102" s="8"/>
-      <c r="K102" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="M102" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="N102" s="73">
-        <v>0</v>
-      </c>
-      <c r="O102" s="70" t="s">
-        <v>73</v>
-      </c>
-      <c r="P102" s="72" t="s">
-        <v>73</v>
-      </c>
+      <c r="K102" s="2"/>
+      <c r="L102" s="2"/>
+      <c r="M102" s="72"/>
+      <c r="N102" s="73"/>
+      <c r="O102" s="70"/>
+      <c r="P102" s="72"/>
       <c r="Q102" s="60"/>
     </row>
     <row r="103" spans="1:19" x14ac:dyDescent="0.25">
@@ -10256,24 +10252,12 @@
       <c r="H103" s="8"/>
       <c r="I103" s="8"/>
       <c r="J103" s="8"/>
-      <c r="K103" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L103" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="M103" s="72">
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="N103" s="73">
-        <v>3</v>
-      </c>
-      <c r="O103" s="70">
-        <v>1</v>
-      </c>
-      <c r="P103" s="72">
-        <v>0.42857142857142855</v>
-      </c>
+      <c r="K103" s="2"/>
+      <c r="L103" s="2"/>
+      <c r="M103" s="72"/>
+      <c r="N103" s="73"/>
+      <c r="O103" s="70"/>
+      <c r="P103" s="72"/>
       <c r="Q103" s="60"/>
     </row>
     <row r="104" spans="1:19" x14ac:dyDescent="0.25">
@@ -10287,24 +10271,12 @@
       <c r="H104" s="8"/>
       <c r="I104" s="8"/>
       <c r="J104" s="8"/>
-      <c r="K104" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L104" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M104" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="N104" s="73">
-        <v>0</v>
-      </c>
-      <c r="O104" s="70" t="s">
-        <v>73</v>
-      </c>
-      <c r="P104" s="72" t="s">
-        <v>73</v>
-      </c>
+      <c r="K104" s="2"/>
+      <c r="L104" s="2"/>
+      <c r="M104" s="72"/>
+      <c r="N104" s="73"/>
+      <c r="O104" s="70"/>
+      <c r="P104" s="72"/>
       <c r="Q104" s="60"/>
     </row>
     <row r="105" spans="1:19" x14ac:dyDescent="0.25">
@@ -10320,24 +10292,12 @@
       <c r="H105" s="8"/>
       <c r="I105" s="8"/>
       <c r="J105" s="8"/>
-      <c r="K105" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L105" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M105" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="N105" s="73">
-        <v>0</v>
-      </c>
-      <c r="O105" s="70" t="s">
-        <v>73</v>
-      </c>
-      <c r="P105" s="72" t="s">
-        <v>73</v>
-      </c>
+      <c r="K105" s="2"/>
+      <c r="L105" s="2"/>
+      <c r="M105" s="72"/>
+      <c r="N105" s="73"/>
+      <c r="O105" s="70"/>
+      <c r="P105" s="72"/>
       <c r="Q105" s="60"/>
     </row>
     <row r="106" spans="1:19" x14ac:dyDescent="0.25">
@@ -10351,24 +10311,12 @@
       <c r="H106" s="8"/>
       <c r="I106" s="8"/>
       <c r="J106" s="8"/>
-      <c r="K106" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L106" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="M106" s="72">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="N106" s="73">
-        <v>2</v>
-      </c>
-      <c r="O106" s="70">
-        <v>1</v>
-      </c>
-      <c r="P106" s="72">
-        <v>0.2857142857142857</v>
-      </c>
+      <c r="K106" s="2"/>
+      <c r="L106" s="2"/>
+      <c r="M106" s="72"/>
+      <c r="N106" s="73"/>
+      <c r="O106" s="70"/>
+      <c r="P106" s="72"/>
       <c r="Q106" s="60"/>
     </row>
     <row r="107" spans="1:19" x14ac:dyDescent="0.25">
@@ -10382,24 +10330,12 @@
       <c r="H107" s="8"/>
       <c r="I107" s="8"/>
       <c r="J107" s="8"/>
-      <c r="K107" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L107" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="M107" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="N107" s="73">
-        <v>0</v>
-      </c>
-      <c r="O107" s="70" t="s">
-        <v>73</v>
-      </c>
-      <c r="P107" s="72" t="s">
-        <v>73</v>
-      </c>
+      <c r="K107" s="2"/>
+      <c r="L107" s="2"/>
+      <c r="M107" s="72"/>
+      <c r="N107" s="73"/>
+      <c r="O107" s="70"/>
+      <c r="P107" s="72"/>
       <c r="Q107" s="60"/>
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.25">
@@ -10413,24 +10349,12 @@
       <c r="H108" s="8"/>
       <c r="I108" s="8"/>
       <c r="J108" s="8"/>
-      <c r="K108" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L108" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="M108" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="N108" s="73">
-        <v>0</v>
-      </c>
-      <c r="O108" s="70" t="s">
-        <v>73</v>
-      </c>
-      <c r="P108" s="72" t="s">
-        <v>73</v>
-      </c>
+      <c r="K108" s="2"/>
+      <c r="L108" s="2"/>
+      <c r="M108" s="72"/>
+      <c r="N108" s="73"/>
+      <c r="O108" s="70"/>
+      <c r="P108" s="72"/>
       <c r="Q108" s="8"/>
     </row>
     <row r="109" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10462,7 +10386,7 @@
       <c r="K110" s="8"/>
       <c r="L110" s="8"/>
       <c r="M110" s="8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="N110" s="8"/>
       <c r="O110" s="8"/>
@@ -10680,7 +10604,9 @@
       <c r="H123" s="5">
         <v>-1</v>
       </c>
-      <c r="I123" s="5"/>
+      <c r="I123" s="5">
+        <v>1</v>
+      </c>
       <c r="J123" s="5"/>
       <c r="K123" s="5"/>
       <c r="L123" s="5"/>
@@ -10732,7 +10658,9 @@
       <c r="H124" s="5">
         <v>1</v>
       </c>
-      <c r="I124" s="5"/>
+      <c r="I124" s="5">
+        <v>1</v>
+      </c>
       <c r="J124" s="5"/>
       <c r="K124" s="5"/>
       <c r="L124" s="5"/>
@@ -10784,7 +10712,9 @@
       <c r="H125" s="5">
         <v>1</v>
       </c>
-      <c r="I125" s="5"/>
+      <c r="I125" s="5">
+        <v>1</v>
+      </c>
       <c r="J125" s="5"/>
       <c r="K125" s="5"/>
       <c r="L125" s="5"/>
@@ -10836,7 +10766,9 @@
       <c r="H126" s="5">
         <v>-1</v>
       </c>
-      <c r="I126" s="5"/>
+      <c r="I126" s="5">
+        <v>1</v>
+      </c>
       <c r="J126" s="5"/>
       <c r="K126" s="5"/>
       <c r="L126" s="5"/>
@@ -10890,7 +10822,9 @@
       <c r="H131" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="I131" s="58"/>
+      <c r="I131" s="58" t="s">
+        <v>70</v>
+      </c>
       <c r="J131" s="58"/>
       <c r="K131" s="58"/>
       <c r="L131" s="58"/>
@@ -10942,7 +10876,9 @@
       <c r="H132" s="5">
         <v>2</v>
       </c>
-      <c r="I132" s="5"/>
+      <c r="I132" s="5">
+        <v>5</v>
+      </c>
       <c r="J132" s="5"/>
       <c r="K132" s="5"/>
       <c r="L132" s="5"/>
@@ -10994,7 +10930,9 @@
       <c r="H133" s="5">
         <v>16</v>
       </c>
-      <c r="I133" s="5"/>
+      <c r="I133" s="5">
+        <v>5</v>
+      </c>
       <c r="J133" s="5"/>
       <c r="K133" s="5"/>
       <c r="L133" s="5"/>
@@ -11046,7 +10984,9 @@
       <c r="H134" s="5">
         <v>6</v>
       </c>
-      <c r="I134" s="5"/>
+      <c r="I134" s="5">
+        <v>6</v>
+      </c>
       <c r="J134" s="5"/>
       <c r="K134" s="5"/>
       <c r="L134" s="5"/>
@@ -11098,7 +11038,9 @@
       <c r="H135" s="5">
         <v>14</v>
       </c>
-      <c r="I135" s="5"/>
+      <c r="I135" s="5">
+        <v>27</v>
+      </c>
       <c r="J135" s="5"/>
       <c r="K135" s="5"/>
       <c r="L135" s="5"/>
@@ -11271,178 +11213,183 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A132:A139">
-    <cfRule type="containsText" dxfId="34" priority="1176" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="35" priority="1177" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A132)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A110:C118">
-    <cfRule type="containsText" dxfId="33" priority="1135" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="34" priority="1136" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A110)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:D20">
-    <cfRule type="containsText" dxfId="32" priority="59" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="33" priority="60" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22:D27">
-    <cfRule type="containsText" dxfId="31" priority="24" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="32" priority="25" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:D34">
-    <cfRule type="containsText" dxfId="30" priority="41" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="31" priority="42" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38:D42">
-    <cfRule type="containsText" dxfId="29" priority="38" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="30" priority="39" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44:D48">
-    <cfRule type="containsText" dxfId="28" priority="14" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="29" priority="15" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A44)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:D56">
-    <cfRule type="containsText" dxfId="27" priority="390" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="28" priority="391" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A52)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:D62">
-    <cfRule type="containsText" dxfId="26" priority="9" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="27" priority="10" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A58)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64:D68">
-    <cfRule type="containsText" dxfId="25" priority="8" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="26" priority="9" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A64)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70:D74">
-    <cfRule type="containsText" dxfId="24" priority="4" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="25" priority="5" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A70)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A78:D82">
-    <cfRule type="containsText" dxfId="23" priority="1" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="24" priority="2" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A78)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A84:D88">
-    <cfRule type="containsText" dxfId="22" priority="17" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="23" priority="18" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A84)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:I11">
-    <cfRule type="containsText" dxfId="21" priority="208" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="22" priority="209" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:I20">
-    <cfRule type="containsText" dxfId="20" priority="44" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="21" priority="45" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F22:I26">
-    <cfRule type="containsText" dxfId="19" priority="10" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="20" priority="11" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:I34">
-    <cfRule type="containsText" dxfId="18" priority="40" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="19" priority="41" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F38:I42">
-    <cfRule type="containsText" dxfId="17" priority="37" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="18" priority="38" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F44:I48">
-    <cfRule type="containsText" dxfId="16" priority="35" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="17" priority="36" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F44)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52:I56">
-    <cfRule type="containsText" dxfId="15" priority="21" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="16" priority="22" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F52)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F58:I62">
-    <cfRule type="containsText" dxfId="14" priority="137" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="15" priority="138" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F58)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F64:I68">
-    <cfRule type="containsText" dxfId="13" priority="7" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="14" priority="8" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F64)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F70:I74">
-    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F70)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F78:I82">
-    <cfRule type="containsText" dxfId="11" priority="19" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="12" priority="20" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F78)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F84:I88">
-    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="11" priority="13" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F84)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16:N20">
-    <cfRule type="containsText" dxfId="9" priority="25" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="10" priority="26" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K22:N26">
-    <cfRule type="containsText" dxfId="8" priority="329" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="9" priority="330" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K30:N34">
-    <cfRule type="containsText" dxfId="7" priority="39" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="8" priority="40" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K30)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K38:N42">
-    <cfRule type="containsText" dxfId="6" priority="143" operator="containsText" text="DOPPEL">
+  <conditionalFormatting sqref="K38:N38 K39:K42 M39:N42">
+    <cfRule type="containsText" dxfId="7" priority="144" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K44:N48">
-    <cfRule type="containsText" dxfId="5" priority="30" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="6" priority="31" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K44)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K52:N56">
-    <cfRule type="containsText" dxfId="4" priority="378" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="5" priority="379" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K52)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K58:N62">
-    <cfRule type="containsText" dxfId="3" priority="13" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="4" priority="14" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K58)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K64:N68">
-    <cfRule type="containsText" dxfId="2" priority="6" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K64)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K78:N82">
-    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="2" priority="19" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K78)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K84:N88">
-    <cfRule type="containsText" dxfId="0" priority="11" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="1" priority="12" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K84)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L39:L42">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="DOPPEL">
+      <formula>NOT(ISERROR(SEARCH("DOPPEL",L39)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/Statistik_Jassen.xlsx
+++ b/Statistik_Jassen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meine Ablage\Jassen Wädi\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D22B551-4071-4744-BEDA-CB3161019211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{422EBA53-B0E7-4A4E-B12B-3F25A935BBB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A8FCF452-0EF5-42A7-A382-1701488C7232}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="76">
   <si>
     <t>Fuchs</t>
   </si>
@@ -251,7 +251,22 @@
 Anteil</t>
   </si>
   <si>
+    <t>Schlagi</t>
+  </si>
+  <si>
+    <t>Zolli</t>
+  </si>
+  <si>
+    <t>Disti</t>
+  </si>
+  <si>
     <t>* Unentschieden wird als Sieg gewertet</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>CHECK</t>
   </si>
   <si>
     <t>15.06.</t>
@@ -919,17 +934,7 @@
     <cellStyle name="Prozent" xfId="1" builtinId="5"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="35">
     <dxf>
       <font>
         <color auto="1"/>
@@ -1543,7 +1548,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1703,7 +1708,7 @@
                   <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1863,7 +1868,7 @@
                   <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2023,7 +2028,7 @@
                   <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>27</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3522,7 +3527,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1</c:v>
+                  <c:v>-1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3694,7 +3699,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1</c:v>
+                  <c:v>-1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4523,7 +4528,7 @@
                   <c:v>-1</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1</c:v>
+                  <c:v>-1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4688,7 +4693,7 @@
                   <c:v>-1</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1</c:v>
+                  <c:v>-1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7281,9 +7286,11 @@
         <v>1</v>
       </c>
       <c r="H8" s="42">
-        <v>35</v>
-      </c>
-      <c r="I8" s="64"/>
+        <v>19</v>
+      </c>
+      <c r="I8" s="64">
+        <v>0.35</v>
+      </c>
       <c r="J8" s="9"/>
       <c r="K8" s="8"/>
       <c r="L8" s="12"/>
@@ -7306,9 +7313,11 @@
         <v>3</v>
       </c>
       <c r="H9" s="42">
-        <v>14</v>
-      </c>
-      <c r="I9" s="64"/>
+        <v>13</v>
+      </c>
+      <c r="I9" s="64">
+        <v>0.3</v>
+      </c>
       <c r="J9" s="9"/>
       <c r="K9" s="8"/>
       <c r="L9" s="12"/>
@@ -7331,9 +7340,11 @@
         <v>2</v>
       </c>
       <c r="H10" s="42">
-        <v>6</v>
-      </c>
-      <c r="I10" s="64"/>
+        <v>4</v>
+      </c>
+      <c r="I10" s="64">
+        <v>0.30508474576271188</v>
+      </c>
       <c r="J10" s="9"/>
       <c r="K10" s="8"/>
       <c r="L10" s="12"/>
@@ -7356,9 +7367,11 @@
         <v>0</v>
       </c>
       <c r="H11" s="66">
-        <v>2</v>
-      </c>
-      <c r="I11" s="67"/>
+        <v>3</v>
+      </c>
+      <c r="I11" s="67">
+        <v>0.26153846153846155</v>
+      </c>
       <c r="J11" s="9"/>
       <c r="K11" s="8"/>
       <c r="L11" s="12"/>
@@ -7497,7 +7510,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="42">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D17" s="42">
         <v>1</v>
@@ -7510,7 +7523,7 @@
         <v>2</v>
       </c>
       <c r="H17" s="42">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I17" s="42">
         <v>1</v>
@@ -7523,7 +7536,7 @@
         <v>1</v>
       </c>
       <c r="M17" s="15">
-        <v>6.4285714285714288</v>
+        <v>7</v>
       </c>
       <c r="N17" s="42">
         <v>1</v>
@@ -7537,14 +7550,12 @@
         <v>2</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" s="42">
-        <v>50</v>
-      </c>
-      <c r="D18" s="42">
-        <v>1</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="D18" s="42"/>
       <c r="E18" s="24"/>
       <c r="F18" s="5">
         <v>2</v>
@@ -7553,7 +7564,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="42">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I18" s="42"/>
       <c r="J18" s="24"/>
@@ -7561,10 +7572,10 @@
         <v>2</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M18" s="15">
-        <v>6.1428571428571432</v>
+        <v>6.5</v>
       </c>
       <c r="N18" s="42"/>
       <c r="O18" s="9"/>
@@ -7576,10 +7587,10 @@
         <v>3</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C19" s="42">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D19" s="42"/>
       <c r="E19" s="24"/>
@@ -7590,7 +7601,7 @@
         <v>3</v>
       </c>
       <c r="H19" s="42">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I19" s="42"/>
       <c r="J19" s="24"/>
@@ -7598,10 +7609,10 @@
         <v>3</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M19" s="15">
-        <v>5.8571428571428568</v>
+        <v>5.625</v>
       </c>
       <c r="N19" s="42"/>
       <c r="O19" s="9"/>
@@ -7617,7 +7628,7 @@
         <v>0</v>
       </c>
       <c r="C20" s="42">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D20" s="42"/>
       <c r="E20" s="24"/>
@@ -7628,7 +7639,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="42">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I20" s="42"/>
       <c r="J20" s="24"/>
@@ -7639,7 +7650,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="15">
-        <v>3.5714285714285716</v>
+        <v>3.375</v>
       </c>
       <c r="N20" s="42"/>
       <c r="O20" s="9"/>
@@ -7716,7 +7727,7 @@
         <v>1</v>
       </c>
       <c r="C23" s="15">
-        <v>2.25</v>
+        <v>2.4347826086956523</v>
       </c>
       <c r="D23" s="42">
         <v>1</v>
@@ -7750,10 +7761,10 @@
         <v>2</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24" s="15">
-        <v>2.15</v>
+        <v>2.2608695652173911</v>
       </c>
       <c r="D24" s="42"/>
       <c r="E24" s="24"/>
@@ -7785,10 +7796,10 @@
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C25" s="15">
-        <v>2.0499999999999998</v>
+        <v>1.9565217391304348</v>
       </c>
       <c r="D25" s="42"/>
       <c r="E25" s="24"/>
@@ -7821,12 +7832,12 @@
         <v>0</v>
       </c>
       <c r="C26" s="15">
-        <v>1.25</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="D26" s="42"/>
       <c r="E26" s="24"/>
       <c r="F26" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>2</v>
@@ -7956,7 +7967,7 @@
         <v>1</v>
       </c>
       <c r="C31" s="4">
-        <v>60953</v>
+        <v>70699</v>
       </c>
       <c r="D31" s="42">
         <v>1</v>
@@ -7969,7 +7980,7 @@
         <v>1</v>
       </c>
       <c r="H31" s="4">
-        <v>8707.5714285714294</v>
+        <v>8837.375</v>
       </c>
       <c r="I31" s="42">
         <v>1</v>
@@ -7982,7 +7993,7 @@
         <v>1</v>
       </c>
       <c r="M31" s="4">
-        <v>3047.65</v>
+        <v>3073.8695652173915</v>
       </c>
       <c r="N31" s="42">
         <v>1</v>
@@ -7999,7 +8010,7 @@
         <v>3</v>
       </c>
       <c r="C32" s="4">
-        <v>59417</v>
+        <v>69163</v>
       </c>
       <c r="D32" s="42"/>
       <c r="E32" s="24"/>
@@ -8010,7 +8021,7 @@
         <v>3</v>
       </c>
       <c r="H32" s="4">
-        <v>8488.1428571428569</v>
+        <v>8645.375</v>
       </c>
       <c r="I32" s="42"/>
       <c r="J32" s="24"/>
@@ -8021,7 +8032,7 @@
         <v>3</v>
       </c>
       <c r="M32" s="4">
-        <v>2970.85</v>
+        <v>3007.086956521739</v>
       </c>
       <c r="N32" s="42"/>
       <c r="O32" s="8"/>
@@ -8036,7 +8047,7 @@
         <v>2</v>
       </c>
       <c r="C33" s="4">
-        <v>59402</v>
+        <v>66891</v>
       </c>
       <c r="D33" s="42"/>
       <c r="E33" s="24"/>
@@ -8047,7 +8058,7 @@
         <v>2</v>
       </c>
       <c r="H33" s="4">
-        <v>8486</v>
+        <v>8361.375</v>
       </c>
       <c r="I33" s="42"/>
       <c r="J33" s="24"/>
@@ -8058,7 +8069,7 @@
         <v>2</v>
       </c>
       <c r="M33" s="4">
-        <v>2970.1</v>
+        <v>2908.304347826087</v>
       </c>
       <c r="N33" s="42"/>
       <c r="O33" s="8"/>
@@ -8074,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="C34" s="4">
-        <v>56562</v>
+        <v>64051</v>
       </c>
       <c r="D34" s="42"/>
       <c r="E34" s="24"/>
@@ -8085,7 +8096,7 @@
         <v>0</v>
       </c>
       <c r="H34" s="4">
-        <v>8080.2857142857147</v>
+        <v>8006.375</v>
       </c>
       <c r="I34" s="42"/>
       <c r="J34" s="24"/>
@@ -8096,7 +8107,7 @@
         <v>0</v>
       </c>
       <c r="M34" s="4">
-        <v>2828.1</v>
+        <v>2784.8260869565215</v>
       </c>
       <c r="N34" s="42"/>
       <c r="O34" s="8"/>
@@ -8213,7 +8224,7 @@
         <v>1</v>
       </c>
       <c r="C39" s="42">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D39" s="42">
         <v>1</v>
@@ -8226,7 +8237,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="4">
-        <v>8481</v>
+        <v>10794</v>
       </c>
       <c r="I39" s="42">
         <v>1</v>
@@ -8256,7 +8267,7 @@
         <v>3</v>
       </c>
       <c r="C40" s="42">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D40" s="42"/>
       <c r="E40" s="24"/>
@@ -8267,12 +8278,12 @@
         <v>3</v>
       </c>
       <c r="H40" s="4">
-        <v>6682</v>
+        <v>8995</v>
       </c>
       <c r="I40" s="42"/>
       <c r="J40" s="24"/>
       <c r="K40" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>3</v>
@@ -8314,7 +8325,7 @@
         <v>3</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M41" s="42">
         <v>0</v>
@@ -8348,10 +8359,10 @@
       <c r="I42" s="42"/>
       <c r="J42" s="24"/>
       <c r="K42" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M42" s="42">
         <v>0</v>
@@ -8431,7 +8442,7 @@
         <v>1</v>
       </c>
       <c r="C45" s="42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D45" s="42">
         <v>1</v>
@@ -8444,7 +8455,7 @@
         <v>3</v>
       </c>
       <c r="H45" s="42">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I45" s="42">
         <v>1</v>
@@ -8474,7 +8485,7 @@
         <v>3</v>
       </c>
       <c r="C46" s="42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D46" s="42">
         <v>1</v>
@@ -8487,7 +8498,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I46" s="42"/>
       <c r="J46" s="24"/>
@@ -8689,7 +8700,7 @@
         <v>3</v>
       </c>
       <c r="C53" s="4">
-        <v>6610</v>
+        <v>7070</v>
       </c>
       <c r="D53" s="42">
         <v>1</v>
@@ -8702,7 +8713,7 @@
         <v>3</v>
       </c>
       <c r="H53" s="42">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="I53" s="42">
         <v>1</v>
@@ -8715,7 +8726,7 @@
         <v>3</v>
       </c>
       <c r="M53" s="4">
-        <v>2460</v>
+        <v>2920</v>
       </c>
       <c r="N53" s="42">
         <v>1</v>
@@ -8732,7 +8743,7 @@
         <v>0</v>
       </c>
       <c r="C54" s="4">
-        <v>4620</v>
+        <v>5390</v>
       </c>
       <c r="D54" s="42"/>
       <c r="E54" s="24"/>
@@ -8743,7 +8754,7 @@
         <v>0</v>
       </c>
       <c r="H54" s="42">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I54" s="42"/>
       <c r="J54" s="24"/>
@@ -8754,7 +8765,7 @@
         <v>0</v>
       </c>
       <c r="M54" s="4">
-        <v>2420</v>
+        <v>2740</v>
       </c>
       <c r="N54" s="42"/>
       <c r="O54" s="8"/>
@@ -8766,10 +8777,10 @@
         <v>3</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55" s="4">
-        <v>4460</v>
+        <v>5300</v>
       </c>
       <c r="D55" s="42"/>
       <c r="E55" s="24"/>
@@ -8777,10 +8788,10 @@
         <v>3</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H55" s="42">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I55" s="42"/>
       <c r="J55" s="24"/>
@@ -8788,10 +8799,10 @@
         <v>3</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M55" s="4">
-        <v>2160</v>
+        <v>2400</v>
       </c>
       <c r="N55" s="42"/>
       <c r="O55" s="8"/>
@@ -8803,10 +8814,10 @@
         <v>4</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56" s="4">
-        <v>4040</v>
+        <v>4920</v>
       </c>
       <c r="D56" s="42"/>
       <c r="E56" s="24"/>
@@ -8814,10 +8825,10 @@
         <v>4</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H56" s="42">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I56" s="42"/>
       <c r="J56" s="24"/>
@@ -8825,10 +8836,10 @@
         <v>4</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M56" s="4">
-        <v>1940</v>
+        <v>2320</v>
       </c>
       <c r="N56" s="42"/>
       <c r="O56" s="8"/>
@@ -8931,7 +8942,7 @@
         <v>0</v>
       </c>
       <c r="M59" s="42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N59" s="42">
         <v>1</v>
@@ -8948,7 +8959,7 @@
         <v>0</v>
       </c>
       <c r="C60" s="42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D60" s="42"/>
       <c r="E60" s="24"/>
@@ -8959,12 +8970,12 @@
         <v>0</v>
       </c>
       <c r="H60" s="4">
-        <v>900</v>
+        <v>950</v>
       </c>
       <c r="I60" s="42"/>
       <c r="J60" s="24"/>
       <c r="K60" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>3</v>
@@ -8972,9 +8983,7 @@
       <c r="M60" s="42">
         <v>5</v>
       </c>
-      <c r="N60" s="42">
-        <v>1</v>
-      </c>
+      <c r="N60" s="42"/>
       <c r="O60" s="8"/>
       <c r="P60" s="8"/>
       <c r="Q60" s="8"/>
@@ -8984,10 +8993,10 @@
         <v>2</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C61" s="42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D61" s="42"/>
       <c r="E61" s="24"/>
@@ -9021,21 +9030,21 @@
         <v>4</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62" s="42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D62" s="42"/>
       <c r="E62" s="24"/>
       <c r="F62" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H62" s="4">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="I62" s="42"/>
       <c r="J62" s="24"/>
@@ -9120,10 +9129,10 @@
         <v>1</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C65" s="4">
-        <v>1400</v>
+        <v>1700</v>
       </c>
       <c r="D65" s="42">
         <v>1</v>
@@ -9163,10 +9172,10 @@
         <v>2</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C66" s="4">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="D66" s="42"/>
       <c r="E66" s="24"/>
@@ -9197,7 +9206,7 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>1</v>
@@ -9256,7 +9265,7 @@
       <c r="I68" s="42"/>
       <c r="J68" s="24"/>
       <c r="K68" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>1</v>
@@ -9330,7 +9339,7 @@
         <v>1</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C71" s="42">
         <v>1</v>
@@ -9343,10 +9352,10 @@
         <v>1</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H71" s="4">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="I71" s="42">
         <v>1</v>
@@ -9366,24 +9375,26 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
+        <v>1</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>0</v>
-      </c>
       <c r="C72" s="42">
-        <v>0</v>
-      </c>
-      <c r="D72" s="42"/>
+        <v>1</v>
+      </c>
+      <c r="D72" s="42">
+        <v>1</v>
+      </c>
       <c r="E72" s="24"/>
       <c r="F72" s="5">
         <v>2</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H72" s="4">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I72" s="42"/>
       <c r="J72" s="24"/>
@@ -9399,10 +9410,10 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C73" s="42">
         <v>0</v>
@@ -9410,10 +9421,10 @@
       <c r="D73" s="42"/>
       <c r="E73" s="24"/>
       <c r="F73" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H73" s="4">
         <v>0</v>
@@ -9432,10 +9443,10 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C74" s="42">
         <v>0</v>
@@ -9443,10 +9454,10 @@
       <c r="D74" s="42"/>
       <c r="E74" s="24"/>
       <c r="F74" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H74" s="4">
         <v>0</v>
@@ -9583,10 +9594,10 @@
         <v>1</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H79" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I79" s="42">
         <v>1</v>
@@ -9616,7 +9627,7 @@
         <v>1</v>
       </c>
       <c r="C80" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D80" s="42"/>
       <c r="E80" s="24"/>
@@ -9624,10 +9635,10 @@
         <v>1</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H80" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I80" s="42">
         <v>1</v>
@@ -9637,10 +9648,10 @@
         <v>2</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M80" s="4">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="N80" s="42"/>
       <c r="O80" s="8"/>
@@ -9655,7 +9666,7 @@
         <v>3</v>
       </c>
       <c r="C81" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D81" s="42"/>
       <c r="E81" s="24"/>
@@ -9663,10 +9674,10 @@
         <v>1</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H81" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I81" s="42">
         <v>1</v>
@@ -9676,10 +9687,10 @@
         <v>3</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M81" s="4">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="N81" s="42"/>
       <c r="O81" s="8"/>
@@ -9702,10 +9713,10 @@
         <v>1</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H82" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I82" s="42">
         <v>1</v>
@@ -9718,7 +9729,7 @@
         <v>0</v>
       </c>
       <c r="M82" s="4">
-        <v>280</v>
+        <v>370</v>
       </c>
       <c r="N82" s="42"/>
       <c r="O82" s="8"/>
@@ -9795,7 +9806,7 @@
         <v>1</v>
       </c>
       <c r="C85" s="44">
-        <v>11.428571428571429</v>
+        <v>10</v>
       </c>
       <c r="D85" s="42">
         <v>1</v>
@@ -9808,7 +9819,7 @@
         <v>1</v>
       </c>
       <c r="H85" s="4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I85" s="42">
         <v>1</v>
@@ -9821,7 +9832,7 @@
         <v>1</v>
       </c>
       <c r="M85" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N85" s="42">
         <v>1</v>
@@ -9835,25 +9846,23 @@
         <v>2</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C86" s="44">
-        <v>14.285714285714286</v>
+        <v>15</v>
       </c>
       <c r="D86" s="42"/>
       <c r="E86" s="24"/>
       <c r="F86" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H86" s="4">
-        <v>11</v>
-      </c>
-      <c r="I86" s="42">
-        <v>1</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I86" s="42"/>
       <c r="J86" s="8"/>
       <c r="K86" s="5">
         <v>1</v>
@@ -9862,7 +9871,7 @@
         <v>3</v>
       </c>
       <c r="M86" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N86" s="42">
         <v>1</v>
@@ -9876,10 +9885,10 @@
         <v>3</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C87" s="44">
-        <v>17.142857142857142</v>
+        <v>23.75</v>
       </c>
       <c r="D87" s="42"/>
       <c r="E87" s="24"/>
@@ -9887,10 +9896,10 @@
         <v>3</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H87" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I87" s="42"/>
       <c r="J87" s="8"/>
@@ -9901,7 +9910,7 @@
         <v>0</v>
       </c>
       <c r="M87" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N87" s="42"/>
       <c r="O87" s="8"/>
@@ -9916,7 +9925,7 @@
         <v>0</v>
       </c>
       <c r="C88" s="44">
-        <v>40</v>
+        <v>46.25</v>
       </c>
       <c r="D88" s="42"/>
       <c r="E88" s="24"/>
@@ -9938,7 +9947,7 @@
         <v>2</v>
       </c>
       <c r="M88" s="4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N88" s="42"/>
       <c r="O88" s="8"/>
@@ -10089,13 +10098,13 @@
         <v>3</v>
       </c>
       <c r="M95" s="70">
-        <v>0.2857142857142857</v>
+        <v>0.25</v>
       </c>
       <c r="N95" s="71">
         <v>2</v>
       </c>
       <c r="O95" s="70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P95" s="70">
         <v>0</v>
@@ -10115,12 +10124,24 @@
       <c r="H96" s="8"/>
       <c r="I96" s="8"/>
       <c r="J96" s="8"/>
-      <c r="K96" s="2"/>
-      <c r="L96" s="2"/>
-      <c r="M96" s="72"/>
-      <c r="N96" s="73"/>
-      <c r="O96" s="70"/>
-      <c r="P96" s="72"/>
+      <c r="K96" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L96" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M96" s="72">
+        <v>0.375</v>
+      </c>
+      <c r="N96" s="73">
+        <v>3</v>
+      </c>
+      <c r="O96" s="70">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="P96" s="72">
+        <v>0.125</v>
+      </c>
       <c r="Q96" s="60"/>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.25">
@@ -10134,12 +10155,24 @@
       <c r="H97" s="8"/>
       <c r="I97" s="8"/>
       <c r="J97" s="8"/>
-      <c r="K97" s="2"/>
-      <c r="L97" s="2"/>
-      <c r="M97" s="72"/>
-      <c r="N97" s="73"/>
-      <c r="O97" s="70"/>
-      <c r="P97" s="72"/>
+      <c r="K97" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L97" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M97" s="72" t="s">
+        <v>73</v>
+      </c>
+      <c r="N97" s="73">
+        <v>0</v>
+      </c>
+      <c r="O97" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="P97" s="72" t="s">
+        <v>73</v>
+      </c>
       <c r="Q97" s="60"/>
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.25">
@@ -10153,12 +10186,24 @@
       <c r="H98" s="8"/>
       <c r="I98" s="8"/>
       <c r="J98" s="8"/>
-      <c r="K98" s="2"/>
-      <c r="L98" s="2"/>
-      <c r="M98" s="72"/>
-      <c r="N98" s="73"/>
-      <c r="O98" s="70"/>
-      <c r="P98" s="72"/>
+      <c r="K98" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L98" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M98" s="72">
+        <v>0.375</v>
+      </c>
+      <c r="N98" s="73">
+        <v>3</v>
+      </c>
+      <c r="O98" s="70">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="P98" s="72">
+        <v>0.125</v>
+      </c>
       <c r="Q98" s="60"/>
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.25">
@@ -10174,12 +10219,24 @@
       <c r="H99" s="8"/>
       <c r="I99" s="8"/>
       <c r="J99" s="8"/>
-      <c r="K99" s="2"/>
-      <c r="L99" s="2"/>
-      <c r="M99" s="72"/>
-      <c r="N99" s="73"/>
-      <c r="O99" s="70"/>
-      <c r="P99" s="72"/>
+      <c r="K99" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M99" s="72" t="s">
+        <v>73</v>
+      </c>
+      <c r="N99" s="73">
+        <v>0</v>
+      </c>
+      <c r="O99" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="P99" s="72" t="s">
+        <v>73</v>
+      </c>
       <c r="Q99" s="60"/>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.25">
@@ -10193,12 +10250,24 @@
       <c r="H100" s="8"/>
       <c r="I100" s="8"/>
       <c r="J100" s="8"/>
-      <c r="K100" s="2"/>
-      <c r="L100" s="2"/>
-      <c r="M100" s="72"/>
-      <c r="N100" s="73"/>
-      <c r="O100" s="70"/>
-      <c r="P100" s="72"/>
+      <c r="K100" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L100" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M100" s="72" t="s">
+        <v>73</v>
+      </c>
+      <c r="N100" s="73">
+        <v>0</v>
+      </c>
+      <c r="O100" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="P100" s="72" t="s">
+        <v>73</v>
+      </c>
       <c r="Q100" s="60"/>
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.25">
@@ -10212,12 +10281,24 @@
       <c r="H101" s="8"/>
       <c r="I101" s="8"/>
       <c r="J101" s="8"/>
-      <c r="K101" s="2"/>
-      <c r="L101" s="2"/>
-      <c r="M101" s="72"/>
-      <c r="N101" s="73"/>
-      <c r="O101" s="70"/>
-      <c r="P101" s="72"/>
+      <c r="K101" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M101" s="72">
+        <v>0.375</v>
+      </c>
+      <c r="N101" s="73">
+        <v>3</v>
+      </c>
+      <c r="O101" s="70">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="P101" s="72">
+        <v>0.25</v>
+      </c>
       <c r="Q101" s="60"/>
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.25">
@@ -10233,12 +10314,24 @@
       <c r="H102" s="8"/>
       <c r="I102" s="8"/>
       <c r="J102" s="8"/>
-      <c r="K102" s="2"/>
-      <c r="L102" s="2"/>
-      <c r="M102" s="72"/>
-      <c r="N102" s="73"/>
-      <c r="O102" s="70"/>
-      <c r="P102" s="72"/>
+      <c r="K102" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M102" s="72" t="s">
+        <v>73</v>
+      </c>
+      <c r="N102" s="73">
+        <v>0</v>
+      </c>
+      <c r="O102" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="P102" s="72" t="s">
+        <v>73</v>
+      </c>
       <c r="Q102" s="60"/>
     </row>
     <row r="103" spans="1:19" x14ac:dyDescent="0.25">
@@ -10252,12 +10345,24 @@
       <c r="H103" s="8"/>
       <c r="I103" s="8"/>
       <c r="J103" s="8"/>
-      <c r="K103" s="2"/>
-      <c r="L103" s="2"/>
-      <c r="M103" s="72"/>
-      <c r="N103" s="73"/>
-      <c r="O103" s="70"/>
-      <c r="P103" s="72"/>
+      <c r="K103" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L103" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M103" s="72">
+        <v>0.375</v>
+      </c>
+      <c r="N103" s="73">
+        <v>3</v>
+      </c>
+      <c r="O103" s="70">
+        <v>1</v>
+      </c>
+      <c r="P103" s="72">
+        <v>0.375</v>
+      </c>
       <c r="Q103" s="60"/>
     </row>
     <row r="104" spans="1:19" x14ac:dyDescent="0.25">
@@ -10271,12 +10376,24 @@
       <c r="H104" s="8"/>
       <c r="I104" s="8"/>
       <c r="J104" s="8"/>
-      <c r="K104" s="2"/>
-      <c r="L104" s="2"/>
-      <c r="M104" s="72"/>
-      <c r="N104" s="73"/>
-      <c r="O104" s="70"/>
-      <c r="P104" s="72"/>
+      <c r="K104" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L104" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M104" s="72" t="s">
+        <v>73</v>
+      </c>
+      <c r="N104" s="73">
+        <v>0</v>
+      </c>
+      <c r="O104" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="P104" s="72" t="s">
+        <v>73</v>
+      </c>
       <c r="Q104" s="60"/>
     </row>
     <row r="105" spans="1:19" x14ac:dyDescent="0.25">
@@ -10292,12 +10409,24 @@
       <c r="H105" s="8"/>
       <c r="I105" s="8"/>
       <c r="J105" s="8"/>
-      <c r="K105" s="2"/>
-      <c r="L105" s="2"/>
-      <c r="M105" s="72"/>
-      <c r="N105" s="73"/>
-      <c r="O105" s="70"/>
-      <c r="P105" s="72"/>
+      <c r="K105" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L105" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M105" s="72" t="s">
+        <v>73</v>
+      </c>
+      <c r="N105" s="73">
+        <v>0</v>
+      </c>
+      <c r="O105" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="P105" s="72" t="s">
+        <v>73</v>
+      </c>
       <c r="Q105" s="60"/>
     </row>
     <row r="106" spans="1:19" x14ac:dyDescent="0.25">
@@ -10311,12 +10440,24 @@
       <c r="H106" s="8"/>
       <c r="I106" s="8"/>
       <c r="J106" s="8"/>
-      <c r="K106" s="2"/>
-      <c r="L106" s="2"/>
-      <c r="M106" s="72"/>
-      <c r="N106" s="73"/>
-      <c r="O106" s="70"/>
-      <c r="P106" s="72"/>
+      <c r="K106" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L106" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M106" s="72">
+        <v>0.25</v>
+      </c>
+      <c r="N106" s="73">
+        <v>2</v>
+      </c>
+      <c r="O106" s="70">
+        <v>1</v>
+      </c>
+      <c r="P106" s="72">
+        <v>0.25</v>
+      </c>
       <c r="Q106" s="60"/>
     </row>
     <row r="107" spans="1:19" x14ac:dyDescent="0.25">
@@ -10330,12 +10471,24 @@
       <c r="H107" s="8"/>
       <c r="I107" s="8"/>
       <c r="J107" s="8"/>
-      <c r="K107" s="2"/>
-      <c r="L107" s="2"/>
-      <c r="M107" s="72"/>
-      <c r="N107" s="73"/>
-      <c r="O107" s="70"/>
-      <c r="P107" s="72"/>
+      <c r="K107" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L107" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M107" s="72" t="s">
+        <v>73</v>
+      </c>
+      <c r="N107" s="73">
+        <v>0</v>
+      </c>
+      <c r="O107" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="P107" s="72" t="s">
+        <v>73</v>
+      </c>
       <c r="Q107" s="60"/>
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.25">
@@ -10349,12 +10502,24 @@
       <c r="H108" s="8"/>
       <c r="I108" s="8"/>
       <c r="J108" s="8"/>
-      <c r="K108" s="2"/>
-      <c r="L108" s="2"/>
-      <c r="M108" s="72"/>
-      <c r="N108" s="73"/>
-      <c r="O108" s="70"/>
-      <c r="P108" s="72"/>
+      <c r="K108" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L108" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M108" s="72" t="s">
+        <v>73</v>
+      </c>
+      <c r="N108" s="73">
+        <v>0</v>
+      </c>
+      <c r="O108" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="P108" s="72" t="s">
+        <v>73</v>
+      </c>
       <c r="Q108" s="8"/>
     </row>
     <row r="109" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10386,7 +10551,7 @@
       <c r="K110" s="8"/>
       <c r="L110" s="8"/>
       <c r="M110" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="N110" s="8"/>
       <c r="O110" s="8"/>
@@ -10402,7 +10567,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K111" s="8"/>
       <c r="L111" s="8"/>
@@ -10420,13 +10585,19 @@
         <v>1</v>
       </c>
       <c r="C112" s="20">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K112" s="8"/>
-      <c r="L112" s="8"/>
-      <c r="M112" s="8"/>
+      <c r="L112" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="M112" s="8">
+        <v>0</v>
+      </c>
       <c r="N112" s="8"/>
-      <c r="O112" s="8"/>
+      <c r="O112" s="8">
+        <v>-0.125</v>
+      </c>
       <c r="P112" s="8"/>
       <c r="Q112" s="60"/>
     </row>
@@ -10438,7 +10609,7 @@
         <v>2</v>
       </c>
       <c r="C113" s="20">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114" spans="1:34" x14ac:dyDescent="0.25">
@@ -10449,7 +10620,7 @@
         <v>3</v>
       </c>
       <c r="C114" s="20">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="115" spans="1:34" x14ac:dyDescent="0.25">
@@ -10605,7 +10776,7 @@
         <v>-1</v>
       </c>
       <c r="I123" s="5">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J123" s="5"/>
       <c r="K123" s="5"/>
@@ -10713,7 +10884,7 @@
         <v>1</v>
       </c>
       <c r="I125" s="5">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J125" s="5"/>
       <c r="K125" s="5"/>
@@ -10823,7 +10994,7 @@
         <v>62</v>
       </c>
       <c r="I131" s="58" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J131" s="58"/>
       <c r="K131" s="58"/>
@@ -10877,7 +11048,7 @@
         <v>2</v>
       </c>
       <c r="I132" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J132" s="5"/>
       <c r="K132" s="5"/>
@@ -10931,7 +11102,7 @@
         <v>16</v>
       </c>
       <c r="I133" s="5">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="J133" s="5"/>
       <c r="K133" s="5"/>
@@ -10985,7 +11156,7 @@
         <v>6</v>
       </c>
       <c r="I134" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J134" s="5"/>
       <c r="K134" s="5"/>
@@ -11039,7 +11210,7 @@
         <v>14</v>
       </c>
       <c r="I135" s="5">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="J135" s="5"/>
       <c r="K135" s="5"/>
@@ -11213,183 +11384,178 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A132:A139">
-    <cfRule type="containsText" dxfId="35" priority="1177" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="34" priority="1176" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A132)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A110:C118">
-    <cfRule type="containsText" dxfId="34" priority="1136" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="33" priority="1135" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A110)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:D20">
-    <cfRule type="containsText" dxfId="33" priority="60" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="32" priority="59" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22:D27">
-    <cfRule type="containsText" dxfId="32" priority="25" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="31" priority="24" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:D34">
-    <cfRule type="containsText" dxfId="31" priority="42" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="30" priority="41" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38:D42">
-    <cfRule type="containsText" dxfId="30" priority="39" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="29" priority="38" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44:D48">
-    <cfRule type="containsText" dxfId="29" priority="15" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="28" priority="14" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A44)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:D56">
-    <cfRule type="containsText" dxfId="28" priority="391" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="27" priority="390" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A52)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:D62">
-    <cfRule type="containsText" dxfId="27" priority="10" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="26" priority="9" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A58)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64:D68">
-    <cfRule type="containsText" dxfId="26" priority="9" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="25" priority="8" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A64)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70:D74">
-    <cfRule type="containsText" dxfId="25" priority="5" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="24" priority="4" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A70)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A78:D82">
-    <cfRule type="containsText" dxfId="24" priority="2" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="23" priority="1" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A78)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A84:D88">
-    <cfRule type="containsText" dxfId="23" priority="18" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="22" priority="17" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A84)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:I11">
-    <cfRule type="containsText" dxfId="22" priority="209" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="21" priority="208" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:I20">
-    <cfRule type="containsText" dxfId="21" priority="45" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="20" priority="44" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F22:I26">
-    <cfRule type="containsText" dxfId="20" priority="11" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="19" priority="10" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:I34">
-    <cfRule type="containsText" dxfId="19" priority="41" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="18" priority="40" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F38:I42">
-    <cfRule type="containsText" dxfId="18" priority="38" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="17" priority="37" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F44:I48">
-    <cfRule type="containsText" dxfId="17" priority="36" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="16" priority="35" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F44)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52:I56">
-    <cfRule type="containsText" dxfId="16" priority="22" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="15" priority="21" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F52)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F58:I62">
-    <cfRule type="containsText" dxfId="15" priority="138" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="14" priority="137" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F58)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F64:I68">
-    <cfRule type="containsText" dxfId="14" priority="8" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="13" priority="7" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F64)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F70:I74">
-    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F70)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F78:I82">
-    <cfRule type="containsText" dxfId="12" priority="20" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="11" priority="19" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F78)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F84:I88">
-    <cfRule type="containsText" dxfId="11" priority="13" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F84)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16:N20">
-    <cfRule type="containsText" dxfId="10" priority="26" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="9" priority="25" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K22:N26">
-    <cfRule type="containsText" dxfId="9" priority="330" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="8" priority="329" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K30:N34">
-    <cfRule type="containsText" dxfId="8" priority="40" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="7" priority="39" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K30)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K38:N38 K39:K42 M39:N42">
-    <cfRule type="containsText" dxfId="7" priority="144" operator="containsText" text="DOPPEL">
+  <conditionalFormatting sqref="K38:N42">
+    <cfRule type="containsText" dxfId="6" priority="143" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K44:N48">
-    <cfRule type="containsText" dxfId="6" priority="31" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="5" priority="30" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K44)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K52:N56">
-    <cfRule type="containsText" dxfId="5" priority="379" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="4" priority="378" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K52)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K58:N62">
-    <cfRule type="containsText" dxfId="4" priority="14" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="3" priority="13" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K58)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K64:N68">
-    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="2" priority="6" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K64)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K78:N82">
-    <cfRule type="containsText" dxfId="2" priority="19" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K78)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K84:N88">
-    <cfRule type="containsText" dxfId="1" priority="12" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="0" priority="11" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K84)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L39:L42">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="DOPPEL">
-      <formula>NOT(ISERROR(SEARCH("DOPPEL",L39)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/Statistik_Jassen.xlsx
+++ b/Statistik_Jassen.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meine Ablage\Jassen Wädi\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{422EBA53-B0E7-4A4E-B12B-3F25A935BBB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FBAA36C-40AD-418E-AD69-1C62B82AF1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A8FCF452-0EF5-42A7-A382-1701488C7232}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="77">
   <si>
     <t>Fuchs</t>
   </si>
@@ -184,6 +184,9 @@
     <t>Rose = 4fach</t>
   </si>
   <si>
+    <t>Schlagi</t>
+  </si>
+  <si>
     <t>ø Anzahl Punkte/Spiel</t>
   </si>
   <si>
@@ -193,7 +196,21 @@
     <t>VH %</t>
   </si>
   <si>
+    <t>Teamkostellationen</t>
+  </si>
+  <si>
     <t>Total Kontermatch</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Win-
+Rate</t>
+  </si>
+  <si>
+    <t>Gesamt-
+Anteil</t>
   </si>
   <si>
     <t>Verlauf Tagessiege</t>
@@ -202,10 +219,30 @@
     <t>Anz. Rundensiege</t>
   </si>
   <si>
+    <t>CHECK</t>
+  </si>
+  <si>
+    <t>Gesamt-
+Anzahl</t>
+  </si>
+  <si>
+    <t>*Win-
+Anteil</t>
+  </si>
+  <si>
+    <t>* Unentschieden wird als Sieg gewertet</t>
+  </si>
+  <si>
+    <t>Zolli</t>
+  </si>
+  <si>
     <t>JFK</t>
   </si>
   <si>
     <t>Verlauf Tagessiege (1 = Sieg / 0 = unentschieden o. abwesend / -1 = Niederlage)</t>
+  </si>
+  <si>
+    <t>Disti</t>
   </si>
   <si>
     <t>21.03.</t>
@@ -232,44 +269,10 @@
     <t>05.06.</t>
   </si>
   <si>
-    <t>Teamkostellationen</t>
+    <t>15.06.</t>
   </si>
   <si>
-    <t>Gesamt-
-Anteil</t>
-  </si>
-  <si>
-    <t>Gesamt-
-Anzahl</t>
-  </si>
-  <si>
-    <t>Win-
-Rate</t>
-  </si>
-  <si>
-    <t>*Win-
-Anteil</t>
-  </si>
-  <si>
-    <t>Schlagi</t>
-  </si>
-  <si>
-    <t>Zolli</t>
-  </si>
-  <si>
-    <t>Disti</t>
-  </si>
-  <si>
-    <t>* Unentschieden wird als Sieg gewertet</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>CHECK</t>
-  </si>
-  <si>
-    <t>15.06.</t>
+    <t>03.07.</t>
   </si>
 </sst>
 </file>
@@ -282,7 +285,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -294,6 +297,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -347,12 +357,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -744,12 +760,12 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -761,26 +777,26 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
@@ -792,59 +808,59 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -853,17 +869,17 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -881,6 +897,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -891,17 +910,32 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -910,24 +944,9 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Komma" xfId="2" builtinId="3"/>
@@ -1492,7 +1511,7 @@
             <c:strRef>
               <c:f>'Gesamtranking Print'!$B$131:$AH$131</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>21.03.</c:v>
                 </c:pt>
@@ -1516,6 +1535,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>15.06.</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>03.07.</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1549,6 +1571,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1652,7 +1677,7 @@
             <c:strRef>
               <c:f>'Gesamtranking Print'!$B$131:$AH$131</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>21.03.</c:v>
                 </c:pt>
@@ -1676,6 +1701,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>15.06.</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>03.07.</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1709,6 +1737,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1812,7 +1843,7 @@
             <c:strRef>
               <c:f>'Gesamtranking Print'!$B$131:$AH$131</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>21.03.</c:v>
                 </c:pt>
@@ -1836,6 +1867,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>15.06.</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>03.07.</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1868,6 +1902,9 @@
                   <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
@@ -1972,7 +2009,7 @@
             <c:strRef>
               <c:f>'Gesamtranking Print'!$B$131:$AH$131</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>21.03.</c:v>
                 </c:pt>
@@ -1996,6 +2033,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>15.06.</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>03.07.</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2029,6 +2069,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>27</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2198,7 +2241,7 @@
                       </c:ext>
                     </c:extLst>
                     <c:strCache>
-                      <c:ptCount val="8"/>
+                      <c:ptCount val="9"/>
                       <c:pt idx="0">
                         <c:v>21.03.</c:v>
                       </c:pt>
@@ -2222,6 +2265,9 @@
                       </c:pt>
                       <c:pt idx="7">
                         <c:v>15.06.</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>03.07.</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -2393,7 +2439,7 @@
                       </c:ext>
                     </c:extLst>
                     <c:strCache>
-                      <c:ptCount val="8"/>
+                      <c:ptCount val="9"/>
                       <c:pt idx="0">
                         <c:v>21.03.</c:v>
                       </c:pt>
@@ -2417,6 +2463,9 @@
                       </c:pt>
                       <c:pt idx="7">
                         <c:v>15.06.</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>03.07.</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -2595,7 +2644,7 @@
                       </c:ext>
                     </c:extLst>
                     <c:strCache>
-                      <c:ptCount val="8"/>
+                      <c:ptCount val="9"/>
                       <c:pt idx="0">
                         <c:v>21.03.</c:v>
                       </c:pt>
@@ -2619,6 +2668,9 @@
                       </c:pt>
                       <c:pt idx="7">
                         <c:v>15.06.</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>03.07.</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -3023,6 +3075,9 @@
                 <c:pt idx="7">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="8">
+                  <c:v>-1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3194,6 +3249,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3529,6 +3587,9 @@
                 <c:pt idx="7">
                   <c:v>-1</c:v>
                 </c:pt>
+                <c:pt idx="8">
+                  <c:v>-1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3699,6 +3760,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>-1</c:v>
                 </c:pt>
               </c:numCache>
@@ -4033,6 +4097,9 @@
                 <c:pt idx="7">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4203,6 +4270,9 @@
                   <c:v>-1</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -4530,6 +4600,9 @@
                 <c:pt idx="7">
                   <c:v>-1</c:v>
                 </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4694,6 +4767,9 @@
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7130,7 +7206,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="43" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -7261,8 +7337,8 @@
       <c r="H7" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="59" t="s">
-        <v>50</v>
+      <c r="I7" s="60" t="s">
+        <v>51</v>
       </c>
       <c r="J7" s="9"/>
       <c r="K7" s="8"/>
@@ -7283,13 +7359,13 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H8" s="42">
-        <v>19</v>
-      </c>
-      <c r="I8" s="64">
-        <v>0.35</v>
+        <v>27</v>
+      </c>
+      <c r="I8" s="69">
+        <v>0.2878787878787879</v>
       </c>
       <c r="J8" s="9"/>
       <c r="K8" s="8"/>
@@ -7310,13 +7386,13 @@
         <v>2</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9" s="42">
-        <v>13</v>
-      </c>
-      <c r="I9" s="64">
-        <v>0.3</v>
+        <v>8</v>
+      </c>
+      <c r="I9" s="69">
+        <v>0.3235294117647059</v>
       </c>
       <c r="J9" s="9"/>
       <c r="K9" s="8"/>
@@ -7342,8 +7418,8 @@
       <c r="H10" s="42">
         <v>4</v>
       </c>
-      <c r="I10" s="64">
-        <v>0.30508474576271188</v>
+      <c r="I10" s="69">
+        <v>0.32835820895522388</v>
       </c>
       <c r="J10" s="9"/>
       <c r="K10" s="8"/>
@@ -7366,11 +7442,11 @@
       <c r="G11" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="H11" s="66">
-        <v>3</v>
-      </c>
-      <c r="I11" s="67">
-        <v>0.26153846153846155</v>
+      <c r="H11" s="72">
+        <v>2</v>
+      </c>
+      <c r="I11" s="73">
+        <v>0.27027027027027029</v>
       </c>
       <c r="J11" s="9"/>
       <c r="K11" s="8"/>
@@ -7507,10 +7583,10 @@
         <v>1</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17" s="42">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D17" s="42">
         <v>1</v>
@@ -7533,7 +7609,7 @@
         <v>1</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M17" s="15">
         <v>7</v>
@@ -7550,10 +7626,10 @@
         <v>2</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" s="42">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D18" s="42"/>
       <c r="E18" s="24"/>
@@ -7561,10 +7637,10 @@
         <v>2</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H18" s="42">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I18" s="42"/>
       <c r="J18" s="24"/>
@@ -7572,10 +7648,10 @@
         <v>2</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M18" s="15">
-        <v>6.5</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="N18" s="42"/>
       <c r="O18" s="9"/>
@@ -7590,7 +7666,7 @@
         <v>2</v>
       </c>
       <c r="C19" s="42">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D19" s="42"/>
       <c r="E19" s="24"/>
@@ -7598,10 +7674,10 @@
         <v>3</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H19" s="42">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I19" s="42"/>
       <c r="J19" s="24"/>
@@ -7612,13 +7688,13 @@
         <v>2</v>
       </c>
       <c r="M19" s="15">
-        <v>5.625</v>
+        <v>5.1111111111111107</v>
       </c>
       <c r="N19" s="42"/>
       <c r="O19" s="9"/>
       <c r="P19" s="8"/>
       <c r="Q19" s="8"/>
-      <c r="S19" s="65"/>
+      <c r="S19" s="71"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
@@ -7628,7 +7704,7 @@
         <v>0</v>
       </c>
       <c r="C20" s="42">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D20" s="42"/>
       <c r="E20" s="24"/>
@@ -7639,7 +7715,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="42">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I20" s="42"/>
       <c r="J20" s="24"/>
@@ -7650,7 +7726,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="15">
-        <v>3.375</v>
+        <v>4.2222222222222223</v>
       </c>
       <c r="N20" s="42"/>
       <c r="O20" s="9"/>
@@ -7684,7 +7760,7 @@
         <v>4</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>24</v>
@@ -7710,7 +7786,7 @@
         <v>4</v>
       </c>
       <c r="M22" s="14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N22" s="14" t="s">
         <v>24</v>
@@ -7724,10 +7800,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C23" s="15">
-        <v>2.4347826086956523</v>
+        <v>2.4230769230769229</v>
       </c>
       <c r="D23" s="42">
         <v>1</v>
@@ -7761,10 +7837,10 @@
         <v>2</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C24" s="15">
-        <v>2.2608695652173911</v>
+        <v>2.1923076923076925</v>
       </c>
       <c r="D24" s="42"/>
       <c r="E24" s="24"/>
@@ -7799,7 +7875,7 @@
         <v>2</v>
       </c>
       <c r="C25" s="15">
-        <v>1.9565217391304348</v>
+        <v>1.7692307692307692</v>
       </c>
       <c r="D25" s="42"/>
       <c r="E25" s="24"/>
@@ -7832,7 +7908,7 @@
         <v>0</v>
       </c>
       <c r="C26" s="15">
-        <v>1.173913043478261</v>
+        <v>1.4615384615384615</v>
       </c>
       <c r="D26" s="42"/>
       <c r="E26" s="24"/>
@@ -7950,7 +8026,7 @@
         <v>4</v>
       </c>
       <c r="M30" s="14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N30" s="14" t="s">
         <v>24</v>
@@ -7964,10 +8040,10 @@
         <v>1</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C31" s="4">
-        <v>70699</v>
+        <v>78740</v>
       </c>
       <c r="D31" s="42">
         <v>1</v>
@@ -7977,10 +8053,10 @@
         <v>1</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31" s="4">
-        <v>8837.375</v>
+        <v>8748.8888888888887</v>
       </c>
       <c r="I31" s="42">
         <v>1</v>
@@ -7990,10 +8066,10 @@
         <v>1</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M31" s="4">
-        <v>3073.8695652173915</v>
+        <v>3028.4615384615386</v>
       </c>
       <c r="N31" s="42">
         <v>1</v>
@@ -8007,10 +8083,10 @@
         <v>2</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32" s="4">
-        <v>69163</v>
+        <v>78675</v>
       </c>
       <c r="D32" s="42"/>
       <c r="E32" s="24"/>
@@ -8018,10 +8094,10 @@
         <v>2</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H32" s="4">
-        <v>8645.375</v>
+        <v>8741.6666666666661</v>
       </c>
       <c r="I32" s="42"/>
       <c r="J32" s="24"/>
@@ -8029,10 +8105,10 @@
         <v>2</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M32" s="4">
-        <v>3007.086956521739</v>
+        <v>3025.9615384615386</v>
       </c>
       <c r="N32" s="42"/>
       <c r="O32" s="8"/>
@@ -8047,7 +8123,7 @@
         <v>2</v>
       </c>
       <c r="C33" s="4">
-        <v>66891</v>
+        <v>74867</v>
       </c>
       <c r="D33" s="42"/>
       <c r="E33" s="24"/>
@@ -8058,7 +8134,7 @@
         <v>2</v>
       </c>
       <c r="H33" s="4">
-        <v>8361.375</v>
+        <v>8318.5555555555547</v>
       </c>
       <c r="I33" s="42"/>
       <c r="J33" s="24"/>
@@ -8069,13 +8145,13 @@
         <v>2</v>
       </c>
       <c r="M33" s="4">
-        <v>2908.304347826087</v>
+        <v>2879.5</v>
       </c>
       <c r="N33" s="42"/>
       <c r="O33" s="8"/>
       <c r="P33" s="8"/>
       <c r="Q33" s="8"/>
-      <c r="S33" s="62"/>
+      <c r="S33" s="67"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
@@ -8085,7 +8161,7 @@
         <v>0</v>
       </c>
       <c r="C34" s="4">
-        <v>64051</v>
+        <v>73628</v>
       </c>
       <c r="D34" s="42"/>
       <c r="E34" s="24"/>
@@ -8096,7 +8172,7 @@
         <v>0</v>
       </c>
       <c r="H34" s="4">
-        <v>8006.375</v>
+        <v>8180.8888888888887</v>
       </c>
       <c r="I34" s="42"/>
       <c r="J34" s="24"/>
@@ -8107,7 +8183,7 @@
         <v>0</v>
       </c>
       <c r="M34" s="4">
-        <v>2784.8260869565215</v>
+        <v>2831.8461538461538</v>
       </c>
       <c r="N34" s="42"/>
       <c r="O34" s="8"/>
@@ -8221,10 +8297,10 @@
         <v>1</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C39" s="42">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D39" s="42">
         <v>1</v>
@@ -8264,10 +8340,10 @@
         <v>2</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C40" s="42">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D40" s="42"/>
       <c r="E40" s="24"/>
@@ -8278,9 +8354,11 @@
         <v>3</v>
       </c>
       <c r="H40" s="4">
-        <v>8995</v>
-      </c>
-      <c r="I40" s="42"/>
+        <v>10794</v>
+      </c>
+      <c r="I40" s="42">
+        <v>1</v>
+      </c>
       <c r="J40" s="24"/>
       <c r="K40" s="5">
         <v>1</v>
@@ -8343,7 +8421,7 @@
         <v>0</v>
       </c>
       <c r="C42" s="42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D42" s="42"/>
       <c r="E42" s="24"/>
@@ -8354,7 +8432,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="4">
-        <v>2313</v>
+        <v>4112</v>
       </c>
       <c r="I42" s="42"/>
       <c r="J42" s="24"/>
@@ -8455,7 +8533,7 @@
         <v>3</v>
       </c>
       <c r="H45" s="42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I45" s="42">
         <v>1</v>
@@ -8532,7 +8610,7 @@
         <v>3</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H47" s="42">
         <v>2</v>
@@ -8546,7 +8624,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N47" s="42"/>
       <c r="O47" s="8"/>
@@ -8566,13 +8644,13 @@
       <c r="D48" s="42"/>
       <c r="E48" s="24"/>
       <c r="F48" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H48" s="42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48" s="42"/>
       <c r="J48" s="24"/>
@@ -8583,7 +8661,7 @@
         <v>3</v>
       </c>
       <c r="M48" s="42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" s="42"/>
       <c r="O48" s="8"/>
@@ -8700,7 +8778,7 @@
         <v>3</v>
       </c>
       <c r="C53" s="4">
-        <v>7070</v>
+        <v>7690</v>
       </c>
       <c r="D53" s="42">
         <v>1</v>
@@ -8713,7 +8791,7 @@
         <v>3</v>
       </c>
       <c r="H53" s="42">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I53" s="42">
         <v>1</v>
@@ -8726,7 +8804,7 @@
         <v>3</v>
       </c>
       <c r="M53" s="4">
-        <v>2920</v>
+        <v>3140</v>
       </c>
       <c r="N53" s="42">
         <v>1</v>
@@ -8740,10 +8818,10 @@
         <v>2</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54" s="4">
-        <v>5390</v>
+        <v>5890</v>
       </c>
       <c r="D54" s="42"/>
       <c r="E54" s="24"/>
@@ -8754,7 +8832,7 @@
         <v>0</v>
       </c>
       <c r="H54" s="42">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I54" s="42"/>
       <c r="J54" s="24"/>
@@ -8765,7 +8843,7 @@
         <v>0</v>
       </c>
       <c r="M54" s="4">
-        <v>2740</v>
+        <v>2940</v>
       </c>
       <c r="N54" s="42"/>
       <c r="O54" s="8"/>
@@ -8777,21 +8855,21 @@
         <v>3</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C55" s="4">
-        <v>5300</v>
+        <v>5740</v>
       </c>
       <c r="D55" s="42"/>
       <c r="E55" s="24"/>
       <c r="F55" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>1</v>
       </c>
       <c r="H55" s="42">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I55" s="42"/>
       <c r="J55" s="24"/>
@@ -8802,7 +8880,7 @@
         <v>1</v>
       </c>
       <c r="M55" s="4">
-        <v>2400</v>
+        <v>2840</v>
       </c>
       <c r="N55" s="42"/>
       <c r="O55" s="8"/>
@@ -8817,7 +8895,7 @@
         <v>2</v>
       </c>
       <c r="C56" s="4">
-        <v>4920</v>
+        <v>5260</v>
       </c>
       <c r="D56" s="42"/>
       <c r="E56" s="24"/>
@@ -8828,7 +8906,7 @@
         <v>2</v>
       </c>
       <c r="H56" s="42">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I56" s="42"/>
       <c r="J56" s="24"/>
@@ -8839,7 +8917,7 @@
         <v>2</v>
       </c>
       <c r="M56" s="4">
-        <v>2320</v>
+        <v>2660</v>
       </c>
       <c r="N56" s="42"/>
       <c r="O56" s="8"/>
@@ -8959,7 +9037,7 @@
         <v>0</v>
       </c>
       <c r="C60" s="42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D60" s="42"/>
       <c r="E60" s="24"/>
@@ -8970,30 +9048,32 @@
         <v>0</v>
       </c>
       <c r="H60" s="4">
-        <v>950</v>
+        <v>1100</v>
       </c>
       <c r="I60" s="42"/>
       <c r="J60" s="24"/>
       <c r="K60" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M60" s="42">
-        <v>5</v>
-      </c>
-      <c r="N60" s="42"/>
+        <v>6</v>
+      </c>
+      <c r="N60" s="42">
+        <v>1</v>
+      </c>
       <c r="O60" s="8"/>
       <c r="P60" s="8"/>
       <c r="Q60" s="8"/>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C61" s="42">
         <v>7</v>
@@ -9007,7 +9087,7 @@
         <v>1</v>
       </c>
       <c r="H61" s="4">
-        <v>800</v>
+        <v>950</v>
       </c>
       <c r="I61" s="42"/>
       <c r="J61" s="24"/>
@@ -9030,15 +9110,15 @@
         <v>4</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62" s="42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D62" s="42"/>
       <c r="E62" s="24"/>
       <c r="F62" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>2</v>
@@ -9129,10 +9209,10 @@
         <v>1</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C65" s="4">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="D65" s="42">
         <v>1</v>
@@ -9172,10 +9252,10 @@
         <v>2</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C66" s="4">
-        <v>1400</v>
+        <v>1700</v>
       </c>
       <c r="D66" s="42"/>
       <c r="E66" s="24"/>
@@ -9265,7 +9345,7 @@
       <c r="I68" s="42"/>
       <c r="J68" s="24"/>
       <c r="K68" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>1</v>
@@ -9594,10 +9674,10 @@
         <v>1</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H79" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I79" s="42">
         <v>1</v>
@@ -9607,10 +9687,10 @@
         <v>1</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M79" s="4">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="N79" s="42">
         <v>1</v>
@@ -9621,15 +9701,17 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C80" s="4">
-        <v>5</v>
-      </c>
-      <c r="D80" s="42"/>
+        <v>6</v>
+      </c>
+      <c r="D80" s="42">
+        <v>1</v>
+      </c>
       <c r="E80" s="24"/>
       <c r="F80" s="5">
         <v>1</v>
@@ -9638,7 +9720,7 @@
         <v>3</v>
       </c>
       <c r="H80" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I80" s="42">
         <v>1</v>
@@ -9648,10 +9730,10 @@
         <v>2</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M80" s="4">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="N80" s="42"/>
       <c r="O80" s="8"/>
@@ -9660,10 +9742,10 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C81" s="4">
         <v>5</v>
@@ -9677,7 +9759,7 @@
         <v>1</v>
       </c>
       <c r="H81" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I81" s="42">
         <v>1</v>
@@ -9690,7 +9772,7 @@
         <v>2</v>
       </c>
       <c r="M81" s="4">
-        <v>190</v>
+        <v>290</v>
       </c>
       <c r="N81" s="42"/>
       <c r="O81" s="8"/>
@@ -9705,7 +9787,7 @@
         <v>0</v>
       </c>
       <c r="C82" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D82" s="42"/>
       <c r="E82" s="24"/>
@@ -9713,10 +9795,10 @@
         <v>1</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H82" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I82" s="42">
         <v>1</v>
@@ -9776,7 +9858,7 @@
         <v>4</v>
       </c>
       <c r="H84" s="14" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I84" s="14" t="s">
         <v>24</v>
@@ -9789,7 +9871,7 @@
         <v>4</v>
       </c>
       <c r="M84" s="14" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="N84" s="14" t="s">
         <v>24</v>
@@ -9803,10 +9885,10 @@
         <v>1</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C85" s="44">
-        <v>10</v>
+        <v>13.333333333333334</v>
       </c>
       <c r="D85" s="42">
         <v>1</v>
@@ -9816,10 +9898,10 @@
         <v>1</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H85" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I85" s="42">
         <v>1</v>
@@ -9829,7 +9911,7 @@
         <v>1</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M85" s="4">
         <v>5</v>
@@ -9839,17 +9921,17 @@
       </c>
       <c r="O85" s="8"/>
       <c r="P85" s="8"/>
-      <c r="Q85" s="60"/>
+      <c r="Q85" s="63"/>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
         <v>2</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C86" s="44">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D86" s="42"/>
       <c r="E86" s="24"/>
@@ -9857,28 +9939,26 @@
         <v>2</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H86" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I86" s="42"/>
       <c r="J86" s="8"/>
       <c r="K86" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M86" s="4">
-        <v>5</v>
-      </c>
-      <c r="N86" s="42">
-        <v>1</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="N86" s="42"/>
       <c r="O86" s="8"/>
       <c r="P86" s="8"/>
-      <c r="Q86" s="60"/>
+      <c r="Q86" s="63"/>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
@@ -9888,7 +9968,7 @@
         <v>2</v>
       </c>
       <c r="C87" s="44">
-        <v>23.75</v>
+        <v>32.222222222222221</v>
       </c>
       <c r="D87" s="42"/>
       <c r="E87" s="24"/>
@@ -9896,7 +9976,7 @@
         <v>3</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H87" s="4">
         <v>11</v>
@@ -9910,12 +9990,12 @@
         <v>0</v>
       </c>
       <c r="M87" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N87" s="42"/>
       <c r="O87" s="8"/>
       <c r="P87" s="8"/>
-      <c r="Q87" s="60"/>
+      <c r="Q87" s="63"/>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
@@ -9925,18 +10005,18 @@
         <v>0</v>
       </c>
       <c r="C88" s="44">
-        <v>46.25</v>
+        <v>41.111111111111114</v>
       </c>
       <c r="D88" s="42"/>
       <c r="E88" s="24"/>
       <c r="F88" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H88" s="4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I88" s="42"/>
       <c r="J88" s="8"/>
@@ -9947,69 +10027,69 @@
         <v>2</v>
       </c>
       <c r="M88" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N88" s="42"/>
       <c r="O88" s="8"/>
       <c r="P88" s="8"/>
-      <c r="Q88" s="60"/>
+      <c r="Q88" s="63"/>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A89" s="60"/>
-      <c r="B89" s="60"/>
-      <c r="C89" s="60"/>
-      <c r="D89" s="60"/>
-      <c r="E89" s="60"/>
-      <c r="F89" s="60"/>
-      <c r="G89" s="60"/>
-      <c r="H89" s="60"/>
-      <c r="I89" s="60"/>
-      <c r="J89" s="60"/>
+      <c r="A89" s="63"/>
+      <c r="B89" s="63"/>
+      <c r="C89" s="63"/>
+      <c r="D89" s="63"/>
+      <c r="E89" s="63"/>
+      <c r="F89" s="63"/>
+      <c r="G89" s="63"/>
+      <c r="H89" s="63"/>
+      <c r="I89" s="63"/>
+      <c r="J89" s="63"/>
       <c r="K89" s="8"/>
       <c r="L89" s="8"/>
       <c r="M89" s="8"/>
       <c r="N89" s="8"/>
       <c r="O89" s="8"/>
       <c r="P89" s="8"/>
-      <c r="Q89" s="60"/>
+      <c r="Q89" s="63"/>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A90" s="60"/>
-      <c r="B90" s="60"/>
-      <c r="C90" s="60"/>
-      <c r="D90" s="60"/>
-      <c r="E90" s="60"/>
-      <c r="F90" s="60"/>
-      <c r="G90" s="60"/>
-      <c r="H90" s="60"/>
-      <c r="I90" s="60"/>
-      <c r="J90" s="60"/>
+      <c r="A90" s="63"/>
+      <c r="B90" s="63"/>
+      <c r="C90" s="63"/>
+      <c r="D90" s="63"/>
+      <c r="E90" s="63"/>
+      <c r="F90" s="63"/>
+      <c r="G90" s="63"/>
+      <c r="H90" s="63"/>
+      <c r="I90" s="63"/>
+      <c r="J90" s="63"/>
       <c r="K90" s="8"/>
       <c r="L90" s="8"/>
       <c r="M90" s="8"/>
       <c r="N90" s="8"/>
       <c r="O90" s="8"/>
       <c r="P90" s="8"/>
-      <c r="Q90" s="60"/>
+      <c r="Q90" s="63"/>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A91" s="60"/>
-      <c r="B91" s="60"/>
-      <c r="C91" s="60"/>
-      <c r="D91" s="60"/>
-      <c r="E91" s="60"/>
-      <c r="F91" s="60"/>
-      <c r="G91" s="60"/>
-      <c r="H91" s="60"/>
-      <c r="I91" s="60"/>
-      <c r="J91" s="60"/>
+      <c r="A91" s="63"/>
+      <c r="B91" s="63"/>
+      <c r="C91" s="63"/>
+      <c r="D91" s="63"/>
+      <c r="E91" s="63"/>
+      <c r="F91" s="63"/>
+      <c r="G91" s="63"/>
+      <c r="H91" s="63"/>
+      <c r="I91" s="63"/>
+      <c r="J91" s="63"/>
       <c r="K91" s="8"/>
       <c r="L91" s="8"/>
       <c r="M91" s="8"/>
       <c r="N91" s="8"/>
       <c r="O91" s="8"/>
       <c r="P91" s="8"/>
-      <c r="Q91" s="60"/>
+      <c r="Q91" s="63"/>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="8"/>
@@ -10028,11 +10108,11 @@
       <c r="N92" s="8"/>
       <c r="O92" s="8"/>
       <c r="P92" s="8"/>
-      <c r="Q92" s="60"/>
+      <c r="Q92" s="63"/>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B93" s="8"/>
       <c r="C93" s="8"/>
@@ -10049,7 +10129,7 @@
       <c r="N93" s="8"/>
       <c r="O93" s="8"/>
       <c r="P93" s="8"/>
-      <c r="Q93" s="60"/>
+      <c r="Q93" s="63"/>
     </row>
     <row r="94" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A94" s="10"/>
@@ -10062,23 +10142,23 @@
       <c r="H94" s="8"/>
       <c r="I94" s="8"/>
       <c r="J94" s="8"/>
-      <c r="K94" s="68" t="s">
-        <v>64</v>
-      </c>
-      <c r="L94" s="68"/>
-      <c r="M94" s="69" t="s">
-        <v>65</v>
-      </c>
-      <c r="N94" s="69" t="s">
-        <v>66</v>
-      </c>
-      <c r="O94" s="69" t="s">
-        <v>67</v>
-      </c>
-      <c r="P94" s="69" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q94" s="60"/>
+      <c r="K94" s="61" t="s">
+        <v>52</v>
+      </c>
+      <c r="L94" s="61"/>
+      <c r="M94" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="N94" s="62" t="s">
+        <v>60</v>
+      </c>
+      <c r="O94" s="62" t="s">
+        <v>55</v>
+      </c>
+      <c r="P94" s="62" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q94" s="63"/>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="8"/>
@@ -10097,22 +10177,22 @@
       <c r="L95" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M95" s="70">
-        <v>0.25</v>
-      </c>
-      <c r="N95" s="71">
-        <v>2</v>
-      </c>
-      <c r="O95" s="70">
-        <v>0</v>
-      </c>
-      <c r="P95" s="70">
-        <v>0</v>
-      </c>
-      <c r="Q95" s="60"/>
+      <c r="M95" s="65">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="N95" s="70">
+        <v>3</v>
+      </c>
+      <c r="O95" s="65">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="P95" s="65">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="Q95" s="63"/>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A96" s="61" t="s">
+      <c r="A96" s="64" t="s">
         <v>0</v>
       </c>
       <c r="B96" s="8"/>
@@ -10130,19 +10210,19 @@
       <c r="L96" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M96" s="72">
-        <v>0.375</v>
-      </c>
-      <c r="N96" s="73">
+      <c r="M96" s="55">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="N96" s="66">
         <v>3</v>
       </c>
-      <c r="O96" s="70">
+      <c r="O96" s="65">
         <v>0.33333333333333331</v>
       </c>
-      <c r="P96" s="72">
-        <v>0.125</v>
-      </c>
-      <c r="Q96" s="60"/>
+      <c r="P96" s="55">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="Q96" s="63"/>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A97" s="8"/>
@@ -10159,21 +10239,21 @@
         <v>0</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M97" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="N97" s="73">
+        <v>48</v>
+      </c>
+      <c r="M97" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="N97" s="66">
         <v>0</v>
       </c>
-      <c r="O97" s="70" t="s">
-        <v>73</v>
-      </c>
-      <c r="P97" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q97" s="60"/>
+      <c r="O97" s="65" t="s">
+        <v>54</v>
+      </c>
+      <c r="P97" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q97" s="63"/>
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A98" s="8"/>
@@ -10192,22 +10272,22 @@
       <c r="L98" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="M98" s="72">
-        <v>0.375</v>
-      </c>
-      <c r="N98" s="73">
+      <c r="M98" s="55">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="N98" s="66">
         <v>3</v>
       </c>
-      <c r="O98" s="70">
+      <c r="O98" s="65">
         <v>0.33333333333333331</v>
       </c>
-      <c r="P98" s="72">
-        <v>0.125</v>
-      </c>
-      <c r="Q98" s="60"/>
+      <c r="P98" s="55">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="Q98" s="63"/>
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A99" s="61" t="s">
+      <c r="A99" s="64" t="s">
         <v>1</v>
       </c>
       <c r="B99" s="8"/>
@@ -10223,24 +10303,24 @@
         <v>0</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="M99" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="N99" s="73">
+        <v>63</v>
+      </c>
+      <c r="M99" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="N99" s="66">
         <v>0</v>
       </c>
-      <c r="O99" s="70" t="s">
-        <v>73</v>
-      </c>
-      <c r="P99" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q99" s="60"/>
+      <c r="O99" s="65" t="s">
+        <v>54</v>
+      </c>
+      <c r="P99" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q99" s="63"/>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A100" s="61"/>
+      <c r="A100" s="64"/>
       <c r="B100" s="8"/>
       <c r="C100" s="8"/>
       <c r="D100" s="8"/>
@@ -10254,24 +10334,24 @@
         <v>0</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="M100" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="N100" s="73">
+        <v>66</v>
+      </c>
+      <c r="M100" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="N100" s="66">
         <v>0</v>
       </c>
-      <c r="O100" s="70" t="s">
-        <v>73</v>
-      </c>
-      <c r="P100" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q100" s="60"/>
+      <c r="O100" s="65" t="s">
+        <v>54</v>
+      </c>
+      <c r="P100" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q100" s="63"/>
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A101" s="61"/>
+      <c r="A101" s="64"/>
       <c r="B101" s="8"/>
       <c r="C101" s="8"/>
       <c r="D101" s="8"/>
@@ -10287,22 +10367,22 @@
       <c r="L101" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M101" s="72">
-        <v>0.375</v>
-      </c>
-      <c r="N101" s="73">
+      <c r="M101" s="55">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="N101" s="66">
         <v>3</v>
       </c>
-      <c r="O101" s="70">
+      <c r="O101" s="65">
         <v>0.66666666666666663</v>
       </c>
-      <c r="P101" s="72">
-        <v>0.25</v>
-      </c>
-      <c r="Q101" s="60"/>
+      <c r="P101" s="55">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="Q101" s="63"/>
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A102" s="61" t="s">
+      <c r="A102" s="64" t="s">
         <v>2</v>
       </c>
       <c r="B102" s="8"/>
@@ -10318,24 +10398,24 @@
         <v>3</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="M102" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="N102" s="73">
+        <v>63</v>
+      </c>
+      <c r="M102" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="N102" s="66">
         <v>0</v>
       </c>
-      <c r="O102" s="70" t="s">
-        <v>73</v>
-      </c>
-      <c r="P102" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q102" s="60"/>
+      <c r="O102" s="65" t="s">
+        <v>54</v>
+      </c>
+      <c r="P102" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q102" s="63"/>
     </row>
     <row r="103" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A103" s="61"/>
+      <c r="A103" s="64"/>
       <c r="B103" s="8"/>
       <c r="C103" s="8"/>
       <c r="D103" s="8"/>
@@ -10351,22 +10431,22 @@
       <c r="L103" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="M103" s="72">
-        <v>0.375</v>
-      </c>
-      <c r="N103" s="73">
+      <c r="M103" s="55">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="N103" s="66">
         <v>3</v>
       </c>
-      <c r="O103" s="70">
-        <v>1</v>
-      </c>
-      <c r="P103" s="72">
-        <v>0.375</v>
-      </c>
-      <c r="Q103" s="60"/>
+      <c r="O103" s="65">
+        <v>1</v>
+      </c>
+      <c r="P103" s="55">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="Q103" s="63"/>
     </row>
     <row r="104" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A104" s="61"/>
+      <c r="A104" s="64"/>
       <c r="B104" s="8"/>
       <c r="C104" s="8"/>
       <c r="D104" s="8"/>
@@ -10380,24 +10460,24 @@
         <v>3</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M104" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="N104" s="73">
+        <v>48</v>
+      </c>
+      <c r="M104" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="N104" s="66">
         <v>0</v>
       </c>
-      <c r="O104" s="70" t="s">
-        <v>73</v>
-      </c>
-      <c r="P104" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q104" s="60"/>
+      <c r="O104" s="65" t="s">
+        <v>54</v>
+      </c>
+      <c r="P104" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q104" s="63"/>
     </row>
     <row r="105" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A105" s="61" t="s">
+      <c r="A105" s="64" t="s">
         <v>3</v>
       </c>
       <c r="B105" s="8"/>
@@ -10413,21 +10493,21 @@
         <v>1</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M105" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="N105" s="73">
+        <v>48</v>
+      </c>
+      <c r="M105" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="N105" s="66">
         <v>0</v>
       </c>
-      <c r="O105" s="70" t="s">
-        <v>73</v>
-      </c>
-      <c r="P105" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q105" s="60"/>
+      <c r="O105" s="65" t="s">
+        <v>54</v>
+      </c>
+      <c r="P105" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q105" s="63"/>
     </row>
     <row r="106" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A106" s="8"/>
@@ -10446,19 +10526,19 @@
       <c r="L106" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="M106" s="72">
-        <v>0.25</v>
-      </c>
-      <c r="N106" s="73">
-        <v>2</v>
-      </c>
-      <c r="O106" s="70">
-        <v>1</v>
-      </c>
-      <c r="P106" s="72">
-        <v>0.25</v>
-      </c>
-      <c r="Q106" s="60"/>
+      <c r="M106" s="55">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="N106" s="66">
+        <v>3</v>
+      </c>
+      <c r="O106" s="65">
+        <v>0.5</v>
+      </c>
+      <c r="P106" s="55">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="Q106" s="63"/>
     </row>
     <row r="107" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A107" s="8"/>
@@ -10475,21 +10555,21 @@
         <v>1</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="M107" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="N107" s="73">
+        <v>63</v>
+      </c>
+      <c r="M107" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="N107" s="66">
         <v>0</v>
       </c>
-      <c r="O107" s="70" t="s">
-        <v>73</v>
-      </c>
-      <c r="P107" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q107" s="60"/>
+      <c r="O107" s="65" t="s">
+        <v>54</v>
+      </c>
+      <c r="P107" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q107" s="63"/>
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A108" s="8"/>
@@ -10506,19 +10586,19 @@
         <v>1</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="M108" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="N108" s="73">
+        <v>66</v>
+      </c>
+      <c r="M108" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="N108" s="66">
         <v>0</v>
       </c>
-      <c r="O108" s="70" t="s">
-        <v>73</v>
-      </c>
-      <c r="P108" s="72" t="s">
-        <v>73</v>
+      <c r="O108" s="65" t="s">
+        <v>54</v>
+      </c>
+      <c r="P108" s="55" t="s">
+        <v>54</v>
       </c>
       <c r="Q108" s="8"/>
     </row>
@@ -10536,7 +10616,7 @@
       <c r="N109" s="8"/>
       <c r="O109" s="8"/>
       <c r="P109" s="8"/>
-      <c r="Q109" s="60"/>
+      <c r="Q109" s="63"/>
     </row>
     <row r="110" spans="1:19" s="49" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="45" t="s">
@@ -10551,12 +10631,12 @@
       <c r="K110" s="8"/>
       <c r="L110" s="8"/>
       <c r="M110" s="8" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="N110" s="8"/>
       <c r="O110" s="8"/>
       <c r="P110" s="8"/>
-      <c r="Q110" s="60"/>
+      <c r="Q110" s="63"/>
       <c r="S110"/>
     </row>
     <row r="111" spans="1:19" x14ac:dyDescent="0.25">
@@ -10567,7 +10647,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K111" s="8"/>
       <c r="L111" s="8"/>
@@ -10575,31 +10655,29 @@
       <c r="N111" s="8"/>
       <c r="O111" s="8"/>
       <c r="P111" s="8"/>
-      <c r="Q111" s="60"/>
+      <c r="Q111" s="63"/>
     </row>
     <row r="112" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A112" s="46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C112" s="20">
-        <v>19</v>
-      </c>
-      <c r="K112" s="8"/>
-      <c r="L112" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="M112" s="8">
+        <v>8</v>
+      </c>
+      <c r="L112" s="74" t="s">
+        <v>59</v>
+      </c>
+      <c r="M112" s="75">
         <v>0</v>
       </c>
-      <c r="N112" s="8"/>
-      <c r="O112" s="8">
-        <v>-0.125</v>
-      </c>
-      <c r="P112" s="8"/>
-      <c r="Q112" s="60"/>
+      <c r="N112" s="75"/>
+      <c r="O112" s="76">
+        <v>-5.555555555555558E-2</v>
+      </c>
+      <c r="Q112" s="63"/>
     </row>
     <row r="113" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A113" s="46">
@@ -10614,13 +10692,13 @@
     </row>
     <row r="114" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A114" s="46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C114" s="20">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="115" spans="1:34" x14ac:dyDescent="0.25">
@@ -10639,13 +10717,13 @@
       <c r="C117" s="20"/>
     </row>
     <row r="118" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="56"/>
-      <c r="B118" s="55"/>
-      <c r="C118" s="57"/>
+      <c r="A118" s="57"/>
+      <c r="B118" s="56"/>
+      <c r="C118" s="58"/>
     </row>
     <row r="120" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="122" spans="1:34" x14ac:dyDescent="0.25">
@@ -10778,7 +10856,9 @@
       <c r="I123" s="5">
         <v>-1</v>
       </c>
-      <c r="J123" s="5"/>
+      <c r="J123" s="5">
+        <v>1</v>
+      </c>
       <c r="K123" s="5"/>
       <c r="L123" s="5"/>
       <c r="M123" s="5"/>
@@ -10832,7 +10912,9 @@
       <c r="I124" s="5">
         <v>1</v>
       </c>
-      <c r="J124" s="5"/>
+      <c r="J124" s="5">
+        <v>-1</v>
+      </c>
       <c r="K124" s="5"/>
       <c r="L124" s="5"/>
       <c r="M124" s="5"/>
@@ -10886,7 +10968,9 @@
       <c r="I125" s="5">
         <v>-1</v>
       </c>
-      <c r="J125" s="5"/>
+      <c r="J125" s="5">
+        <v>-1</v>
+      </c>
       <c r="K125" s="5"/>
       <c r="L125" s="5"/>
       <c r="M125" s="5"/>
@@ -10940,7 +11024,9 @@
       <c r="I126" s="5">
         <v>1</v>
       </c>
-      <c r="J126" s="5"/>
+      <c r="J126" s="5">
+        <v>1</v>
+      </c>
       <c r="K126" s="5"/>
       <c r="L126" s="5"/>
       <c r="M126" s="5"/>
@@ -10972,47 +11058,49 @@
       </c>
     </row>
     <row r="131" spans="1:34" s="49" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B131" s="58" t="s">
-        <v>56</v>
-      </c>
-      <c r="C131" s="58" t="s">
-        <v>58</v>
-      </c>
-      <c r="D131" s="58" t="s">
-        <v>59</v>
-      </c>
-      <c r="E131" s="58" t="s">
-        <v>60</v>
-      </c>
-      <c r="F131" s="58" t="s">
-        <v>61</v>
-      </c>
-      <c r="G131" s="58" t="s">
-        <v>63</v>
-      </c>
-      <c r="H131" s="58" t="s">
-        <v>62</v>
-      </c>
-      <c r="I131" s="58" t="s">
+      <c r="B131" s="59" t="s">
+        <v>67</v>
+      </c>
+      <c r="C131" s="59" t="s">
+        <v>69</v>
+      </c>
+      <c r="D131" s="59" t="s">
+        <v>70</v>
+      </c>
+      <c r="E131" s="59" t="s">
+        <v>71</v>
+      </c>
+      <c r="F131" s="59" t="s">
+        <v>72</v>
+      </c>
+      <c r="G131" s="59" t="s">
+        <v>74</v>
+      </c>
+      <c r="H131" s="59" t="s">
+        <v>73</v>
+      </c>
+      <c r="I131" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="J131" s="58"/>
-      <c r="K131" s="58"/>
-      <c r="L131" s="58"/>
-      <c r="M131" s="58"/>
-      <c r="N131" s="58"/>
-      <c r="O131" s="58"/>
-      <c r="P131" s="58"/>
-      <c r="Q131" s="58"/>
-      <c r="R131" s="58"/>
-      <c r="S131" s="58"/>
+      <c r="J131" s="59" t="s">
+        <v>76</v>
+      </c>
+      <c r="K131" s="59"/>
+      <c r="L131" s="59"/>
+      <c r="M131" s="59"/>
+      <c r="N131" s="59"/>
+      <c r="O131" s="59"/>
+      <c r="P131" s="59"/>
+      <c r="Q131" s="59"/>
+      <c r="R131" s="59"/>
+      <c r="S131" s="59"/>
       <c r="T131" s="50"/>
       <c r="U131" s="50"/>
       <c r="V131" s="50"/>
       <c r="W131" s="50"/>
       <c r="X131" s="50"/>
-      <c r="Y131" s="58"/>
-      <c r="Z131" s="58"/>
+      <c r="Y131" s="59"/>
+      <c r="Z131" s="59"/>
       <c r="AA131" s="50"/>
       <c r="AB131" s="50"/>
       <c r="AC131" s="50"/>
@@ -11050,11 +11138,13 @@
       <c r="I132" s="5">
         <v>3</v>
       </c>
-      <c r="J132" s="5"/>
+      <c r="J132" s="5">
+        <v>2</v>
+      </c>
       <c r="K132" s="5"/>
       <c r="L132" s="5"/>
       <c r="M132" s="5"/>
-      <c r="N132" s="63"/>
+      <c r="N132" s="68"/>
       <c r="O132" s="5"/>
       <c r="P132" s="5"/>
       <c r="Q132" s="5"/>
@@ -11104,11 +11194,13 @@
       <c r="I133" s="5">
         <v>19</v>
       </c>
-      <c r="J133" s="5"/>
+      <c r="J133" s="5">
+        <v>8</v>
+      </c>
       <c r="K133" s="5"/>
       <c r="L133" s="5"/>
       <c r="M133" s="5"/>
-      <c r="N133" s="63"/>
+      <c r="N133" s="68"/>
       <c r="O133" s="5"/>
       <c r="P133" s="5"/>
       <c r="Q133" s="5"/>
@@ -11158,11 +11250,13 @@
       <c r="I134" s="5">
         <v>4</v>
       </c>
-      <c r="J134" s="5"/>
+      <c r="J134" s="5">
+        <v>4</v>
+      </c>
       <c r="K134" s="5"/>
       <c r="L134" s="5"/>
       <c r="M134" s="5"/>
-      <c r="N134" s="63"/>
+      <c r="N134" s="68"/>
       <c r="O134" s="5"/>
       <c r="P134" s="5"/>
       <c r="Q134" s="5"/>
@@ -11212,11 +11306,13 @@
       <c r="I135" s="5">
         <v>13</v>
       </c>
-      <c r="J135" s="5"/>
+      <c r="J135" s="5">
+        <v>27</v>
+      </c>
       <c r="K135" s="5"/>
       <c r="L135" s="5"/>
       <c r="M135" s="5"/>
-      <c r="N135" s="63"/>
+      <c r="N135" s="68"/>
       <c r="O135" s="5"/>
       <c r="P135" s="5"/>
       <c r="Q135" s="5"/>
@@ -11252,7 +11348,7 @@
       <c r="K136" s="5"/>
       <c r="L136" s="5"/>
       <c r="M136" s="5"/>
-      <c r="N136" s="63"/>
+      <c r="N136" s="68"/>
       <c r="O136" s="5"/>
       <c r="P136" s="5"/>
       <c r="Q136" s="5"/>
@@ -11288,7 +11384,7 @@
       <c r="K137" s="5"/>
       <c r="L137" s="5"/>
       <c r="M137" s="5"/>
-      <c r="N137" s="63"/>
+      <c r="N137" s="68"/>
       <c r="O137" s="5"/>
       <c r="P137" s="5"/>
       <c r="Q137" s="5"/>
@@ -11384,42 +11480,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A132:A139">
-    <cfRule type="containsText" dxfId="34" priority="1176" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="34" priority="1197" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A132)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A110:C118">
-    <cfRule type="containsText" dxfId="33" priority="1135" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="33" priority="1156" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A110)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:D20">
-    <cfRule type="containsText" dxfId="32" priority="59" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="32" priority="80" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22:D27">
-    <cfRule type="containsText" dxfId="31" priority="24" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="31" priority="45" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:D34">
-    <cfRule type="containsText" dxfId="30" priority="41" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="30" priority="62" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38:D42">
-    <cfRule type="containsText" dxfId="29" priority="38" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="29" priority="59" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44:D48">
-    <cfRule type="containsText" dxfId="28" priority="14" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="28" priority="12" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A44)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:D56">
-    <cfRule type="containsText" dxfId="27" priority="390" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="27" priority="411" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A52)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11429,7 +11525,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64:D68">
-    <cfRule type="containsText" dxfId="25" priority="8" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="25" priority="48" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A64)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11439,52 +11535,52 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A78:D82">
-    <cfRule type="containsText" dxfId="23" priority="1" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="23" priority="2" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A78)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A84:D88">
-    <cfRule type="containsText" dxfId="22" priority="17" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="22" priority="38" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A84)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:I11">
-    <cfRule type="containsText" dxfId="21" priority="208" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="21" priority="229" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:I20">
-    <cfRule type="containsText" dxfId="20" priority="44" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="20" priority="65" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F22:I26">
-    <cfRule type="containsText" dxfId="19" priority="10" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="19" priority="16" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:I34">
-    <cfRule type="containsText" dxfId="18" priority="40" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="18" priority="61" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F38:I42">
-    <cfRule type="containsText" dxfId="17" priority="37" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="17" priority="15" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F44:I48">
-    <cfRule type="containsText" dxfId="16" priority="35" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="16" priority="11" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F44)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52:I56">
-    <cfRule type="containsText" dxfId="15" priority="21" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="15" priority="10" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F52)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F58:I62">
-    <cfRule type="containsText" dxfId="14" priority="137" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="14" priority="23" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F58)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11494,52 +11590,52 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F70:I74">
-    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="12" priority="3" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F70)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F78:I82">
-    <cfRule type="containsText" dxfId="11" priority="19" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="11" priority="40" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F78)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F84:I88">
-    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F84)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16:N20">
-    <cfRule type="containsText" dxfId="9" priority="25" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="9" priority="46" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K22:N26">
-    <cfRule type="containsText" dxfId="8" priority="329" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="8" priority="350" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K30:N34">
-    <cfRule type="containsText" dxfId="7" priority="39" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="7" priority="60" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K38:N42">
-    <cfRule type="containsText" dxfId="6" priority="143" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="6" priority="13" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K44:N48">
-    <cfRule type="containsText" dxfId="5" priority="30" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="5" priority="51" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K44)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K52:N56">
-    <cfRule type="containsText" dxfId="4" priority="378" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="4" priority="399" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K52)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K58:N62">
-    <cfRule type="containsText" dxfId="3" priority="13" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="3" priority="8" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K58)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11549,12 +11645,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K78:N82">
-    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="1" priority="39" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K78)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K84:N88">
-    <cfRule type="containsText" dxfId="0" priority="11" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="0" priority="27" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K84)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Statistik_Jassen.xlsx
+++ b/Statistik_Jassen.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meine Ablage\Jassen Wädi\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FBAA36C-40AD-418E-AD69-1C62B82AF1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1319A1A4-30F7-415E-A8DD-8292564CCCC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A8FCF452-0EF5-42A7-A382-1701488C7232}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="78">
   <si>
     <t>Fuchs</t>
   </si>
@@ -273,6 +273,9 @@
   </si>
   <si>
     <t>03.07.</t>
+  </si>
+  <si>
+    <t>17.08.</t>
   </si>
 </sst>
 </file>
@@ -1511,7 +1514,7 @@
             <c:strRef>
               <c:f>'Gesamtranking Print'!$B$131:$AH$131</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>21.03.</c:v>
                 </c:pt>
@@ -1538,6 +1541,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>03.07.</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>17.08.</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1573,6 +1579,9 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
@@ -1677,7 +1686,7 @@
             <c:strRef>
               <c:f>'Gesamtranking Print'!$B$131:$AH$131</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>21.03.</c:v>
                 </c:pt>
@@ -1704,6 +1713,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>03.07.</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>17.08.</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1739,6 +1751,9 @@
                   <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
@@ -1843,7 +1858,7 @@
             <c:strRef>
               <c:f>'Gesamtranking Print'!$B$131:$AH$131</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>21.03.</c:v>
                 </c:pt>
@@ -1870,6 +1885,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>03.07.</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>17.08.</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1905,6 +1923,9 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
@@ -2009,7 +2030,7 @@
             <c:strRef>
               <c:f>'Gesamtranking Print'!$B$131:$AH$131</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>21.03.</c:v>
                 </c:pt>
@@ -2036,6 +2057,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>03.07.</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>17.08.</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2071,6 +2095,9 @@
                   <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>27</c:v>
                 </c:pt>
               </c:numCache>
@@ -2241,7 +2268,7 @@
                       </c:ext>
                     </c:extLst>
                     <c:strCache>
-                      <c:ptCount val="9"/>
+                      <c:ptCount val="10"/>
                       <c:pt idx="0">
                         <c:v>21.03.</c:v>
                       </c:pt>
@@ -2268,6 +2295,9 @@
                       </c:pt>
                       <c:pt idx="8">
                         <c:v>03.07.</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>17.08.</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -2439,7 +2469,7 @@
                       </c:ext>
                     </c:extLst>
                     <c:strCache>
-                      <c:ptCount val="9"/>
+                      <c:ptCount val="10"/>
                       <c:pt idx="0">
                         <c:v>21.03.</c:v>
                       </c:pt>
@@ -2466,6 +2496,9 @@
                       </c:pt>
                       <c:pt idx="8">
                         <c:v>03.07.</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>17.08.</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -2644,7 +2677,7 @@
                       </c:ext>
                     </c:extLst>
                     <c:strCache>
-                      <c:ptCount val="9"/>
+                      <c:ptCount val="10"/>
                       <c:pt idx="0">
                         <c:v>21.03.</c:v>
                       </c:pt>
@@ -2671,6 +2704,9 @@
                       </c:pt>
                       <c:pt idx="8">
                         <c:v>03.07.</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>17.08.</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -3078,6 +3114,9 @@
                 <c:pt idx="8">
                   <c:v>-1</c:v>
                 </c:pt>
+                <c:pt idx="9">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3252,6 +3291,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3590,6 +3632,9 @@
                 <c:pt idx="8">
                   <c:v>-1</c:v>
                 </c:pt>
+                <c:pt idx="9">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3764,6 +3809,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4100,6 +4148,9 @@
                 <c:pt idx="8">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="9">
+                  <c:v>-1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4274,6 +4325,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4603,6 +4657,9 @@
                 <c:pt idx="8">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="9">
+                  <c:v>-1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4770,6 +4827,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7362,10 +7422,10 @@
         <v>3</v>
       </c>
       <c r="H8" s="42">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I8" s="69">
-        <v>0.2878787878787879</v>
+        <v>0.28169014084507044</v>
       </c>
       <c r="J8" s="9"/>
       <c r="K8" s="8"/>
@@ -7389,10 +7449,10 @@
         <v>1</v>
       </c>
       <c r="H9" s="42">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I9" s="69">
-        <v>0.3235294117647059</v>
+        <v>0.31506849315068491</v>
       </c>
       <c r="J9" s="9"/>
       <c r="K9" s="8"/>
@@ -7419,7 +7479,7 @@
         <v>4</v>
       </c>
       <c r="I10" s="69">
-        <v>0.32835820895522388</v>
+        <v>0.32876712328767121</v>
       </c>
       <c r="J10" s="9"/>
       <c r="K10" s="8"/>
@@ -7443,10 +7503,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11" s="73">
-        <v>0.27027027027027029</v>
+        <v>0.29113924050632911</v>
       </c>
       <c r="J11" s="9"/>
       <c r="K11" s="8"/>
@@ -7586,7 +7646,7 @@
         <v>3</v>
       </c>
       <c r="C17" s="42">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D17" s="42">
         <v>1</v>
@@ -7599,7 +7659,7 @@
         <v>2</v>
       </c>
       <c r="H17" s="42">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I17" s="42">
         <v>1</v>
@@ -7612,7 +7672,7 @@
         <v>3</v>
       </c>
       <c r="M17" s="15">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="N17" s="42">
         <v>1</v>
@@ -7629,7 +7689,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="42">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D18" s="42"/>
       <c r="E18" s="24"/>
@@ -7640,7 +7700,7 @@
         <v>3</v>
       </c>
       <c r="H18" s="42">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I18" s="42"/>
       <c r="J18" s="24"/>
@@ -7651,7 +7711,7 @@
         <v>1</v>
       </c>
       <c r="M18" s="15">
-        <v>6.333333333333333</v>
+        <v>6.1</v>
       </c>
       <c r="N18" s="42"/>
       <c r="O18" s="9"/>
@@ -7666,7 +7726,7 @@
         <v>2</v>
       </c>
       <c r="C19" s="42">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D19" s="42"/>
       <c r="E19" s="24"/>
@@ -7677,7 +7737,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="42">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I19" s="42"/>
       <c r="J19" s="24"/>
@@ -7688,7 +7748,7 @@
         <v>2</v>
       </c>
       <c r="M19" s="15">
-        <v>5.1111111111111107</v>
+        <v>5</v>
       </c>
       <c r="N19" s="42"/>
       <c r="O19" s="9"/>
@@ -7704,7 +7764,7 @@
         <v>0</v>
       </c>
       <c r="C20" s="42">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D20" s="42"/>
       <c r="E20" s="24"/>
@@ -7715,7 +7775,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="42">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I20" s="42"/>
       <c r="J20" s="24"/>
@@ -7726,7 +7786,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="15">
-        <v>4.2222222222222223</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N20" s="42"/>
       <c r="O20" s="9"/>
@@ -7803,7 +7863,7 @@
         <v>3</v>
       </c>
       <c r="C23" s="15">
-        <v>2.4230769230769229</v>
+        <v>2.3571428571428572</v>
       </c>
       <c r="D23" s="42">
         <v>1</v>
@@ -7840,7 +7900,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="15">
-        <v>2.1923076923076925</v>
+        <v>2.1785714285714284</v>
       </c>
       <c r="D24" s="42"/>
       <c r="E24" s="24"/>
@@ -7875,7 +7935,7 @@
         <v>2</v>
       </c>
       <c r="C25" s="15">
-        <v>1.7692307692307692</v>
+        <v>1.7857142857142858</v>
       </c>
       <c r="D25" s="42"/>
       <c r="E25" s="24"/>
@@ -7908,7 +7968,7 @@
         <v>0</v>
       </c>
       <c r="C26" s="15">
-        <v>1.4615384615384615</v>
+        <v>1.4642857142857142</v>
       </c>
       <c r="D26" s="42"/>
       <c r="E26" s="24"/>
@@ -8040,10 +8100,10 @@
         <v>1</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31" s="4">
-        <v>78740</v>
+        <v>84529</v>
       </c>
       <c r="D31" s="42">
         <v>1</v>
@@ -8053,10 +8113,10 @@
         <v>1</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H31" s="4">
-        <v>8748.8888888888887</v>
+        <v>8452.9</v>
       </c>
       <c r="I31" s="42">
         <v>1</v>
@@ -8066,10 +8126,10 @@
         <v>1</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M31" s="4">
-        <v>3028.4615384615386</v>
+        <v>3018.8928571428573</v>
       </c>
       <c r="N31" s="42">
         <v>1</v>
@@ -8083,10 +8143,10 @@
         <v>2</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" s="4">
-        <v>78675</v>
+        <v>84263</v>
       </c>
       <c r="D32" s="42"/>
       <c r="E32" s="24"/>
@@ -8094,10 +8154,10 @@
         <v>2</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H32" s="4">
-        <v>8741.6666666666661</v>
+        <v>8426.2999999999993</v>
       </c>
       <c r="I32" s="42"/>
       <c r="J32" s="24"/>
@@ -8105,10 +8165,10 @@
         <v>2</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M32" s="4">
-        <v>3025.9615384615386</v>
+        <v>3009.3928571428573</v>
       </c>
       <c r="N32" s="42"/>
       <c r="O32" s="8"/>
@@ -8123,7 +8183,7 @@
         <v>2</v>
       </c>
       <c r="C33" s="4">
-        <v>74867</v>
+        <v>80721</v>
       </c>
       <c r="D33" s="42"/>
       <c r="E33" s="24"/>
@@ -8134,7 +8194,7 @@
         <v>2</v>
       </c>
       <c r="H33" s="4">
-        <v>8318.5555555555547</v>
+        <v>8072.1</v>
       </c>
       <c r="I33" s="42"/>
       <c r="J33" s="24"/>
@@ -8145,7 +8205,7 @@
         <v>2</v>
       </c>
       <c r="M33" s="4">
-        <v>2879.5</v>
+        <v>2882.8928571428573</v>
       </c>
       <c r="N33" s="42"/>
       <c r="O33" s="8"/>
@@ -8161,7 +8221,7 @@
         <v>0</v>
       </c>
       <c r="C34" s="4">
-        <v>73628</v>
+        <v>79151</v>
       </c>
       <c r="D34" s="42"/>
       <c r="E34" s="24"/>
@@ -8172,7 +8232,7 @@
         <v>0</v>
       </c>
       <c r="H34" s="4">
-        <v>8180.8888888888887</v>
+        <v>7915.1</v>
       </c>
       <c r="I34" s="42"/>
       <c r="J34" s="24"/>
@@ -8183,7 +8243,7 @@
         <v>0</v>
       </c>
       <c r="M34" s="4">
-        <v>2831.8461538461538</v>
+        <v>2826.8214285714284</v>
       </c>
       <c r="N34" s="42"/>
       <c r="O34" s="8"/>
@@ -8297,7 +8357,7 @@
         <v>1</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C39" s="42">
         <v>16</v>
@@ -8313,7 +8373,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="4">
-        <v>10794</v>
+        <v>11565</v>
       </c>
       <c r="I39" s="42">
         <v>1</v>
@@ -8337,15 +8397,17 @@
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C40" s="42">
-        <v>15</v>
-      </c>
-      <c r="D40" s="42"/>
+        <v>16</v>
+      </c>
+      <c r="D40" s="42">
+        <v>1</v>
+      </c>
       <c r="E40" s="24"/>
       <c r="F40" s="5">
         <v>2</v>
@@ -8356,9 +8418,7 @@
       <c r="H40" s="4">
         <v>10794</v>
       </c>
-      <c r="I40" s="42">
-        <v>1</v>
-      </c>
+      <c r="I40" s="42"/>
       <c r="J40" s="24"/>
       <c r="K40" s="5">
         <v>1</v>
@@ -8384,7 +8444,7 @@
         <v>2</v>
       </c>
       <c r="C41" s="42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D41" s="42"/>
       <c r="E41" s="24"/>
@@ -8395,7 +8455,7 @@
         <v>2</v>
       </c>
       <c r="H41" s="4">
-        <v>6168</v>
+        <v>6939</v>
       </c>
       <c r="I41" s="42"/>
       <c r="J41" s="24"/>
@@ -8576,7 +8636,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I46" s="42"/>
       <c r="J46" s="24"/>
@@ -8610,10 +8670,10 @@
         <v>3</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H47" s="42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I47" s="42"/>
       <c r="J47" s="24"/>
@@ -8644,10 +8704,10 @@
       <c r="D48" s="42"/>
       <c r="E48" s="24"/>
       <c r="F48" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H48" s="42">
         <v>2</v>
@@ -8778,7 +8838,7 @@
         <v>3</v>
       </c>
       <c r="C53" s="4">
-        <v>7690</v>
+        <v>8170</v>
       </c>
       <c r="D53" s="42">
         <v>1</v>
@@ -8791,7 +8851,7 @@
         <v>3</v>
       </c>
       <c r="H53" s="42">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I53" s="42">
         <v>1</v>
@@ -8804,7 +8864,7 @@
         <v>3</v>
       </c>
       <c r="M53" s="4">
-        <v>3140</v>
+        <v>3420</v>
       </c>
       <c r="N53" s="42">
         <v>1</v>
@@ -8818,10 +8878,10 @@
         <v>2</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C54" s="4">
-        <v>5890</v>
+        <v>6530</v>
       </c>
       <c r="D54" s="42"/>
       <c r="E54" s="24"/>
@@ -8832,7 +8892,7 @@
         <v>0</v>
       </c>
       <c r="H54" s="42">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I54" s="42"/>
       <c r="J54" s="24"/>
@@ -8843,7 +8903,7 @@
         <v>0</v>
       </c>
       <c r="M54" s="4">
-        <v>2940</v>
+        <v>3180</v>
       </c>
       <c r="N54" s="42"/>
       <c r="O54" s="8"/>
@@ -8855,21 +8915,21 @@
         <v>3</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C55" s="4">
-        <v>5740</v>
+        <v>6030</v>
       </c>
       <c r="D55" s="42"/>
       <c r="E55" s="24"/>
       <c r="F55" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>1</v>
       </c>
       <c r="H55" s="42">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I55" s="42"/>
       <c r="J55" s="24"/>
@@ -8880,7 +8940,7 @@
         <v>1</v>
       </c>
       <c r="M55" s="4">
-        <v>2840</v>
+        <v>2980</v>
       </c>
       <c r="N55" s="42"/>
       <c r="O55" s="8"/>
@@ -8895,7 +8955,7 @@
         <v>2</v>
       </c>
       <c r="C56" s="4">
-        <v>5260</v>
+        <v>5750</v>
       </c>
       <c r="D56" s="42"/>
       <c r="E56" s="24"/>
@@ -8906,7 +8966,7 @@
         <v>2</v>
       </c>
       <c r="H56" s="42">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I56" s="42"/>
       <c r="J56" s="24"/>
@@ -8917,7 +8977,7 @@
         <v>2</v>
       </c>
       <c r="M56" s="4">
-        <v>2660</v>
+        <v>2800</v>
       </c>
       <c r="N56" s="42"/>
       <c r="O56" s="8"/>
@@ -8994,7 +9054,7 @@
         <v>3</v>
       </c>
       <c r="C59" s="42">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D59" s="42">
         <v>1</v>
@@ -9007,7 +9067,7 @@
         <v>3</v>
       </c>
       <c r="H59" s="4">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="I59" s="42">
         <v>1</v>
@@ -9020,7 +9080,7 @@
         <v>0</v>
       </c>
       <c r="M59" s="42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N59" s="42">
         <v>1</v>
@@ -9037,7 +9097,7 @@
         <v>0</v>
       </c>
       <c r="C60" s="42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D60" s="42"/>
       <c r="E60" s="24"/>
@@ -9048,12 +9108,12 @@
         <v>0</v>
       </c>
       <c r="H60" s="4">
-        <v>1100</v>
+        <v>1250</v>
       </c>
       <c r="I60" s="42"/>
       <c r="J60" s="24"/>
       <c r="K60" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>3</v>
@@ -9061,9 +9121,7 @@
       <c r="M60" s="42">
         <v>6</v>
       </c>
-      <c r="N60" s="42">
-        <v>1</v>
-      </c>
+      <c r="N60" s="42"/>
       <c r="O60" s="8"/>
       <c r="P60" s="8"/>
       <c r="Q60" s="8"/>
@@ -9073,10 +9131,10 @@
         <v>3</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C61" s="42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D61" s="42"/>
       <c r="E61" s="24"/>
@@ -9110,7 +9168,7 @@
         <v>4</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62" s="42">
         <v>7</v>
@@ -9118,13 +9176,13 @@
       <c r="D62" s="42"/>
       <c r="E62" s="24"/>
       <c r="F62" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H62" s="4">
-        <v>800</v>
+        <v>950</v>
       </c>
       <c r="I62" s="42"/>
       <c r="J62" s="24"/>
@@ -9135,7 +9193,7 @@
         <v>2</v>
       </c>
       <c r="M62" s="42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N62" s="42"/>
       <c r="O62" s="8"/>
@@ -9209,10 +9267,10 @@
         <v>1</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C65" s="4">
-        <v>1800</v>
+        <v>2100</v>
       </c>
       <c r="D65" s="42">
         <v>1</v>
@@ -9252,10 +9310,10 @@
         <v>2</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C66" s="4">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="D66" s="42"/>
       <c r="E66" s="24"/>
@@ -9329,7 +9387,7 @@
         <v>2</v>
       </c>
       <c r="C68" s="4">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="D68" s="42"/>
       <c r="E68" s="24"/>
@@ -9664,7 +9722,7 @@
         <v>2</v>
       </c>
       <c r="C79" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D79" s="42">
         <v>1</v>
@@ -9677,7 +9735,7 @@
         <v>2</v>
       </c>
       <c r="H79" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I79" s="42">
         <v>1</v>
@@ -9690,7 +9748,7 @@
         <v>3</v>
       </c>
       <c r="M79" s="4">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="N79" s="42">
         <v>1</v>
@@ -9701,26 +9759,24 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C80" s="4">
         <v>6</v>
       </c>
-      <c r="D80" s="42">
-        <v>1</v>
-      </c>
+      <c r="D80" s="42"/>
       <c r="E80" s="24"/>
       <c r="F80" s="5">
         <v>1</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H80" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I80" s="42">
         <v>1</v>
@@ -9742,13 +9798,13 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
+        <v>2</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>1</v>
-      </c>
       <c r="C81" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D81" s="42"/>
       <c r="E81" s="24"/>
@@ -9756,10 +9812,10 @@
         <v>1</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H81" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I81" s="42">
         <v>1</v>
@@ -9798,7 +9854,7 @@
         <v>0</v>
       </c>
       <c r="H82" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I82" s="42">
         <v>1</v>
@@ -9811,7 +9867,7 @@
         <v>0</v>
       </c>
       <c r="M82" s="4">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="N82" s="42"/>
       <c r="O82" s="8"/>
@@ -9888,7 +9944,7 @@
         <v>3</v>
       </c>
       <c r="C85" s="44">
-        <v>13.333333333333334</v>
+        <v>13</v>
       </c>
       <c r="D85" s="42">
         <v>1</v>
@@ -9901,7 +9957,7 @@
         <v>3</v>
       </c>
       <c r="H85" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I85" s="42">
         <v>1</v>
@@ -9914,7 +9970,7 @@
         <v>3</v>
       </c>
       <c r="M85" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N85" s="42">
         <v>1</v>
@@ -9931,7 +9987,7 @@
         <v>1</v>
       </c>
       <c r="C86" s="44">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D86" s="42"/>
       <c r="E86" s="24"/>
@@ -9942,7 +9998,7 @@
         <v>1</v>
       </c>
       <c r="H86" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I86" s="42"/>
       <c r="J86" s="8"/>
@@ -9968,7 +10024,7 @@
         <v>2</v>
       </c>
       <c r="C87" s="44">
-        <v>32.222222222222221</v>
+        <v>29</v>
       </c>
       <c r="D87" s="42"/>
       <c r="E87" s="24"/>
@@ -9979,7 +10035,7 @@
         <v>0</v>
       </c>
       <c r="H87" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I87" s="42"/>
       <c r="J87" s="8"/>
@@ -10005,7 +10061,7 @@
         <v>0</v>
       </c>
       <c r="C88" s="44">
-        <v>41.111111111111114</v>
+        <v>38</v>
       </c>
       <c r="D88" s="42"/>
       <c r="E88" s="24"/>
@@ -10016,7 +10072,7 @@
         <v>2</v>
       </c>
       <c r="H88" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I88" s="42"/>
       <c r="J88" s="8"/>
@@ -10178,16 +10234,16 @@
         <v>3</v>
       </c>
       <c r="M95" s="65">
-        <v>0.33333333333333331</v>
+        <v>0.4</v>
       </c>
       <c r="N95" s="70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O95" s="65">
-        <v>0.33333333333333331</v>
+        <v>0.25</v>
       </c>
       <c r="P95" s="65">
-        <v>0.1111111111111111</v>
+        <v>0.1</v>
       </c>
       <c r="Q95" s="63"/>
     </row>
@@ -10211,7 +10267,7 @@
         <v>1</v>
       </c>
       <c r="M96" s="55">
-        <v>0.33333333333333331</v>
+        <v>0.3</v>
       </c>
       <c r="N96" s="66">
         <v>3</v>
@@ -10220,7 +10276,7 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="P96" s="55">
-        <v>0.1111111111111111</v>
+        <v>9.9999999999999992E-2</v>
       </c>
       <c r="Q96" s="63"/>
     </row>
@@ -10273,7 +10329,7 @@
         <v>2</v>
       </c>
       <c r="M98" s="55">
-        <v>0.33333333333333331</v>
+        <v>0.3</v>
       </c>
       <c r="N98" s="66">
         <v>3</v>
@@ -10282,7 +10338,7 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="P98" s="55">
-        <v>0.1111111111111111</v>
+        <v>9.9999999999999992E-2</v>
       </c>
       <c r="Q98" s="63"/>
     </row>
@@ -10368,7 +10424,7 @@
         <v>1</v>
       </c>
       <c r="M101" s="55">
-        <v>0.33333333333333331</v>
+        <v>0.3</v>
       </c>
       <c r="N101" s="66">
         <v>3</v>
@@ -10377,7 +10433,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="P101" s="55">
-        <v>0.22222222222222221</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="Q101" s="63"/>
     </row>
@@ -10432,7 +10488,7 @@
         <v>2</v>
       </c>
       <c r="M103" s="55">
-        <v>0.33333333333333331</v>
+        <v>0.3</v>
       </c>
       <c r="N103" s="66">
         <v>3</v>
@@ -10441,7 +10497,7 @@
         <v>1</v>
       </c>
       <c r="P103" s="55">
-        <v>0.33333333333333331</v>
+        <v>0.3</v>
       </c>
       <c r="Q103" s="63"/>
     </row>
@@ -10527,16 +10583,16 @@
         <v>2</v>
       </c>
       <c r="M106" s="55">
-        <v>0.33333333333333331</v>
+        <v>0.4</v>
       </c>
       <c r="N106" s="66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O106" s="65">
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="P106" s="55">
-        <v>0.16666666666666666</v>
+        <v>0.26666666666666666</v>
       </c>
       <c r="Q106" s="63"/>
     </row>
@@ -10647,7 +10703,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K111" s="8"/>
       <c r="L111" s="8"/>
@@ -10665,7 +10721,7 @@
         <v>1</v>
       </c>
       <c r="C112" s="20">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L112" s="74" t="s">
         <v>59</v>
@@ -10675,7 +10731,7 @@
       </c>
       <c r="N112" s="75"/>
       <c r="O112" s="76">
-        <v>-5.555555555555558E-2</v>
+        <v>-6.6666666666666652E-2</v>
       </c>
       <c r="Q112" s="63"/>
     </row>
@@ -10698,7 +10754,7 @@
         <v>3</v>
       </c>
       <c r="C114" s="20">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="115" spans="1:34" x14ac:dyDescent="0.25">
@@ -10859,7 +10915,9 @@
       <c r="J123" s="5">
         <v>1</v>
       </c>
-      <c r="K123" s="5"/>
+      <c r="K123" s="5">
+        <v>-1</v>
+      </c>
       <c r="L123" s="5"/>
       <c r="M123" s="5"/>
       <c r="N123" s="5"/>
@@ -10915,7 +10973,9 @@
       <c r="J124" s="5">
         <v>-1</v>
       </c>
-      <c r="K124" s="5"/>
+      <c r="K124" s="5">
+        <v>1</v>
+      </c>
       <c r="L124" s="5"/>
       <c r="M124" s="5"/>
       <c r="N124" s="5"/>
@@ -10971,7 +11031,9 @@
       <c r="J125" s="5">
         <v>-1</v>
       </c>
-      <c r="K125" s="5"/>
+      <c r="K125" s="5">
+        <v>1</v>
+      </c>
       <c r="L125" s="5"/>
       <c r="M125" s="5"/>
       <c r="N125" s="5"/>
@@ -11027,7 +11089,9 @@
       <c r="J126" s="5">
         <v>1</v>
       </c>
-      <c r="K126" s="5"/>
+      <c r="K126" s="5">
+        <v>-1</v>
+      </c>
       <c r="L126" s="5"/>
       <c r="M126" s="5"/>
       <c r="N126" s="5"/>
@@ -11085,7 +11149,9 @@
       <c r="J131" s="59" t="s">
         <v>76</v>
       </c>
-      <c r="K131" s="59"/>
+      <c r="K131" s="59" t="s">
+        <v>77</v>
+      </c>
       <c r="L131" s="59"/>
       <c r="M131" s="59"/>
       <c r="N131" s="59"/>
@@ -11141,7 +11207,9 @@
       <c r="J132" s="5">
         <v>2</v>
       </c>
-      <c r="K132" s="5"/>
+      <c r="K132" s="5">
+        <v>2</v>
+      </c>
       <c r="L132" s="5"/>
       <c r="M132" s="5"/>
       <c r="N132" s="68"/>
@@ -11197,7 +11265,9 @@
       <c r="J133" s="5">
         <v>8</v>
       </c>
-      <c r="K133" s="5"/>
+      <c r="K133" s="5">
+        <v>8</v>
+      </c>
       <c r="L133" s="5"/>
       <c r="M133" s="5"/>
       <c r="N133" s="68"/>
@@ -11253,7 +11323,9 @@
       <c r="J134" s="5">
         <v>4</v>
       </c>
-      <c r="K134" s="5"/>
+      <c r="K134" s="5">
+        <v>4</v>
+      </c>
       <c r="L134" s="5"/>
       <c r="M134" s="5"/>
       <c r="N134" s="68"/>
@@ -11309,7 +11381,9 @@
       <c r="J135" s="5">
         <v>27</v>
       </c>
-      <c r="K135" s="5"/>
+      <c r="K135" s="5">
+        <v>27</v>
+      </c>
       <c r="L135" s="5"/>
       <c r="M135" s="5"/>
       <c r="N135" s="68"/>
@@ -11480,52 +11554,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A132:A139">
-    <cfRule type="containsText" dxfId="34" priority="1197" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="34" priority="1211" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A132)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A110:C118">
-    <cfRule type="containsText" dxfId="33" priority="1156" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="33" priority="1170" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A110)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:D20">
-    <cfRule type="containsText" dxfId="32" priority="80" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="32" priority="94" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22:D27">
-    <cfRule type="containsText" dxfId="31" priority="45" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="31" priority="59" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:D34">
-    <cfRule type="containsText" dxfId="30" priority="62" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="30" priority="76" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38:D42">
-    <cfRule type="containsText" dxfId="29" priority="59" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="29" priority="12" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44:D48">
-    <cfRule type="containsText" dxfId="28" priority="12" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="28" priority="9" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A44)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:D56">
-    <cfRule type="containsText" dxfId="27" priority="411" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="27" priority="425" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A52)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:D62">
-    <cfRule type="containsText" dxfId="26" priority="9" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="26" priority="23" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A58)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64:D68">
-    <cfRule type="containsText" dxfId="25" priority="48" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="25" priority="62" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A64)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11540,47 +11614,47 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A84:D88">
-    <cfRule type="containsText" dxfId="22" priority="38" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="22" priority="52" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A84)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:I11">
-    <cfRule type="containsText" dxfId="21" priority="229" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="21" priority="243" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:I20">
-    <cfRule type="containsText" dxfId="20" priority="65" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="20" priority="79" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F22:I26">
-    <cfRule type="containsText" dxfId="19" priority="16" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="19" priority="13" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:I34">
-    <cfRule type="containsText" dxfId="18" priority="61" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="18" priority="75" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F38:I42">
-    <cfRule type="containsText" dxfId="17" priority="15" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="17" priority="29" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F44:I48">
-    <cfRule type="containsText" dxfId="16" priority="11" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="16" priority="25" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F44)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52:I56">
-    <cfRule type="containsText" dxfId="15" priority="10" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="15" priority="24" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F52)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F58:I62">
-    <cfRule type="containsText" dxfId="14" priority="23" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="14" priority="8" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F58)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11595,7 +11669,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F78:I82">
-    <cfRule type="containsText" dxfId="11" priority="40" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="11" priority="54" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F78)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11605,37 +11679,37 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16:N20">
-    <cfRule type="containsText" dxfId="9" priority="46" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="9" priority="60" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K22:N26">
-    <cfRule type="containsText" dxfId="8" priority="350" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="8" priority="364" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K30:N34">
-    <cfRule type="containsText" dxfId="7" priority="60" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="7" priority="74" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K38:N42">
-    <cfRule type="containsText" dxfId="6" priority="13" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="6" priority="10" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K44:N48">
-    <cfRule type="containsText" dxfId="5" priority="51" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="5" priority="65" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K44)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K52:N56">
-    <cfRule type="containsText" dxfId="4" priority="399" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="4" priority="413" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K52)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K58:N62">
-    <cfRule type="containsText" dxfId="3" priority="8" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="3" priority="22" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K58)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11645,12 +11719,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K78:N82">
-    <cfRule type="containsText" dxfId="1" priority="39" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="1" priority="53" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K78)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K84:N88">
-    <cfRule type="containsText" dxfId="0" priority="27" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="0" priority="41" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K84)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Statistik_Jassen.xlsx
+++ b/Statistik_Jassen.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meine Ablage\Jassen Wädi\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1319A1A4-30F7-415E-A8DD-8292564CCCC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2EC3E86F-781C-4E7A-85BD-18FC3C70E790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A8FCF452-0EF5-42A7-A382-1701488C7232}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="79">
   <si>
     <t>Fuchs</t>
   </si>
@@ -276,6 +276,9 @@
   </si>
   <si>
     <t>17.08.</t>
+  </si>
+  <si>
+    <t>04.09.</t>
   </si>
 </sst>
 </file>
@@ -1514,7 +1517,7 @@
             <c:strRef>
               <c:f>'Gesamtranking Print'!$B$131:$AH$131</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>21.03.</c:v>
                 </c:pt>
@@ -1544,6 +1547,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>17.08.</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>04.09.</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1582,6 +1588,9 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
@@ -1686,7 +1695,7 @@
             <c:strRef>
               <c:f>'Gesamtranking Print'!$B$131:$AH$131</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>21.03.</c:v>
                 </c:pt>
@@ -1716,6 +1725,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>17.08.</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>04.09.</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1755,6 +1767,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1858,7 +1873,7 @@
             <c:strRef>
               <c:f>'Gesamtranking Print'!$B$131:$AH$131</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>21.03.</c:v>
                 </c:pt>
@@ -1888,6 +1903,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>17.08.</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>04.09.</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1927,6 +1945,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2030,7 +2051,7 @@
             <c:strRef>
               <c:f>'Gesamtranking Print'!$B$131:$AH$131</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>21.03.</c:v>
                 </c:pt>
@@ -2060,6 +2081,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>17.08.</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>04.09.</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2099,6 +2123,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>22</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2268,7 +2295,7 @@
                       </c:ext>
                     </c:extLst>
                     <c:strCache>
-                      <c:ptCount val="10"/>
+                      <c:ptCount val="11"/>
                       <c:pt idx="0">
                         <c:v>21.03.</c:v>
                       </c:pt>
@@ -2298,6 +2325,9 @@
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>17.08.</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>04.09.</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -2469,7 +2499,7 @@
                       </c:ext>
                     </c:extLst>
                     <c:strCache>
-                      <c:ptCount val="10"/>
+                      <c:ptCount val="11"/>
                       <c:pt idx="0">
                         <c:v>21.03.</c:v>
                       </c:pt>
@@ -2499,6 +2529,9 @@
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>17.08.</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>04.09.</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -2677,7 +2710,7 @@
                       </c:ext>
                     </c:extLst>
                     <c:strCache>
-                      <c:ptCount val="10"/>
+                      <c:ptCount val="11"/>
                       <c:pt idx="0">
                         <c:v>21.03.</c:v>
                       </c:pt>
@@ -2707,6 +2740,9 @@
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>17.08.</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>04.09.</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -3117,6 +3153,9 @@
                 <c:pt idx="9">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3293,6 +3332,9 @@
                   <c:v>-1</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -3635,6 +3677,9 @@
                 <c:pt idx="9">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3811,6 +3856,9 @@
                   <c:v>-1</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -4151,6 +4199,9 @@
                 <c:pt idx="9">
                   <c:v>-1</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>-1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4327,6 +4378,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>-1</c:v>
                 </c:pt>
               </c:numCache>
@@ -4660,6 +4714,9 @@
                 <c:pt idx="9">
                   <c:v>-1</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>-1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4829,6 +4886,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>-1</c:v>
                 </c:pt>
               </c:numCache>
@@ -7422,10 +7482,10 @@
         <v>3</v>
       </c>
       <c r="H8" s="42">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I8" s="69">
-        <v>0.28169014084507044</v>
+        <v>0.28205128205128205</v>
       </c>
       <c r="J8" s="9"/>
       <c r="K8" s="8"/>
@@ -7449,10 +7509,10 @@
         <v>1</v>
       </c>
       <c r="H9" s="42">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I9" s="69">
-        <v>0.31506849315068491</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="J9" s="9"/>
       <c r="K9" s="8"/>
@@ -7476,10 +7536,10 @@
         <v>2</v>
       </c>
       <c r="H10" s="42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10" s="69">
-        <v>0.32876712328767121</v>
+        <v>0.30864197530864196</v>
       </c>
       <c r="J10" s="9"/>
       <c r="K10" s="8"/>
@@ -7503,10 +7563,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I11" s="73">
-        <v>0.29113924050632911</v>
+        <v>0.28735632183908044</v>
       </c>
       <c r="J11" s="9"/>
       <c r="K11" s="8"/>
@@ -7646,7 +7706,7 @@
         <v>3</v>
       </c>
       <c r="C17" s="42">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D17" s="42">
         <v>1</v>
@@ -7659,7 +7719,7 @@
         <v>2</v>
       </c>
       <c r="H17" s="42">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I17" s="42">
         <v>1</v>
@@ -7672,7 +7732,7 @@
         <v>3</v>
       </c>
       <c r="M17" s="15">
-        <v>6.6</v>
+        <v>6.4545454545454541</v>
       </c>
       <c r="N17" s="42">
         <v>1</v>
@@ -7689,7 +7749,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="42">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D18" s="42"/>
       <c r="E18" s="24"/>
@@ -7697,10 +7757,10 @@
         <v>2</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18" s="42">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I18" s="42"/>
       <c r="J18" s="24"/>
@@ -7711,7 +7771,7 @@
         <v>1</v>
       </c>
       <c r="M18" s="15">
-        <v>6.1</v>
+        <v>6.3636363636363633</v>
       </c>
       <c r="N18" s="42"/>
       <c r="O18" s="9"/>
@@ -7726,7 +7786,7 @@
         <v>2</v>
       </c>
       <c r="C19" s="42">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="D19" s="42"/>
       <c r="E19" s="24"/>
@@ -7734,10 +7794,10 @@
         <v>3</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H19" s="42">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I19" s="42"/>
       <c r="J19" s="24"/>
@@ -7748,7 +7808,7 @@
         <v>2</v>
       </c>
       <c r="M19" s="15">
-        <v>5</v>
+        <v>5.3636363636363633</v>
       </c>
       <c r="N19" s="42"/>
       <c r="O19" s="9"/>
@@ -7764,7 +7824,7 @@
         <v>0</v>
       </c>
       <c r="C20" s="42">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D20" s="42"/>
       <c r="E20" s="24"/>
@@ -7786,7 +7846,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="15">
-        <v>4.0999999999999996</v>
+        <v>4.1818181818181817</v>
       </c>
       <c r="N20" s="42"/>
       <c r="O20" s="9"/>
@@ -7863,7 +7923,7 @@
         <v>3</v>
       </c>
       <c r="C23" s="15">
-        <v>2.3571428571428572</v>
+        <v>2.2903225806451615</v>
       </c>
       <c r="D23" s="42">
         <v>1</v>
@@ -7873,10 +7933,10 @@
         <v>1</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H23" s="42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" s="42">
         <v>1</v>
@@ -7900,22 +7960,20 @@
         <v>1</v>
       </c>
       <c r="C24" s="15">
-        <v>2.1785714285714284</v>
+        <v>2.2580645161290325</v>
       </c>
       <c r="D24" s="42"/>
       <c r="E24" s="24"/>
       <c r="F24" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H24" s="42">
         <v>1</v>
       </c>
-      <c r="I24" s="42">
-        <v>1</v>
-      </c>
+      <c r="I24" s="42"/>
       <c r="J24" s="8"/>
       <c r="K24" s="5">
         <v>2</v>
@@ -7935,18 +7993,18 @@
         <v>2</v>
       </c>
       <c r="C25" s="15">
-        <v>1.7857142857142858</v>
+        <v>1.903225806451613</v>
       </c>
       <c r="D25" s="42"/>
       <c r="E25" s="24"/>
       <c r="F25" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" s="42"/>
       <c r="J25" s="8"/>
@@ -7968,12 +8026,12 @@
         <v>0</v>
       </c>
       <c r="C26" s="15">
-        <v>1.4642857142857142</v>
+        <v>1.4838709677419355</v>
       </c>
       <c r="D26" s="42"/>
       <c r="E26" s="24"/>
       <c r="F26" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>2</v>
@@ -8100,10 +8158,10 @@
         <v>1</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C31" s="4">
-        <v>84529</v>
+        <v>92606</v>
       </c>
       <c r="D31" s="42">
         <v>1</v>
@@ -8113,10 +8171,10 @@
         <v>1</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31" s="4">
-        <v>8452.9</v>
+        <v>8418.7272727272721</v>
       </c>
       <c r="I31" s="42">
         <v>1</v>
@@ -8126,10 +8184,10 @@
         <v>1</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M31" s="4">
-        <v>3018.8928571428573</v>
+        <v>2987.2903225806454</v>
       </c>
       <c r="N31" s="42">
         <v>1</v>
@@ -8143,10 +8201,10 @@
         <v>2</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32" s="4">
-        <v>84263</v>
+        <v>92417</v>
       </c>
       <c r="D32" s="42"/>
       <c r="E32" s="24"/>
@@ -8154,10 +8212,10 @@
         <v>2</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H32" s="4">
-        <v>8426.2999999999993</v>
+        <v>8401.545454545454</v>
       </c>
       <c r="I32" s="42"/>
       <c r="J32" s="24"/>
@@ -8165,10 +8223,10 @@
         <v>2</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M32" s="4">
-        <v>3009.3928571428573</v>
+        <v>2981.1935483870966</v>
       </c>
       <c r="N32" s="42"/>
       <c r="O32" s="8"/>
@@ -8183,7 +8241,7 @@
         <v>2</v>
       </c>
       <c r="C33" s="4">
-        <v>80721</v>
+        <v>88609</v>
       </c>
       <c r="D33" s="42"/>
       <c r="E33" s="24"/>
@@ -8194,7 +8252,7 @@
         <v>2</v>
       </c>
       <c r="H33" s="4">
-        <v>8072.1</v>
+        <v>8055.363636363636</v>
       </c>
       <c r="I33" s="42"/>
       <c r="J33" s="24"/>
@@ -8205,7 +8263,7 @@
         <v>2</v>
       </c>
       <c r="M33" s="4">
-        <v>2882.8928571428573</v>
+        <v>2858.3548387096776</v>
       </c>
       <c r="N33" s="42"/>
       <c r="O33" s="8"/>
@@ -8221,7 +8279,7 @@
         <v>0</v>
       </c>
       <c r="C34" s="4">
-        <v>79151</v>
+        <v>87494</v>
       </c>
       <c r="D34" s="42"/>
       <c r="E34" s="24"/>
@@ -8232,7 +8290,7 @@
         <v>0</v>
       </c>
       <c r="H34" s="4">
-        <v>7915.1</v>
+        <v>7954</v>
       </c>
       <c r="I34" s="42"/>
       <c r="J34" s="24"/>
@@ -8243,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="M34" s="4">
-        <v>2826.8214285714284</v>
+        <v>2822.3870967741937</v>
       </c>
       <c r="N34" s="42"/>
       <c r="O34" s="8"/>
@@ -8360,7 +8418,7 @@
         <v>1</v>
       </c>
       <c r="C39" s="42">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D39" s="42">
         <v>1</v>
@@ -8373,7 +8431,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="4">
-        <v>11565</v>
+        <v>13364</v>
       </c>
       <c r="I39" s="42">
         <v>1</v>
@@ -8403,7 +8461,7 @@
         <v>3</v>
       </c>
       <c r="C40" s="42">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D40" s="42">
         <v>1</v>
@@ -8416,7 +8474,7 @@
         <v>3</v>
       </c>
       <c r="H40" s="4">
-        <v>10794</v>
+        <v>12850</v>
       </c>
       <c r="I40" s="42"/>
       <c r="J40" s="24"/>
@@ -8444,7 +8502,7 @@
         <v>2</v>
       </c>
       <c r="C41" s="42">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D41" s="42"/>
       <c r="E41" s="24"/>
@@ -8455,7 +8513,7 @@
         <v>2</v>
       </c>
       <c r="H41" s="4">
-        <v>6939</v>
+        <v>8738</v>
       </c>
       <c r="I41" s="42"/>
       <c r="J41" s="24"/>
@@ -8481,7 +8539,7 @@
         <v>0</v>
       </c>
       <c r="C42" s="42">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D42" s="42"/>
       <c r="E42" s="24"/>
@@ -8492,7 +8550,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="4">
-        <v>4112</v>
+        <v>6168</v>
       </c>
       <c r="I42" s="42"/>
       <c r="J42" s="24"/>
@@ -8606,7 +8664,7 @@
         <v>1</v>
       </c>
       <c r="M45" s="42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N45" s="42">
         <v>1</v>
@@ -8636,7 +8694,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I46" s="42"/>
       <c r="J46" s="24"/>
@@ -8644,10 +8702,10 @@
         <v>2</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M46" s="42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N46" s="42"/>
       <c r="O46" s="8"/>
@@ -8673,18 +8731,18 @@
         <v>2</v>
       </c>
       <c r="H47" s="42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I47" s="42"/>
       <c r="J47" s="24"/>
       <c r="K47" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M47" s="42">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N47" s="42"/>
       <c r="O47" s="8"/>
@@ -8721,7 +8779,7 @@
         <v>3</v>
       </c>
       <c r="M48" s="42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N48" s="42"/>
       <c r="O48" s="8"/>
@@ -8838,7 +8896,7 @@
         <v>3</v>
       </c>
       <c r="C53" s="4">
-        <v>8170</v>
+        <v>8890</v>
       </c>
       <c r="D53" s="42">
         <v>1</v>
@@ -8851,7 +8909,7 @@
         <v>3</v>
       </c>
       <c r="H53" s="42">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I53" s="42">
         <v>1</v>
@@ -8864,7 +8922,7 @@
         <v>3</v>
       </c>
       <c r="M53" s="4">
-        <v>3420</v>
+        <v>3540</v>
       </c>
       <c r="N53" s="42">
         <v>1</v>
@@ -8881,7 +8939,7 @@
         <v>0</v>
       </c>
       <c r="C54" s="4">
-        <v>6530</v>
+        <v>7100</v>
       </c>
       <c r="D54" s="42"/>
       <c r="E54" s="24"/>
@@ -8892,7 +8950,7 @@
         <v>0</v>
       </c>
       <c r="H54" s="42">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="I54" s="42"/>
       <c r="J54" s="24"/>
@@ -8903,7 +8961,7 @@
         <v>0</v>
       </c>
       <c r="M54" s="4">
-        <v>3180</v>
+        <v>3500</v>
       </c>
       <c r="N54" s="42"/>
       <c r="O54" s="8"/>
@@ -8918,7 +8976,7 @@
         <v>1</v>
       </c>
       <c r="C55" s="4">
-        <v>6030</v>
+        <v>6530</v>
       </c>
       <c r="D55" s="42"/>
       <c r="E55" s="24"/>
@@ -8929,7 +8987,7 @@
         <v>1</v>
       </c>
       <c r="H55" s="42">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I55" s="42"/>
       <c r="J55" s="24"/>
@@ -8940,7 +8998,7 @@
         <v>1</v>
       </c>
       <c r="M55" s="4">
-        <v>2980</v>
+        <v>3180</v>
       </c>
       <c r="N55" s="42"/>
       <c r="O55" s="8"/>
@@ -8955,7 +9013,7 @@
         <v>2</v>
       </c>
       <c r="C56" s="4">
-        <v>5750</v>
+        <v>5810</v>
       </c>
       <c r="D56" s="42"/>
       <c r="E56" s="24"/>
@@ -8966,7 +9024,7 @@
         <v>2</v>
       </c>
       <c r="H56" s="42">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I56" s="42"/>
       <c r="J56" s="24"/>
@@ -8977,7 +9035,7 @@
         <v>2</v>
       </c>
       <c r="M56" s="4">
-        <v>2800</v>
+        <v>2860</v>
       </c>
       <c r="N56" s="42"/>
       <c r="O56" s="8"/>
@@ -9054,7 +9112,7 @@
         <v>3</v>
       </c>
       <c r="C59" s="42">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D59" s="42">
         <v>1</v>
@@ -9067,7 +9125,7 @@
         <v>3</v>
       </c>
       <c r="H59" s="4">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="I59" s="42">
         <v>1</v>
@@ -9097,7 +9155,7 @@
         <v>0</v>
       </c>
       <c r="C60" s="42">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D60" s="42"/>
       <c r="E60" s="24"/>
@@ -9108,20 +9166,22 @@
         <v>0</v>
       </c>
       <c r="H60" s="4">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="I60" s="42"/>
       <c r="J60" s="24"/>
       <c r="K60" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M60" s="42">
-        <v>6</v>
-      </c>
-      <c r="N60" s="42"/>
+        <v>7</v>
+      </c>
+      <c r="N60" s="42">
+        <v>1</v>
+      </c>
       <c r="O60" s="8"/>
       <c r="P60" s="8"/>
       <c r="Q60" s="8"/>
@@ -9156,7 +9216,7 @@
         <v>1</v>
       </c>
       <c r="M61" s="42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N61" s="42"/>
       <c r="O61" s="8"/>
@@ -9298,9 +9358,7 @@
       <c r="M65" s="4">
         <v>1350</v>
       </c>
-      <c r="N65" s="42">
-        <v>1</v>
-      </c>
+      <c r="N65" s="42"/>
       <c r="O65" s="8"/>
       <c r="P65" s="8"/>
       <c r="Q65" s="8"/>
@@ -9313,7 +9371,7 @@
         <v>3</v>
       </c>
       <c r="C66" s="4">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="D66" s="42"/>
       <c r="E66" s="24"/>
@@ -9350,7 +9408,7 @@
         <v>1</v>
       </c>
       <c r="C67" s="4">
-        <v>1300</v>
+        <v>1600</v>
       </c>
       <c r="D67" s="42"/>
       <c r="E67" s="24"/>
@@ -9722,7 +9780,7 @@
         <v>2</v>
       </c>
       <c r="C79" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D79" s="42">
         <v>1</v>
@@ -9732,14 +9790,12 @@
         <v>1</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H79" s="4">
-        <v>10</v>
-      </c>
-      <c r="I79" s="42">
-        <v>1</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="I79" s="42"/>
       <c r="J79" s="24"/>
       <c r="K79" s="5">
         <v>1</v>
@@ -9748,7 +9804,7 @@
         <v>3</v>
       </c>
       <c r="M79" s="4">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="N79" s="42">
         <v>1</v>
@@ -9765,7 +9821,7 @@
         <v>1</v>
       </c>
       <c r="C80" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D80" s="42"/>
       <c r="E80" s="24"/>
@@ -9773,14 +9829,12 @@
         <v>1</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H80" s="4">
-        <v>10</v>
-      </c>
-      <c r="I80" s="42">
-        <v>1</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="I80" s="42"/>
       <c r="J80" s="24"/>
       <c r="K80" s="5">
         <v>2</v>
@@ -9798,7 +9852,7 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>3</v>
@@ -9812,14 +9866,12 @@
         <v>1</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H81" s="4">
-        <v>10</v>
-      </c>
-      <c r="I81" s="42">
-        <v>1</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="I81" s="42"/>
       <c r="J81" s="24"/>
       <c r="K81" s="5">
         <v>3</v>
@@ -9851,14 +9903,12 @@
         <v>1</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H82" s="4">
-        <v>10</v>
-      </c>
-      <c r="I82" s="42">
-        <v>1</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="I82" s="42"/>
       <c r="J82" s="24"/>
       <c r="K82" s="5">
         <v>4</v>
@@ -9867,7 +9917,7 @@
         <v>0</v>
       </c>
       <c r="M82" s="4">
-        <v>380</v>
+        <v>420</v>
       </c>
       <c r="N82" s="42"/>
       <c r="O82" s="8"/>
@@ -9944,7 +9994,7 @@
         <v>3</v>
       </c>
       <c r="C85" s="44">
-        <v>13</v>
+        <v>15.454545454545455</v>
       </c>
       <c r="D85" s="42">
         <v>1</v>
@@ -9957,7 +10007,7 @@
         <v>3</v>
       </c>
       <c r="H85" s="4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I85" s="42">
         <v>1</v>
@@ -9970,7 +10020,7 @@
         <v>3</v>
       </c>
       <c r="M85" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N85" s="42">
         <v>1</v>
@@ -9987,7 +10037,7 @@
         <v>1</v>
       </c>
       <c r="C86" s="44">
-        <v>18</v>
+        <v>16.363636363636363</v>
       </c>
       <c r="D86" s="42"/>
       <c r="E86" s="24"/>
@@ -9998,7 +10048,7 @@
         <v>1</v>
       </c>
       <c r="H86" s="4">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I86" s="42"/>
       <c r="J86" s="8"/>
@@ -10009,7 +10059,7 @@
         <v>1</v>
       </c>
       <c r="M86" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N86" s="42"/>
       <c r="O86" s="8"/>
@@ -10024,7 +10074,7 @@
         <v>2</v>
       </c>
       <c r="C87" s="44">
-        <v>29</v>
+        <v>26.363636363636363</v>
       </c>
       <c r="D87" s="42"/>
       <c r="E87" s="24"/>
@@ -10032,10 +10082,10 @@
         <v>3</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H87" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I87" s="42"/>
       <c r="J87" s="8"/>
@@ -10046,7 +10096,7 @@
         <v>0</v>
       </c>
       <c r="M87" s="4">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N87" s="42"/>
       <c r="O87" s="8"/>
@@ -10061,18 +10111,18 @@
         <v>0</v>
       </c>
       <c r="C88" s="44">
-        <v>38</v>
+        <v>38.18181818181818</v>
       </c>
       <c r="D88" s="42"/>
       <c r="E88" s="24"/>
       <c r="F88" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H88" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I88" s="42"/>
       <c r="J88" s="8"/>
@@ -10083,7 +10133,7 @@
         <v>2</v>
       </c>
       <c r="M88" s="4">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="N88" s="42"/>
       <c r="O88" s="8"/>
@@ -10234,16 +10284,16 @@
         <v>3</v>
       </c>
       <c r="M95" s="65">
-        <v>0.4</v>
+        <v>0.45454545454545453</v>
       </c>
       <c r="N95" s="70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O95" s="65">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="P95" s="65">
-        <v>0.1</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="Q95" s="63"/>
     </row>
@@ -10267,7 +10317,7 @@
         <v>1</v>
       </c>
       <c r="M96" s="55">
-        <v>0.3</v>
+        <v>0.27272727272727271</v>
       </c>
       <c r="N96" s="66">
         <v>3</v>
@@ -10276,7 +10326,7 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="P96" s="55">
-        <v>9.9999999999999992E-2</v>
+        <v>9.0909090909090898E-2</v>
       </c>
       <c r="Q96" s="63"/>
     </row>
@@ -10329,7 +10379,7 @@
         <v>2</v>
       </c>
       <c r="M98" s="55">
-        <v>0.3</v>
+        <v>0.27272727272727271</v>
       </c>
       <c r="N98" s="66">
         <v>3</v>
@@ -10338,7 +10388,7 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="P98" s="55">
-        <v>9.9999999999999992E-2</v>
+        <v>9.0909090909090898E-2</v>
       </c>
       <c r="Q98" s="63"/>
     </row>
@@ -10424,7 +10474,7 @@
         <v>1</v>
       </c>
       <c r="M101" s="55">
-        <v>0.3</v>
+        <v>0.27272727272727271</v>
       </c>
       <c r="N101" s="66">
         <v>3</v>
@@ -10433,7 +10483,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="P101" s="55">
-        <v>0.19999999999999998</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="Q101" s="63"/>
     </row>
@@ -10488,7 +10538,7 @@
         <v>2</v>
       </c>
       <c r="M103" s="55">
-        <v>0.3</v>
+        <v>0.27272727272727271</v>
       </c>
       <c r="N103" s="66">
         <v>3</v>
@@ -10497,7 +10547,7 @@
         <v>1</v>
       </c>
       <c r="P103" s="55">
-        <v>0.3</v>
+        <v>0.27272727272727271</v>
       </c>
       <c r="Q103" s="63"/>
     </row>
@@ -10583,16 +10633,16 @@
         <v>2</v>
       </c>
       <c r="M106" s="55">
-        <v>0.4</v>
+        <v>0.45454545454545453</v>
       </c>
       <c r="N106" s="66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O106" s="65">
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="P106" s="55">
-        <v>0.26666666666666666</v>
+        <v>0.34090909090909088</v>
       </c>
       <c r="Q106" s="63"/>
     </row>
@@ -10703,7 +10753,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K111" s="8"/>
       <c r="L111" s="8"/>
@@ -10721,7 +10771,7 @@
         <v>1</v>
       </c>
       <c r="C112" s="20">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L112" s="74" t="s">
         <v>59</v>
@@ -10731,7 +10781,7 @@
       </c>
       <c r="N112" s="75"/>
       <c r="O112" s="76">
-        <v>-6.6666666666666652E-2</v>
+        <v>-6.8181818181818121E-2</v>
       </c>
       <c r="Q112" s="63"/>
     </row>
@@ -10743,7 +10793,7 @@
         <v>2</v>
       </c>
       <c r="C113" s="20">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114" spans="1:34" x14ac:dyDescent="0.25">
@@ -10754,7 +10804,7 @@
         <v>3</v>
       </c>
       <c r="C114" s="20">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="115" spans="1:34" x14ac:dyDescent="0.25">
@@ -10918,7 +10968,9 @@
       <c r="K123" s="5">
         <v>-1</v>
       </c>
-      <c r="L123" s="5"/>
+      <c r="L123" s="5">
+        <v>-1</v>
+      </c>
       <c r="M123" s="5"/>
       <c r="N123" s="5"/>
       <c r="O123" s="5"/>
@@ -10976,7 +11028,9 @@
       <c r="K124" s="5">
         <v>1</v>
       </c>
-      <c r="L124" s="5"/>
+      <c r="L124" s="5">
+        <v>1</v>
+      </c>
       <c r="M124" s="5"/>
       <c r="N124" s="5"/>
       <c r="O124" s="5"/>
@@ -11034,7 +11088,9 @@
       <c r="K125" s="5">
         <v>1</v>
       </c>
-      <c r="L125" s="5"/>
+      <c r="L125" s="5">
+        <v>1</v>
+      </c>
       <c r="M125" s="5"/>
       <c r="N125" s="5"/>
       <c r="O125" s="5"/>
@@ -11092,7 +11148,9 @@
       <c r="K126" s="5">
         <v>-1</v>
       </c>
-      <c r="L126" s="5"/>
+      <c r="L126" s="5">
+        <v>-1</v>
+      </c>
       <c r="M126" s="5"/>
       <c r="N126" s="5"/>
       <c r="O126" s="5"/>
@@ -11152,7 +11210,9 @@
       <c r="K131" s="59" t="s">
         <v>77</v>
       </c>
-      <c r="L131" s="59"/>
+      <c r="L131" s="59" t="s">
+        <v>78</v>
+      </c>
       <c r="M131" s="59"/>
       <c r="N131" s="59"/>
       <c r="O131" s="59"/>
@@ -11210,7 +11270,9 @@
       <c r="K132" s="5">
         <v>2</v>
       </c>
-      <c r="L132" s="5"/>
+      <c r="L132" s="5">
+        <v>2</v>
+      </c>
       <c r="M132" s="5"/>
       <c r="N132" s="68"/>
       <c r="O132" s="5"/>
@@ -11268,7 +11330,9 @@
       <c r="K133" s="5">
         <v>8</v>
       </c>
-      <c r="L133" s="5"/>
+      <c r="L133" s="5">
+        <v>7</v>
+      </c>
       <c r="M133" s="5"/>
       <c r="N133" s="68"/>
       <c r="O133" s="5"/>
@@ -11326,7 +11390,9 @@
       <c r="K134" s="5">
         <v>4</v>
       </c>
-      <c r="L134" s="5"/>
+      <c r="L134" s="5">
+        <v>3</v>
+      </c>
       <c r="M134" s="5"/>
       <c r="N134" s="68"/>
       <c r="O134" s="5"/>
@@ -11384,7 +11450,9 @@
       <c r="K135" s="5">
         <v>27</v>
       </c>
-      <c r="L135" s="5"/>
+      <c r="L135" s="5">
+        <v>22</v>
+      </c>
       <c r="M135" s="5"/>
       <c r="N135" s="68"/>
       <c r="O135" s="5"/>
@@ -11554,52 +11622,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A132:A139">
-    <cfRule type="containsText" dxfId="34" priority="1211" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="34" priority="1226" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A132)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A110:C118">
-    <cfRule type="containsText" dxfId="33" priority="1170" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="33" priority="1185" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A110)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:D20">
-    <cfRule type="containsText" dxfId="32" priority="94" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="32" priority="109" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22:D27">
-    <cfRule type="containsText" dxfId="31" priority="59" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="31" priority="74" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:D34">
-    <cfRule type="containsText" dxfId="30" priority="76" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="30" priority="91" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38:D42">
-    <cfRule type="containsText" dxfId="29" priority="12" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="29" priority="14" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44:D48">
-    <cfRule type="containsText" dxfId="28" priority="9" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="28" priority="11" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A44)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:D56">
-    <cfRule type="containsText" dxfId="27" priority="425" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="27" priority="440" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A52)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:D62">
-    <cfRule type="containsText" dxfId="26" priority="23" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="26" priority="38" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A58)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64:D68">
-    <cfRule type="containsText" dxfId="25" priority="62" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="25" priority="77" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A64)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11609,52 +11677,52 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A78:D82">
-    <cfRule type="containsText" dxfId="23" priority="2" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="23" priority="17" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A78)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A84:D88">
-    <cfRule type="containsText" dxfId="22" priority="52" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="22" priority="67" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A84)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:I11">
-    <cfRule type="containsText" dxfId="21" priority="243" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="21" priority="258" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:I20">
-    <cfRule type="containsText" dxfId="20" priority="79" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="20" priority="94" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F22:I26">
-    <cfRule type="containsText" dxfId="19" priority="13" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="19" priority="15" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:I34">
-    <cfRule type="containsText" dxfId="18" priority="75" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="18" priority="90" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F38:I42">
-    <cfRule type="containsText" dxfId="17" priority="29" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="17" priority="44" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F44:I48">
-    <cfRule type="containsText" dxfId="16" priority="25" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="16" priority="40" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F44)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52:I56">
-    <cfRule type="containsText" dxfId="15" priority="24" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="15" priority="39" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F52)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F58:I62">
-    <cfRule type="containsText" dxfId="14" priority="8" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="14" priority="9" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F58)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11664,52 +11732,52 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F70:I74">
-    <cfRule type="containsText" dxfId="12" priority="3" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F70)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F78:I82">
-    <cfRule type="containsText" dxfId="11" priority="54" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="11" priority="1" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F78)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F84:I88">
-    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="10" priority="16" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F84)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16:N20">
-    <cfRule type="containsText" dxfId="9" priority="60" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="9" priority="75" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K22:N26">
-    <cfRule type="containsText" dxfId="8" priority="364" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="8" priority="379" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K30:N34">
-    <cfRule type="containsText" dxfId="7" priority="74" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="7" priority="89" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K38:N42">
-    <cfRule type="containsText" dxfId="6" priority="10" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="6" priority="12" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K44:N48">
-    <cfRule type="containsText" dxfId="5" priority="65" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="5" priority="10" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K44)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K52:N56">
-    <cfRule type="containsText" dxfId="4" priority="413" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="4" priority="428" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K52)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K58:N62">
-    <cfRule type="containsText" dxfId="3" priority="22" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="3" priority="8" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K58)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11719,12 +11787,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K78:N82">
-    <cfRule type="containsText" dxfId="1" priority="53" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="1" priority="68" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K78)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K84:N88">
-    <cfRule type="containsText" dxfId="0" priority="41" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="0" priority="56" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K84)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Statistik_Jassen.xlsx
+++ b/Statistik_Jassen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meine Ablage\Jassen Wädi\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2EC3E86F-781C-4E7A-85BD-18FC3C70E790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1374AA8D-4044-4087-9902-134412426502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A8FCF452-0EF5-42A7-A382-1701488C7232}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="80">
   <si>
     <t>Fuchs</t>
   </si>
@@ -279,6 +279,9 @@
   </si>
   <si>
     <t>04.09.</t>
+  </si>
+  <si>
+    <t>07.09.</t>
   </si>
 </sst>
 </file>
@@ -1517,7 +1520,7 @@
             <c:strRef>
               <c:f>'Gesamtranking Print'!$B$131:$AH$131</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>21.03.</c:v>
                 </c:pt>
@@ -1550,6 +1553,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>04.09.</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>07.09.</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1592,6 +1598,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1695,7 +1704,7 @@
             <c:strRef>
               <c:f>'Gesamtranking Print'!$B$131:$AH$131</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>21.03.</c:v>
                 </c:pt>
@@ -1728,6 +1737,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>04.09.</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>07.09.</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1770,6 +1782,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1873,7 +1888,7 @@
             <c:strRef>
               <c:f>'Gesamtranking Print'!$B$131:$AH$131</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>21.03.</c:v>
                 </c:pt>
@@ -1906,6 +1921,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>04.09.</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>07.09.</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1947,6 +1965,9 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
@@ -2051,7 +2072,7 @@
             <c:strRef>
               <c:f>'Gesamtranking Print'!$B$131:$AH$131</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>21.03.</c:v>
                 </c:pt>
@@ -2084,6 +2105,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>04.09.</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>07.09.</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2126,6 +2150,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2295,7 +2322,7 @@
                       </c:ext>
                     </c:extLst>
                     <c:strCache>
-                      <c:ptCount val="11"/>
+                      <c:ptCount val="12"/>
                       <c:pt idx="0">
                         <c:v>21.03.</c:v>
                       </c:pt>
@@ -2328,6 +2355,9 @@
                       </c:pt>
                       <c:pt idx="10">
                         <c:v>04.09.</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>07.09.</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -2499,7 +2529,7 @@
                       </c:ext>
                     </c:extLst>
                     <c:strCache>
-                      <c:ptCount val="11"/>
+                      <c:ptCount val="12"/>
                       <c:pt idx="0">
                         <c:v>21.03.</c:v>
                       </c:pt>
@@ -2532,6 +2562,9 @@
                       </c:pt>
                       <c:pt idx="10">
                         <c:v>04.09.</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>07.09.</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -2710,7 +2743,7 @@
                       </c:ext>
                     </c:extLst>
                     <c:strCache>
-                      <c:ptCount val="11"/>
+                      <c:ptCount val="12"/>
                       <c:pt idx="0">
                         <c:v>21.03.</c:v>
                       </c:pt>
@@ -2743,6 +2776,9 @@
                       </c:pt>
                       <c:pt idx="10">
                         <c:v>04.09.</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>07.09.</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -3156,6 +3192,9 @@
                 <c:pt idx="10">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3335,6 +3374,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -3680,6 +3722,9 @@
                 <c:pt idx="10">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>-1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3860,6 +3905,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4202,6 +4250,9 @@
                 <c:pt idx="10">
                   <c:v>-1</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4382,6 +4433,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4717,6 +4771,9 @@
                 <c:pt idx="10">
                   <c:v>-1</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>-1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4889,6 +4946,9 @@
                   <c:v>-1</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>-1</c:v>
                 </c:pt>
               </c:numCache>
@@ -7482,10 +7542,10 @@
         <v>3</v>
       </c>
       <c r="H8" s="42">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I8" s="69">
-        <v>0.28205128205128205</v>
+        <v>0.26190476190476192</v>
       </c>
       <c r="J8" s="9"/>
       <c r="K8" s="8"/>
@@ -7509,10 +7569,10 @@
         <v>1</v>
       </c>
       <c r="H9" s="42">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I9" s="69">
-        <v>0.32500000000000001</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J9" s="9"/>
       <c r="K9" s="8"/>
@@ -7539,7 +7599,7 @@
         <v>3</v>
       </c>
       <c r="I10" s="69">
-        <v>0.30864197530864196</v>
+        <v>0.29545454545454547</v>
       </c>
       <c r="J10" s="9"/>
       <c r="K10" s="8"/>
@@ -7563,10 +7623,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" s="73">
-        <v>0.28735632183908044</v>
+        <v>0.29032258064516131</v>
       </c>
       <c r="J11" s="9"/>
       <c r="K11" s="8"/>
@@ -7706,7 +7766,7 @@
         <v>3</v>
       </c>
       <c r="C17" s="42">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="D17" s="42">
         <v>1</v>
@@ -7719,7 +7779,7 @@
         <v>2</v>
       </c>
       <c r="H17" s="42">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I17" s="42">
         <v>1</v>
@@ -7732,7 +7792,7 @@
         <v>3</v>
       </c>
       <c r="M17" s="15">
-        <v>6.4545454545454541</v>
+        <v>6.75</v>
       </c>
       <c r="N17" s="42">
         <v>1</v>
@@ -7749,7 +7809,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="42">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D18" s="42"/>
       <c r="E18" s="24"/>
@@ -7760,7 +7820,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="42">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I18" s="42"/>
       <c r="J18" s="24"/>
@@ -7771,7 +7831,7 @@
         <v>1</v>
       </c>
       <c r="M18" s="15">
-        <v>6.3636363636363633</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="N18" s="42"/>
       <c r="O18" s="9"/>
@@ -7786,7 +7846,7 @@
         <v>2</v>
       </c>
       <c r="C19" s="42">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D19" s="42"/>
       <c r="E19" s="24"/>
@@ -7797,7 +7857,7 @@
         <v>3</v>
       </c>
       <c r="H19" s="42">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I19" s="42"/>
       <c r="J19" s="24"/>
@@ -7808,7 +7868,7 @@
         <v>2</v>
       </c>
       <c r="M19" s="15">
-        <v>5.3636363636363633</v>
+        <v>5.25</v>
       </c>
       <c r="N19" s="42"/>
       <c r="O19" s="9"/>
@@ -7824,7 +7884,7 @@
         <v>0</v>
       </c>
       <c r="C20" s="42">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D20" s="42"/>
       <c r="E20" s="24"/>
@@ -7835,7 +7895,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="42">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I20" s="42"/>
       <c r="J20" s="24"/>
@@ -7846,7 +7906,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="15">
-        <v>4.1818181818181817</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="N20" s="42"/>
       <c r="O20" s="9"/>
@@ -7923,7 +7983,7 @@
         <v>3</v>
       </c>
       <c r="C23" s="15">
-        <v>2.2903225806451615</v>
+        <v>2.3823529411764706</v>
       </c>
       <c r="D23" s="42">
         <v>1</v>
@@ -7960,7 +8020,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="15">
-        <v>2.2580645161290325</v>
+        <v>2.3529411764705883</v>
       </c>
       <c r="D24" s="42"/>
       <c r="E24" s="24"/>
@@ -7993,7 +8053,7 @@
         <v>2</v>
       </c>
       <c r="C25" s="15">
-        <v>1.903225806451613</v>
+        <v>1.8529411764705883</v>
       </c>
       <c r="D25" s="42"/>
       <c r="E25" s="24"/>
@@ -8026,7 +8086,7 @@
         <v>0</v>
       </c>
       <c r="C26" s="15">
-        <v>1.4838709677419355</v>
+        <v>1.4705882352941178</v>
       </c>
       <c r="D26" s="42"/>
       <c r="E26" s="24"/>
@@ -8161,7 +8221,7 @@
         <v>3</v>
       </c>
       <c r="C31" s="4">
-        <v>92606</v>
+        <v>102210</v>
       </c>
       <c r="D31" s="42">
         <v>1</v>
@@ -8174,7 +8234,7 @@
         <v>3</v>
       </c>
       <c r="H31" s="4">
-        <v>8418.7272727272721</v>
+        <v>8517.5</v>
       </c>
       <c r="I31" s="42">
         <v>1</v>
@@ -8187,7 +8247,7 @@
         <v>3</v>
       </c>
       <c r="M31" s="4">
-        <v>2987.2903225806454</v>
+        <v>3006.1764705882351</v>
       </c>
       <c r="N31" s="42">
         <v>1</v>
@@ -8204,7 +8264,7 @@
         <v>1</v>
       </c>
       <c r="C32" s="4">
-        <v>92417</v>
+        <v>102021</v>
       </c>
       <c r="D32" s="42"/>
       <c r="E32" s="24"/>
@@ -8215,7 +8275,7 @@
         <v>1</v>
       </c>
       <c r="H32" s="4">
-        <v>8401.545454545454</v>
+        <v>8501.75</v>
       </c>
       <c r="I32" s="42"/>
       <c r="J32" s="24"/>
@@ -8226,7 +8286,7 @@
         <v>1</v>
       </c>
       <c r="M32" s="4">
-        <v>2981.1935483870966</v>
+        <v>3000.6176470588234</v>
       </c>
       <c r="N32" s="42"/>
       <c r="O32" s="8"/>
@@ -8241,7 +8301,7 @@
         <v>2</v>
       </c>
       <c r="C33" s="4">
-        <v>88609</v>
+        <v>96754</v>
       </c>
       <c r="D33" s="42"/>
       <c r="E33" s="24"/>
@@ -8252,7 +8312,7 @@
         <v>2</v>
       </c>
       <c r="H33" s="4">
-        <v>8055.363636363636</v>
+        <v>8062.833333333333</v>
       </c>
       <c r="I33" s="42"/>
       <c r="J33" s="24"/>
@@ -8263,7 +8323,7 @@
         <v>2</v>
       </c>
       <c r="M33" s="4">
-        <v>2858.3548387096776</v>
+        <v>2845.705882352941</v>
       </c>
       <c r="N33" s="42"/>
       <c r="O33" s="8"/>
@@ -8279,7 +8339,7 @@
         <v>0</v>
       </c>
       <c r="C34" s="4">
-        <v>87494</v>
+        <v>95639</v>
       </c>
       <c r="D34" s="42"/>
       <c r="E34" s="24"/>
@@ -8290,7 +8350,7 @@
         <v>0</v>
       </c>
       <c r="H34" s="4">
-        <v>7954</v>
+        <v>7969.916666666667</v>
       </c>
       <c r="I34" s="42"/>
       <c r="J34" s="24"/>
@@ -8301,7 +8361,7 @@
         <v>0</v>
       </c>
       <c r="M34" s="4">
-        <v>2822.3870967741937</v>
+        <v>2812.9117647058824</v>
       </c>
       <c r="N34" s="42"/>
       <c r="O34" s="8"/>
@@ -8418,7 +8478,7 @@
         <v>1</v>
       </c>
       <c r="C39" s="42">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D39" s="42">
         <v>1</v>
@@ -8431,7 +8491,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="4">
-        <v>13364</v>
+        <v>15420</v>
       </c>
       <c r="I39" s="42">
         <v>1</v>
@@ -8461,7 +8521,7 @@
         <v>3</v>
       </c>
       <c r="C40" s="42">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D40" s="42">
         <v>1</v>
@@ -8474,7 +8534,7 @@
         <v>3</v>
       </c>
       <c r="H40" s="4">
-        <v>12850</v>
+        <v>14906</v>
       </c>
       <c r="I40" s="42"/>
       <c r="J40" s="24"/>
@@ -8502,7 +8562,7 @@
         <v>2</v>
       </c>
       <c r="C41" s="42">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D41" s="42"/>
       <c r="E41" s="24"/>
@@ -8513,7 +8573,7 @@
         <v>2</v>
       </c>
       <c r="H41" s="4">
-        <v>8738</v>
+        <v>11308</v>
       </c>
       <c r="I41" s="42"/>
       <c r="J41" s="24"/>
@@ -8539,7 +8599,7 @@
         <v>0</v>
       </c>
       <c r="C42" s="42">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D42" s="42"/>
       <c r="E42" s="24"/>
@@ -8550,7 +8610,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="4">
-        <v>6168</v>
+        <v>8738</v>
       </c>
       <c r="I42" s="42"/>
       <c r="J42" s="24"/>
@@ -8664,7 +8724,7 @@
         <v>1</v>
       </c>
       <c r="M45" s="42">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N45" s="42">
         <v>1</v>
@@ -8705,7 +8765,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N46" s="42"/>
       <c r="O46" s="8"/>
@@ -8731,7 +8791,7 @@
         <v>2</v>
       </c>
       <c r="H47" s="42">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I47" s="42"/>
       <c r="J47" s="24"/>
@@ -8739,10 +8799,10 @@
         <v>2</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M47" s="42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N47" s="42"/>
       <c r="O47" s="8"/>
@@ -8768,18 +8828,18 @@
         <v>0</v>
       </c>
       <c r="H48" s="42">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I48" s="42"/>
       <c r="J48" s="24"/>
       <c r="K48" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M48" s="42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N48" s="42"/>
       <c r="O48" s="8"/>
@@ -8896,7 +8956,7 @@
         <v>3</v>
       </c>
       <c r="C53" s="4">
-        <v>8890</v>
+        <v>10310</v>
       </c>
       <c r="D53" s="42">
         <v>1</v>
@@ -8909,7 +8969,7 @@
         <v>3</v>
       </c>
       <c r="H53" s="42">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="I53" s="42">
         <v>1</v>
@@ -8922,7 +8982,7 @@
         <v>3</v>
       </c>
       <c r="M53" s="4">
-        <v>3540</v>
+        <v>4060</v>
       </c>
       <c r="N53" s="42">
         <v>1</v>
@@ -8936,10 +8996,10 @@
         <v>2</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54" s="4">
-        <v>7100</v>
+        <v>8200</v>
       </c>
       <c r="D54" s="42"/>
       <c r="E54" s="24"/>
@@ -8947,10 +9007,10 @@
         <v>2</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" s="42">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="I54" s="42"/>
       <c r="J54" s="24"/>
@@ -8958,10 +9018,10 @@
         <v>2</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="4">
-        <v>3500</v>
+        <v>3700</v>
       </c>
       <c r="N54" s="42"/>
       <c r="O54" s="8"/>
@@ -8973,10 +9033,10 @@
         <v>3</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C55" s="4">
-        <v>6530</v>
+        <v>7810</v>
       </c>
       <c r="D55" s="42"/>
       <c r="E55" s="24"/>
@@ -8984,10 +9044,10 @@
         <v>3</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" s="42">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I55" s="42"/>
       <c r="J55" s="24"/>
@@ -8995,10 +9055,10 @@
         <v>3</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" s="4">
-        <v>3180</v>
+        <v>3660</v>
       </c>
       <c r="N55" s="42"/>
       <c r="O55" s="8"/>
@@ -9013,7 +9073,7 @@
         <v>2</v>
       </c>
       <c r="C56" s="4">
-        <v>5810</v>
+        <v>5990</v>
       </c>
       <c r="D56" s="42"/>
       <c r="E56" s="24"/>
@@ -9024,7 +9084,7 @@
         <v>2</v>
       </c>
       <c r="H56" s="42">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="I56" s="42"/>
       <c r="J56" s="24"/>
@@ -9035,7 +9095,7 @@
         <v>2</v>
       </c>
       <c r="M56" s="4">
-        <v>2860</v>
+        <v>3040</v>
       </c>
       <c r="N56" s="42"/>
       <c r="O56" s="8"/>
@@ -9112,7 +9172,7 @@
         <v>3</v>
       </c>
       <c r="C59" s="42">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D59" s="42">
         <v>1</v>
@@ -9125,7 +9185,7 @@
         <v>3</v>
       </c>
       <c r="H59" s="4">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="I59" s="42">
         <v>1</v>
@@ -9135,10 +9195,10 @@
         <v>1</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M59" s="42">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N59" s="42">
         <v>1</v>
@@ -9155,7 +9215,7 @@
         <v>0</v>
       </c>
       <c r="C60" s="42">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D60" s="42"/>
       <c r="E60" s="24"/>
@@ -9166,22 +9226,20 @@
         <v>0</v>
       </c>
       <c r="H60" s="4">
-        <v>1500</v>
+        <v>1650</v>
       </c>
       <c r="I60" s="42"/>
       <c r="J60" s="24"/>
       <c r="K60" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M60" s="42">
-        <v>7</v>
-      </c>
-      <c r="N60" s="42">
-        <v>1</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="N60" s="42"/>
       <c r="O60" s="8"/>
       <c r="P60" s="8"/>
       <c r="Q60" s="8"/>
@@ -9191,10 +9249,10 @@
         <v>3</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C61" s="42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D61" s="42"/>
       <c r="E61" s="24"/>
@@ -9205,7 +9263,7 @@
         <v>1</v>
       </c>
       <c r="H61" s="4">
-        <v>950</v>
+        <v>1300</v>
       </c>
       <c r="I61" s="42"/>
       <c r="J61" s="24"/>
@@ -9228,15 +9286,15 @@
         <v>4</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62" s="42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D62" s="42"/>
       <c r="E62" s="24"/>
       <c r="F62" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>2</v>
@@ -9327,10 +9385,10 @@
         <v>1</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C65" s="4">
-        <v>2100</v>
+        <v>2800</v>
       </c>
       <c r="D65" s="42">
         <v>1</v>
@@ -9358,7 +9416,9 @@
       <c r="M65" s="4">
         <v>1350</v>
       </c>
-      <c r="N65" s="42"/>
+      <c r="N65" s="42">
+        <v>1</v>
+      </c>
       <c r="O65" s="8"/>
       <c r="P65" s="8"/>
       <c r="Q65" s="8"/>
@@ -9368,10 +9428,10 @@
         <v>2</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C66" s="4">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="D66" s="42"/>
       <c r="E66" s="24"/>
@@ -9538,7 +9598,7 @@
         <v>1</v>
       </c>
       <c r="C71" s="42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D71" s="42">
         <v>1</v>
@@ -9551,7 +9611,7 @@
         <v>1</v>
       </c>
       <c r="H71" s="4">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="I71" s="42">
         <v>1</v>
@@ -9571,7 +9631,7 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>2</v>
@@ -9579,9 +9639,7 @@
       <c r="C72" s="42">
         <v>1</v>
       </c>
-      <c r="D72" s="42">
-        <v>1</v>
-      </c>
+      <c r="D72" s="42"/>
       <c r="E72" s="24"/>
       <c r="F72" s="5">
         <v>2</v>
@@ -9777,7 +9835,7 @@
         <v>1</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" s="4">
         <v>8</v>
@@ -9793,9 +9851,11 @@
         <v>0</v>
       </c>
       <c r="H79" s="4">
-        <v>11</v>
-      </c>
-      <c r="I79" s="42"/>
+        <v>12</v>
+      </c>
+      <c r="I79" s="42">
+        <v>1</v>
+      </c>
       <c r="J79" s="24"/>
       <c r="K79" s="5">
         <v>1</v>
@@ -9815,26 +9875,30 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
+        <v>1</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>1</v>
-      </c>
       <c r="C80" s="4">
-        <v>7</v>
-      </c>
-      <c r="D80" s="42"/>
+        <v>8</v>
+      </c>
+      <c r="D80" s="42">
+        <v>1</v>
+      </c>
       <c r="E80" s="24"/>
       <c r="F80" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H80" s="4">
-        <v>11</v>
-      </c>
-      <c r="I80" s="42"/>
+        <v>12</v>
+      </c>
+      <c r="I80" s="42">
+        <v>1</v>
+      </c>
       <c r="J80" s="24"/>
       <c r="K80" s="5">
         <v>2</v>
@@ -9858,20 +9922,22 @@
         <v>3</v>
       </c>
       <c r="C81" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D81" s="42"/>
       <c r="E81" s="24"/>
       <c r="F81" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H81" s="4">
-        <v>11</v>
-      </c>
-      <c r="I81" s="42"/>
+        <v>12</v>
+      </c>
+      <c r="I81" s="42">
+        <v>1</v>
+      </c>
       <c r="J81" s="24"/>
       <c r="K81" s="5">
         <v>3</v>
@@ -9880,7 +9946,7 @@
         <v>2</v>
       </c>
       <c r="M81" s="4">
-        <v>290</v>
+        <v>350</v>
       </c>
       <c r="N81" s="42"/>
       <c r="O81" s="8"/>
@@ -9900,15 +9966,17 @@
       <c r="D82" s="42"/>
       <c r="E82" s="24"/>
       <c r="F82" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H82" s="4">
-        <v>11</v>
-      </c>
-      <c r="I82" s="42"/>
+        <v>12</v>
+      </c>
+      <c r="I82" s="42">
+        <v>1</v>
+      </c>
       <c r="J82" s="24"/>
       <c r="K82" s="5">
         <v>4</v>
@@ -9917,7 +9985,7 @@
         <v>0</v>
       </c>
       <c r="M82" s="4">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="N82" s="42"/>
       <c r="O82" s="8"/>
@@ -9994,7 +10062,7 @@
         <v>3</v>
       </c>
       <c r="C85" s="44">
-        <v>15.454545454545455</v>
+        <v>14.166666666666666</v>
       </c>
       <c r="D85" s="42">
         <v>1</v>
@@ -10007,7 +10075,7 @@
         <v>3</v>
       </c>
       <c r="H85" s="4">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I85" s="42">
         <v>1</v>
@@ -10037,7 +10105,7 @@
         <v>1</v>
       </c>
       <c r="C86" s="44">
-        <v>16.363636363636363</v>
+        <v>15</v>
       </c>
       <c r="D86" s="42"/>
       <c r="E86" s="24"/>
@@ -10048,7 +10116,7 @@
         <v>1</v>
       </c>
       <c r="H86" s="4">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I86" s="42"/>
       <c r="J86" s="8"/>
@@ -10059,7 +10127,7 @@
         <v>1</v>
       </c>
       <c r="M86" s="4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N86" s="42"/>
       <c r="O86" s="8"/>
@@ -10074,7 +10142,7 @@
         <v>2</v>
       </c>
       <c r="C87" s="44">
-        <v>26.363636363636363</v>
+        <v>29.166666666666668</v>
       </c>
       <c r="D87" s="42"/>
       <c r="E87" s="24"/>
@@ -10111,7 +10179,7 @@
         <v>0</v>
       </c>
       <c r="C88" s="44">
-        <v>38.18181818181818</v>
+        <v>40</v>
       </c>
       <c r="D88" s="42"/>
       <c r="E88" s="24"/>
@@ -10284,7 +10352,7 @@
         <v>3</v>
       </c>
       <c r="M95" s="65">
-        <v>0.45454545454545453</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="N95" s="70">
         <v>5</v>
@@ -10293,7 +10361,7 @@
         <v>0.2</v>
       </c>
       <c r="P95" s="65">
-        <v>9.0909090909090912E-2</v>
+        <v>8.3333333333333343E-2</v>
       </c>
       <c r="Q95" s="63"/>
     </row>
@@ -10317,7 +10385,7 @@
         <v>1</v>
       </c>
       <c r="M96" s="55">
-        <v>0.27272727272727271</v>
+        <v>0.25</v>
       </c>
       <c r="N96" s="66">
         <v>3</v>
@@ -10326,7 +10394,7 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="P96" s="55">
-        <v>9.0909090909090898E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="Q96" s="63"/>
     </row>
@@ -10379,16 +10447,16 @@
         <v>2</v>
       </c>
       <c r="M98" s="55">
-        <v>0.27272727272727271</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="N98" s="66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O98" s="65">
-        <v>0.33333333333333331</v>
+        <v>0.25</v>
       </c>
       <c r="P98" s="55">
-        <v>9.0909090909090898E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="Q98" s="63"/>
     </row>
@@ -10474,16 +10542,16 @@
         <v>1</v>
       </c>
       <c r="M101" s="55">
-        <v>0.27272727272727271</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="N101" s="66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O101" s="65">
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="P101" s="55">
-        <v>0.1818181818181818</v>
+        <v>0.25</v>
       </c>
       <c r="Q101" s="63"/>
     </row>
@@ -10538,7 +10606,7 @@
         <v>2</v>
       </c>
       <c r="M103" s="55">
-        <v>0.27272727272727271</v>
+        <v>0.25</v>
       </c>
       <c r="N103" s="66">
         <v>3</v>
@@ -10547,7 +10615,7 @@
         <v>1</v>
       </c>
       <c r="P103" s="55">
-        <v>0.27272727272727271</v>
+        <v>0.25</v>
       </c>
       <c r="Q103" s="63"/>
     </row>
@@ -10633,7 +10701,7 @@
         <v>2</v>
       </c>
       <c r="M106" s="55">
-        <v>0.45454545454545453</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="N106" s="66">
         <v>5</v>
@@ -10642,7 +10710,7 @@
         <v>0.75</v>
       </c>
       <c r="P106" s="55">
-        <v>0.34090909090909088</v>
+        <v>0.3125</v>
       </c>
       <c r="Q106" s="63"/>
     </row>
@@ -10753,7 +10821,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K111" s="8"/>
       <c r="L111" s="8"/>
@@ -10771,7 +10839,7 @@
         <v>1</v>
       </c>
       <c r="C112" s="20">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L112" s="74" t="s">
         <v>59</v>
@@ -10781,7 +10849,7 @@
       </c>
       <c r="N112" s="75"/>
       <c r="O112" s="76">
-        <v>-6.8181818181818121E-2</v>
+        <v>-6.25E-2</v>
       </c>
       <c r="Q112" s="63"/>
     </row>
@@ -10804,7 +10872,7 @@
         <v>3</v>
       </c>
       <c r="C114" s="20">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="115" spans="1:34" x14ac:dyDescent="0.25">
@@ -10971,7 +11039,9 @@
       <c r="L123" s="5">
         <v>-1</v>
       </c>
-      <c r="M123" s="5"/>
+      <c r="M123" s="5">
+        <v>-1</v>
+      </c>
       <c r="N123" s="5"/>
       <c r="O123" s="5"/>
       <c r="P123" s="5"/>
@@ -11031,7 +11101,9 @@
       <c r="L124" s="5">
         <v>1</v>
       </c>
-      <c r="M124" s="5"/>
+      <c r="M124" s="5">
+        <v>1</v>
+      </c>
       <c r="N124" s="5"/>
       <c r="O124" s="5"/>
       <c r="P124" s="5"/>
@@ -11091,7 +11163,9 @@
       <c r="L125" s="5">
         <v>1</v>
       </c>
-      <c r="M125" s="5"/>
+      <c r="M125" s="5">
+        <v>-1</v>
+      </c>
       <c r="N125" s="5"/>
       <c r="O125" s="5"/>
       <c r="P125" s="5"/>
@@ -11151,7 +11225,9 @@
       <c r="L126" s="5">
         <v>-1</v>
       </c>
-      <c r="M126" s="5"/>
+      <c r="M126" s="5">
+        <v>1</v>
+      </c>
       <c r="N126" s="5"/>
       <c r="O126" s="5"/>
       <c r="P126" s="5"/>
@@ -11213,7 +11289,9 @@
       <c r="L131" s="59" t="s">
         <v>78</v>
       </c>
-      <c r="M131" s="59"/>
+      <c r="M131" s="59" t="s">
+        <v>79</v>
+      </c>
       <c r="N131" s="59"/>
       <c r="O131" s="59"/>
       <c r="P131" s="59"/>
@@ -11273,7 +11351,9 @@
       <c r="L132" s="5">
         <v>2</v>
       </c>
-      <c r="M132" s="5"/>
+      <c r="M132" s="5">
+        <v>1</v>
+      </c>
       <c r="N132" s="68"/>
       <c r="O132" s="5"/>
       <c r="P132" s="5"/>
@@ -11333,7 +11413,9 @@
       <c r="L133" s="5">
         <v>7</v>
       </c>
-      <c r="M133" s="5"/>
+      <c r="M133" s="5">
+        <v>9</v>
+      </c>
       <c r="N133" s="68"/>
       <c r="O133" s="5"/>
       <c r="P133" s="5"/>
@@ -11393,7 +11475,9 @@
       <c r="L134" s="5">
         <v>3</v>
       </c>
-      <c r="M134" s="5"/>
+      <c r="M134" s="5">
+        <v>3</v>
+      </c>
       <c r="N134" s="68"/>
       <c r="O134" s="5"/>
       <c r="P134" s="5"/>
@@ -11453,7 +11537,9 @@
       <c r="L135" s="5">
         <v>22</v>
       </c>
-      <c r="M135" s="5"/>
+      <c r="M135" s="5">
+        <v>25</v>
+      </c>
       <c r="N135" s="68"/>
       <c r="O135" s="5"/>
       <c r="P135" s="5"/>
@@ -11622,107 +11708,107 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A132:A139">
-    <cfRule type="containsText" dxfId="34" priority="1226" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="34" priority="1240" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A132)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A110:C118">
-    <cfRule type="containsText" dxfId="33" priority="1185" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="33" priority="1199" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A110)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:D20">
-    <cfRule type="containsText" dxfId="32" priority="109" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="32" priority="123" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22:D27">
-    <cfRule type="containsText" dxfId="31" priority="74" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="31" priority="88" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30:D34">
-    <cfRule type="containsText" dxfId="30" priority="91" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="30" priority="105" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38:D42">
-    <cfRule type="containsText" dxfId="29" priority="14" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="29" priority="13" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44:D48">
-    <cfRule type="containsText" dxfId="28" priority="11" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="28" priority="10" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A44)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:D56">
-    <cfRule type="containsText" dxfId="27" priority="440" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="27" priority="454" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A52)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:D62">
-    <cfRule type="containsText" dxfId="26" priority="38" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="26" priority="52" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A58)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64:D68">
-    <cfRule type="containsText" dxfId="25" priority="77" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="25" priority="91" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A64)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A70:D74">
-    <cfRule type="containsText" dxfId="24" priority="4" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="24" priority="5" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A70)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A78:D82">
-    <cfRule type="containsText" dxfId="23" priority="17" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="23" priority="3" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A78)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A84:D88">
-    <cfRule type="containsText" dxfId="22" priority="67" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="22" priority="81" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",A84)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:I11">
-    <cfRule type="containsText" dxfId="21" priority="258" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="21" priority="272" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:I20">
-    <cfRule type="containsText" dxfId="20" priority="94" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="20" priority="108" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F22:I26">
-    <cfRule type="containsText" dxfId="19" priority="15" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="19" priority="14" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:I34">
-    <cfRule type="containsText" dxfId="18" priority="90" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="18" priority="104" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F38:I42">
-    <cfRule type="containsText" dxfId="17" priority="44" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="17" priority="58" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F44:I48">
-    <cfRule type="containsText" dxfId="16" priority="40" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="16" priority="54" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F44)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52:I56">
-    <cfRule type="containsText" dxfId="15" priority="39" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="15" priority="53" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F52)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F58:I62">
-    <cfRule type="containsText" dxfId="14" priority="9" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="14" priority="23" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F58)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11732,7 +11818,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F70:I74">
-    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="12" priority="4" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F70)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11742,42 +11828,42 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F84:I88">
-    <cfRule type="containsText" dxfId="10" priority="16" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="10" priority="30" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",F84)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16:N20">
-    <cfRule type="containsText" dxfId="9" priority="75" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="9" priority="89" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K22:N26">
-    <cfRule type="containsText" dxfId="8" priority="379" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="8" priority="393" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K30:N34">
-    <cfRule type="containsText" dxfId="7" priority="89" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="7" priority="103" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K38:N42">
-    <cfRule type="containsText" dxfId="6" priority="12" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="6" priority="11" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K44:N48">
-    <cfRule type="containsText" dxfId="5" priority="10" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="5" priority="9" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K44)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K52:N56">
-    <cfRule type="containsText" dxfId="4" priority="428" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="4" priority="442" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K52)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K58:N62">
-    <cfRule type="containsText" dxfId="3" priority="8" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="3" priority="22" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K58)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11787,12 +11873,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K78:N82">
-    <cfRule type="containsText" dxfId="1" priority="68" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="1" priority="82" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K78)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K84:N88">
-    <cfRule type="containsText" dxfId="0" priority="56" operator="containsText" text="DOPPEL">
+    <cfRule type="containsText" dxfId="0" priority="70" operator="containsText" text="DOPPEL">
       <formula>NOT(ISERROR(SEARCH("DOPPEL",K84)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Statistik_Jassen.xlsx
+++ b/Statistik_Jassen.xlsx
@@ -32,8 +32,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="60" formatCode="dd.mm.yyyy"/>
   </numFmts>
   <fonts count="1">
     <font>

--- a/Statistik_Jassen.xlsx
+++ b/Statistik_Jassen.xlsx
@@ -432,10 +432,10 @@
         <v>Chäli</v>
       </c>
       <c r="H8">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I8">
-        <v>0.2619047619047619</v>
+        <v>0.27058823529411763</v>
       </c>
     </row>
     <row r="9">
@@ -446,10 +446,10 @@
         <v>Küng</v>
       </c>
       <c r="H9">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I9">
-        <v>0.3333333333333333</v>
+        <v>0.34831460674157305</v>
       </c>
     </row>
     <row r="10">
@@ -460,10 +460,10 @@
         <v>Goonse</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10">
-        <v>0.29545454545454547</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="11">
@@ -477,7 +477,7 @@
         <v>1</v>
       </c>
       <c r="I11">
-        <v>0.2903225806451613</v>
+        <v>0.2872340425531915</v>
       </c>
     </row>
     <row r="14">
@@ -531,7 +531,7 @@
         <v>Chäli</v>
       </c>
       <c r="C17">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -543,7 +543,7 @@
         <v>Goonse</v>
       </c>
       <c r="H17">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I17">
         <v>1</v>
@@ -555,7 +555,7 @@
         <v>Chäli</v>
       </c>
       <c r="M17">
-        <v>6.75</v>
+        <v>6.307692</v>
       </c>
       <c r="N17">
         <v>1</v>
@@ -569,7 +569,7 @@
         <v>Küng</v>
       </c>
       <c r="C18">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F18">
         <v>2</v>
@@ -587,7 +587,7 @@
         <v>Küng</v>
       </c>
       <c r="M18">
-        <v>6.583333</v>
+        <v>6.230769</v>
       </c>
     </row>
     <row r="19">
@@ -598,16 +598,16 @@
         <v>Goonse</v>
       </c>
       <c r="C19">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" t="str">
         <v>Chäli</v>
       </c>
       <c r="H19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K19">
         <v>3</v>
@@ -616,7 +616,7 @@
         <v>Goonse</v>
       </c>
       <c r="M19">
-        <v>5.166667</v>
+        <v>4.846154</v>
       </c>
     </row>
     <row r="20">
@@ -627,7 +627,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C20">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F20">
         <v>4</v>
@@ -645,7 +645,7 @@
         <v>Fuchs</v>
       </c>
       <c r="M20">
-        <v>4.166667</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -694,7 +694,7 @@
         <v>Chäli</v>
       </c>
       <c r="C23">
-        <v>2.382353</v>
+        <v>2.342857</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -729,7 +729,7 @@
         <v>Küng</v>
       </c>
       <c r="C24">
-        <v>2.323529</v>
+        <v>2.314286</v>
       </c>
       <c r="F24">
         <v>2</v>
@@ -758,7 +758,7 @@
         <v>Goonse</v>
       </c>
       <c r="C25">
-        <v>1.823529</v>
+        <v>1.8</v>
       </c>
       <c r="F25">
         <v>2</v>
@@ -787,7 +787,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C26">
-        <v>1.470588</v>
+        <v>1.485714</v>
       </c>
       <c r="F26">
         <v>4</v>
@@ -856,10 +856,10 @@
         <v>1</v>
       </c>
       <c r="B31" t="str">
-        <v>Chäli</v>
+        <v>Küng</v>
       </c>
       <c r="C31">
-        <v>102210</v>
+        <v>105036</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -868,10 +868,10 @@
         <v>1</v>
       </c>
       <c r="G31" t="str">
-        <v>Chäli</v>
+        <v>Küng</v>
       </c>
       <c r="H31">
-        <v>8517.5</v>
+        <v>8079.692308</v>
       </c>
       <c r="I31">
         <v>1</v>
@@ -880,10 +880,10 @@
         <v>1</v>
       </c>
       <c r="L31" t="str">
-        <v>Chäli</v>
+        <v>Küng</v>
       </c>
       <c r="M31">
-        <v>3006.176471</v>
+        <v>3001.028571</v>
       </c>
       <c r="N31">
         <v>1</v>
@@ -894,28 +894,28 @@
         <v>2</v>
       </c>
       <c r="B32" t="str">
-        <v>Küng</v>
+        <v>Chäli</v>
       </c>
       <c r="C32">
-        <v>102021</v>
+        <v>104010</v>
       </c>
       <c r="F32">
         <v>2</v>
       </c>
       <c r="G32" t="str">
-        <v>Küng</v>
+        <v>Chäli</v>
       </c>
       <c r="H32">
-        <v>8501.75</v>
+        <v>8000.769231</v>
       </c>
       <c r="K32">
         <v>2</v>
       </c>
       <c r="L32" t="str">
-        <v>Küng</v>
+        <v>Chäli</v>
       </c>
       <c r="M32">
-        <v>3000.617647</v>
+        <v>2971.714286</v>
       </c>
     </row>
     <row r="33">
@@ -923,28 +923,28 @@
         <v>3</v>
       </c>
       <c r="B33" t="str">
-        <v>Goonse</v>
+        <v>Fuchs</v>
       </c>
       <c r="C33">
-        <v>96754</v>
+        <v>98654</v>
       </c>
       <c r="F33">
         <v>3</v>
       </c>
       <c r="G33" t="str">
-        <v>Goonse</v>
+        <v>Fuchs</v>
       </c>
       <c r="H33">
-        <v>8062.833333</v>
+        <v>7588.769231</v>
       </c>
       <c r="K33">
         <v>3</v>
       </c>
       <c r="L33" t="str">
-        <v>Goonse</v>
+        <v>Fuchs</v>
       </c>
       <c r="M33">
-        <v>2845.705882</v>
+        <v>2818.685714</v>
       </c>
     </row>
     <row r="34">
@@ -952,28 +952,28 @@
         <v>4</v>
       </c>
       <c r="B34" t="str">
-        <v>Fuchs</v>
+        <v>Goonse</v>
       </c>
       <c r="C34">
-        <v>95639</v>
+        <v>98554</v>
       </c>
       <c r="F34">
         <v>4</v>
       </c>
       <c r="G34" t="str">
-        <v>Fuchs</v>
+        <v>Goonse</v>
       </c>
       <c r="H34">
-        <v>7969.916667</v>
+        <v>7581.076923</v>
       </c>
       <c r="K34">
         <v>4</v>
       </c>
       <c r="L34" t="str">
-        <v>Fuchs</v>
+        <v>Goonse</v>
       </c>
       <c r="M34">
-        <v>2812.911765</v>
+        <v>2815.828571</v>
       </c>
     </row>
     <row r="36">
@@ -1367,7 +1367,7 @@
         <v>Chäli</v>
       </c>
       <c r="C53">
-        <v>10310</v>
+        <v>10460</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -1463,7 +1463,7 @@
         <v>Goonse</v>
       </c>
       <c r="C56">
-        <v>5990</v>
+        <v>6030</v>
       </c>
       <c r="F56">
         <v>4</v>
@@ -1472,7 +1472,7 @@
         <v>Goonse</v>
       </c>
       <c r="H56">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K56">
         <v>4</v>
@@ -1481,7 +1481,7 @@
         <v>Goonse</v>
       </c>
       <c r="M56">
-        <v>3040</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="58">
@@ -1530,7 +1530,7 @@
         <v>Chäli</v>
       </c>
       <c r="C59">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -1542,7 +1542,7 @@
         <v>Chäli</v>
       </c>
       <c r="H59">
-        <v>2100</v>
+        <v>2250</v>
       </c>
       <c r="I59">
         <v>1</v>
@@ -1991,7 +1991,7 @@
         <v>Küng</v>
       </c>
       <c r="C79">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -2003,7 +2003,7 @@
         <v>Küng</v>
       </c>
       <c r="H79">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I79">
         <v>1</v>
@@ -2015,7 +2015,7 @@
         <v>Chäli</v>
       </c>
       <c r="M79">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="N79">
         <v>1</v>
@@ -2023,7 +2023,7 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B80" t="str">
         <v>Goonse</v>
@@ -2031,9 +2031,6 @@
       <c r="C80">
         <v>8</v>
       </c>
-      <c r="D80">
-        <v>1</v>
-      </c>
       <c r="F80">
         <v>1</v>
       </c>
@@ -2041,7 +2038,7 @@
         <v>Fuchs</v>
       </c>
       <c r="H80">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I80">
         <v>1</v>
@@ -2073,7 +2070,7 @@
         <v>Goonse</v>
       </c>
       <c r="H81">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I81">
         <v>1</v>
@@ -2085,7 +2082,7 @@
         <v>Goonse</v>
       </c>
       <c r="M81">
-        <v>360</v>
+        <v>370</v>
       </c>
     </row>
     <row r="82">
@@ -2096,7 +2093,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C82">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82">
         <v>1</v>
@@ -2105,7 +2102,7 @@
         <v>Chäli</v>
       </c>
       <c r="H82">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I82">
         <v>1</v>
@@ -2166,7 +2163,7 @@
         <v>Chäli</v>
       </c>
       <c r="C85">
-        <v>14.166667</v>
+        <v>13.846154</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -2175,7 +2172,7 @@
         <v>1</v>
       </c>
       <c r="G85" t="str">
-        <v>Chäli</v>
+        <v>Küng</v>
       </c>
       <c r="H85">
         <v>21</v>
@@ -2190,7 +2187,7 @@
         <v>Chäli</v>
       </c>
       <c r="M85">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N85">
         <v>1</v>
@@ -2204,16 +2201,19 @@
         <v>Küng</v>
       </c>
       <c r="C86">
-        <v>15.833333</v>
+        <v>14.615385</v>
       </c>
       <c r="F86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G86" t="str">
-        <v>Küng</v>
+        <v>Chäli</v>
       </c>
       <c r="H86">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="I86">
+        <v>1</v>
       </c>
       <c r="K86">
         <v>2</v>
@@ -2233,13 +2233,13 @@
         <v>Goonse</v>
       </c>
       <c r="C87">
-        <v>30</v>
+        <v>28.461538</v>
       </c>
       <c r="F87">
         <v>3</v>
       </c>
       <c r="G87" t="str">
-        <v>Goonse</v>
+        <v>Fuchs</v>
       </c>
       <c r="H87">
         <v>14</v>
@@ -2262,16 +2262,16 @@
         <v>Fuchs</v>
       </c>
       <c r="C88">
-        <v>40</v>
+        <v>36.923077</v>
       </c>
       <c r="F88">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G88" t="str">
-        <v>Fuchs</v>
+        <v>Goonse</v>
       </c>
       <c r="H88">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K88">
         <v>4</v>
@@ -2308,16 +2308,16 @@
         <v>Fuchs</v>
       </c>
       <c r="M95">
-        <v>0.25</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="N95">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O95">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="P95">
-        <v>0.08333333333333333</v>
+        <v>0.15384615384615385</v>
       </c>
     </row>
     <row r="96">
@@ -2328,7 +2328,7 @@
         <v>Goonse</v>
       </c>
       <c r="M96">
-        <v>0.4166666666666667</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="N96">
         <v>5</v>
@@ -2337,7 +2337,7 @@
         <v>0.8</v>
       </c>
       <c r="P96">
-        <v>0.3333333333333333</v>
+        <v>0.3076923076923077</v>
       </c>
     </row>
     <row r="97">
@@ -2348,7 +2348,7 @@
         <v>Chäli</v>
       </c>
       <c r="M97">
-        <v>0.3333333333333333</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="N97">
         <v>4</v>
@@ -2357,7 +2357,7 @@
         <v>0.75</v>
       </c>
       <c r="P97">
-        <v>0.25</v>
+        <v>0.23076923076923078</v>
       </c>
     </row>
     <row r="98">
@@ -2368,7 +2368,7 @@
         <v>Goonse</v>
       </c>
       <c r="M98">
-        <v>0.3333333333333333</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="N98">
         <v>4</v>
@@ -2377,7 +2377,7 @@
         <v>0.25</v>
       </c>
       <c r="P98">
-        <v>0.08333333333333333</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="99">
@@ -2388,7 +2388,7 @@
         <v>Chäli</v>
       </c>
       <c r="M99">
-        <v>0.4166666666666667</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="N99">
         <v>5</v>
@@ -2397,7 +2397,7 @@
         <v>0.2</v>
       </c>
       <c r="P99">
-        <v>0.08333333333333333</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="100">
@@ -2408,16 +2408,16 @@
         <v>Chäli</v>
       </c>
       <c r="M100">
-        <v>0.25</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="N100">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O100">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="P100">
-        <v>0.25</v>
+        <v>0.23076923076923078</v>
       </c>
     </row>
     <row r="110">
@@ -2442,7 +2442,7 @@
         <v>Chäli</v>
       </c>
       <c r="C111">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="112">
@@ -2453,7 +2453,7 @@
         <v>Küng</v>
       </c>
       <c r="C112">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="113">
@@ -2464,7 +2464,7 @@
         <v>Goonse</v>
       </c>
       <c r="C113">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
@@ -2520,6 +2520,9 @@
       <c r="M122">
         <v>12</v>
       </c>
+      <c r="N122">
+        <v>13</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -2561,6 +2564,9 @@
       <c r="M123">
         <v>1</v>
       </c>
+      <c r="N123">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -2602,6 +2608,9 @@
       <c r="M124">
         <v>-1</v>
       </c>
+      <c r="N124">
+        <v>1</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -2643,6 +2652,9 @@
       <c r="M125">
         <v>-1</v>
       </c>
+      <c r="N125">
+        <v>-1</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -2683,6 +2695,9 @@
       </c>
       <c r="M126">
         <v>1</v>
+      </c>
+      <c r="N126">
+        <v>-1</v>
       </c>
     </row>
     <row r="129">
@@ -2727,6 +2742,9 @@
       <c r="M131" t="str">
         <v>07.09.</v>
       </c>
+      <c r="N131" t="str">
+        <v>01.01.</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -2768,6 +2786,9 @@
       <c r="M132">
         <v>9</v>
       </c>
+      <c r="N132">
+        <v>13</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -2809,6 +2830,9 @@
       <c r="M133">
         <v>1</v>
       </c>
+      <c r="N133">
+        <v>1</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -2850,6 +2874,9 @@
       <c r="M134">
         <v>3</v>
       </c>
+      <c r="N134">
+        <v>2</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -2890,6 +2917,9 @@
       </c>
       <c r="M135">
         <v>25</v>
+      </c>
+      <c r="N135">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Statistik_Jassen.xlsx
+++ b/Statistik_Jassen.xlsx
@@ -432,10 +432,10 @@
         <v>Chäli</v>
       </c>
       <c r="H8">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I8">
-        <v>0.27058823529411763</v>
+        <v>0.2619047619047619</v>
       </c>
     </row>
     <row r="9">
@@ -446,10 +446,10 @@
         <v>Küng</v>
       </c>
       <c r="H9">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I9">
-        <v>0.34831460674157305</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -460,10 +460,10 @@
         <v>Goonse</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I10">
-        <v>0.3</v>
+        <v>0.29545454545454547</v>
       </c>
     </row>
     <row r="11">
@@ -477,7 +477,7 @@
         <v>1</v>
       </c>
       <c r="I11">
-        <v>0.2872340425531915</v>
+        <v>0.2903225806451613</v>
       </c>
     </row>
     <row r="14">
@@ -531,7 +531,7 @@
         <v>Chäli</v>
       </c>
       <c r="C17">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -543,7 +543,7 @@
         <v>Goonse</v>
       </c>
       <c r="H17">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I17">
         <v>1</v>
@@ -555,7 +555,7 @@
         <v>Chäli</v>
       </c>
       <c r="M17">
-        <v>6.307692</v>
+        <v>6.75</v>
       </c>
       <c r="N17">
         <v>1</v>
@@ -569,7 +569,7 @@
         <v>Küng</v>
       </c>
       <c r="C18">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F18">
         <v>2</v>
@@ -587,7 +587,7 @@
         <v>Küng</v>
       </c>
       <c r="M18">
-        <v>6.230769</v>
+        <v>6.583333</v>
       </c>
     </row>
     <row r="19">
@@ -598,16 +598,16 @@
         <v>Goonse</v>
       </c>
       <c r="C19">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" t="str">
         <v>Chäli</v>
       </c>
       <c r="H19">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K19">
         <v>3</v>
@@ -616,7 +616,7 @@
         <v>Goonse</v>
       </c>
       <c r="M19">
-        <v>4.846154</v>
+        <v>5.166667</v>
       </c>
     </row>
     <row r="20">
@@ -627,7 +627,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C20">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F20">
         <v>4</v>
@@ -645,7 +645,7 @@
         <v>Fuchs</v>
       </c>
       <c r="M20">
-        <v>4</v>
+        <v>4.166667</v>
       </c>
     </row>
     <row r="22">
@@ -694,7 +694,7 @@
         <v>Chäli</v>
       </c>
       <c r="C23">
-        <v>2.342857</v>
+        <v>2.382353</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -729,7 +729,7 @@
         <v>Küng</v>
       </c>
       <c r="C24">
-        <v>2.314286</v>
+        <v>2.323529</v>
       </c>
       <c r="F24">
         <v>2</v>
@@ -758,7 +758,7 @@
         <v>Goonse</v>
       </c>
       <c r="C25">
-        <v>1.8</v>
+        <v>1.823529</v>
       </c>
       <c r="F25">
         <v>2</v>
@@ -787,7 +787,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C26">
-        <v>1.485714</v>
+        <v>1.470588</v>
       </c>
       <c r="F26">
         <v>4</v>
@@ -856,10 +856,10 @@
         <v>1</v>
       </c>
       <c r="B31" t="str">
-        <v>Küng</v>
+        <v>Chäli</v>
       </c>
       <c r="C31">
-        <v>105036</v>
+        <v>102210</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -868,10 +868,10 @@
         <v>1</v>
       </c>
       <c r="G31" t="str">
-        <v>Küng</v>
+        <v>Chäli</v>
       </c>
       <c r="H31">
-        <v>8079.692308</v>
+        <v>8517.5</v>
       </c>
       <c r="I31">
         <v>1</v>
@@ -880,10 +880,10 @@
         <v>1</v>
       </c>
       <c r="L31" t="str">
-        <v>Küng</v>
+        <v>Chäli</v>
       </c>
       <c r="M31">
-        <v>3001.028571</v>
+        <v>3006.176471</v>
       </c>
       <c r="N31">
         <v>1</v>
@@ -894,28 +894,28 @@
         <v>2</v>
       </c>
       <c r="B32" t="str">
-        <v>Chäli</v>
+        <v>Küng</v>
       </c>
       <c r="C32">
-        <v>104010</v>
+        <v>102021</v>
       </c>
       <c r="F32">
         <v>2</v>
       </c>
       <c r="G32" t="str">
-        <v>Chäli</v>
+        <v>Küng</v>
       </c>
       <c r="H32">
-        <v>8000.769231</v>
+        <v>8501.75</v>
       </c>
       <c r="K32">
         <v>2</v>
       </c>
       <c r="L32" t="str">
-        <v>Chäli</v>
+        <v>Küng</v>
       </c>
       <c r="M32">
-        <v>2971.714286</v>
+        <v>3000.617647</v>
       </c>
     </row>
     <row r="33">
@@ -923,28 +923,28 @@
         <v>3</v>
       </c>
       <c r="B33" t="str">
-        <v>Fuchs</v>
+        <v>Goonse</v>
       </c>
       <c r="C33">
-        <v>98654</v>
+        <v>96754</v>
       </c>
       <c r="F33">
         <v>3</v>
       </c>
       <c r="G33" t="str">
-        <v>Fuchs</v>
+        <v>Goonse</v>
       </c>
       <c r="H33">
-        <v>7588.769231</v>
+        <v>8062.833333</v>
       </c>
       <c r="K33">
         <v>3</v>
       </c>
       <c r="L33" t="str">
-        <v>Fuchs</v>
+        <v>Goonse</v>
       </c>
       <c r="M33">
-        <v>2818.685714</v>
+        <v>2845.705882</v>
       </c>
     </row>
     <row r="34">
@@ -952,28 +952,28 @@
         <v>4</v>
       </c>
       <c r="B34" t="str">
-        <v>Goonse</v>
+        <v>Fuchs</v>
       </c>
       <c r="C34">
-        <v>98554</v>
+        <v>95639</v>
       </c>
       <c r="F34">
         <v>4</v>
       </c>
       <c r="G34" t="str">
-        <v>Goonse</v>
+        <v>Fuchs</v>
       </c>
       <c r="H34">
-        <v>7581.076923</v>
+        <v>7969.916667</v>
       </c>
       <c r="K34">
         <v>4</v>
       </c>
       <c r="L34" t="str">
-        <v>Goonse</v>
+        <v>Fuchs</v>
       </c>
       <c r="M34">
-        <v>2815.828571</v>
+        <v>2812.911765</v>
       </c>
     </row>
     <row r="36">
@@ -1367,7 +1367,7 @@
         <v>Chäli</v>
       </c>
       <c r="C53">
-        <v>10460</v>
+        <v>10310</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -1463,7 +1463,7 @@
         <v>Goonse</v>
       </c>
       <c r="C56">
-        <v>6030</v>
+        <v>5990</v>
       </c>
       <c r="F56">
         <v>4</v>
@@ -1472,7 +1472,7 @@
         <v>Goonse</v>
       </c>
       <c r="H56">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K56">
         <v>4</v>
@@ -1481,7 +1481,7 @@
         <v>Goonse</v>
       </c>
       <c r="M56">
-        <v>3080</v>
+        <v>3040</v>
       </c>
     </row>
     <row r="58">
@@ -1530,7 +1530,7 @@
         <v>Chäli</v>
       </c>
       <c r="C59">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -1542,7 +1542,7 @@
         <v>Chäli</v>
       </c>
       <c r="H59">
-        <v>2250</v>
+        <v>2100</v>
       </c>
       <c r="I59">
         <v>1</v>
@@ -1991,7 +1991,7 @@
         <v>Küng</v>
       </c>
       <c r="C79">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -2003,7 +2003,7 @@
         <v>Küng</v>
       </c>
       <c r="H79">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I79">
         <v>1</v>
@@ -2015,7 +2015,7 @@
         <v>Chäli</v>
       </c>
       <c r="M79">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="N79">
         <v>1</v>
@@ -2023,7 +2023,7 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B80" t="str">
         <v>Goonse</v>
@@ -2031,6 +2031,9 @@
       <c r="C80">
         <v>8</v>
       </c>
+      <c r="D80">
+        <v>1</v>
+      </c>
       <c r="F80">
         <v>1</v>
       </c>
@@ -2038,7 +2041,7 @@
         <v>Fuchs</v>
       </c>
       <c r="H80">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I80">
         <v>1</v>
@@ -2070,7 +2073,7 @@
         <v>Goonse</v>
       </c>
       <c r="H81">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I81">
         <v>1</v>
@@ -2082,7 +2085,7 @@
         <v>Goonse</v>
       </c>
       <c r="M81">
-        <v>370</v>
+        <v>360</v>
       </c>
     </row>
     <row r="82">
@@ -2093,7 +2096,7 @@
         <v>Fuchs</v>
       </c>
       <c r="C82">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F82">
         <v>1</v>
@@ -2102,7 +2105,7 @@
         <v>Chäli</v>
       </c>
       <c r="H82">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I82">
         <v>1</v>
@@ -2163,7 +2166,7 @@
         <v>Chäli</v>
       </c>
       <c r="C85">
-        <v>13.846154</v>
+        <v>14.166667</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -2172,7 +2175,7 @@
         <v>1</v>
       </c>
       <c r="G85" t="str">
-        <v>Küng</v>
+        <v>Chäli</v>
       </c>
       <c r="H85">
         <v>21</v>
@@ -2187,7 +2190,7 @@
         <v>Chäli</v>
       </c>
       <c r="M85">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N85">
         <v>1</v>
@@ -2201,19 +2204,16 @@
         <v>Küng</v>
       </c>
       <c r="C86">
-        <v>14.615385</v>
+        <v>15.833333</v>
       </c>
       <c r="F86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G86" t="str">
-        <v>Chäli</v>
+        <v>Küng</v>
       </c>
       <c r="H86">
-        <v>21</v>
-      </c>
-      <c r="I86">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K86">
         <v>2</v>
@@ -2233,13 +2233,13 @@
         <v>Goonse</v>
       </c>
       <c r="C87">
-        <v>28.461538</v>
+        <v>30</v>
       </c>
       <c r="F87">
         <v>3</v>
       </c>
       <c r="G87" t="str">
-        <v>Fuchs</v>
+        <v>Goonse</v>
       </c>
       <c r="H87">
         <v>14</v>
@@ -2262,16 +2262,16 @@
         <v>Fuchs</v>
       </c>
       <c r="C88">
-        <v>36.923077</v>
+        <v>40</v>
       </c>
       <c r="F88">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" t="str">
-        <v>Goonse</v>
+        <v>Fuchs</v>
       </c>
       <c r="H88">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K88">
         <v>4</v>
@@ -2308,16 +2308,16 @@
         <v>Fuchs</v>
       </c>
       <c r="M95">
-        <v>0.3076923076923077</v>
+        <v>0.25</v>
       </c>
       <c r="N95">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O95">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="P95">
-        <v>0.15384615384615385</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="96">
@@ -2328,7 +2328,7 @@
         <v>Goonse</v>
       </c>
       <c r="M96">
-        <v>0.38461538461538464</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="N96">
         <v>5</v>
@@ -2337,7 +2337,7 @@
         <v>0.8</v>
       </c>
       <c r="P96">
-        <v>0.3076923076923077</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="97">
@@ -2348,7 +2348,7 @@
         <v>Chäli</v>
       </c>
       <c r="M97">
-        <v>0.3076923076923077</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="N97">
         <v>4</v>
@@ -2357,7 +2357,7 @@
         <v>0.75</v>
       </c>
       <c r="P97">
-        <v>0.23076923076923078</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="98">
@@ -2368,7 +2368,7 @@
         <v>Goonse</v>
       </c>
       <c r="M98">
-        <v>0.3076923076923077</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="N98">
         <v>4</v>
@@ -2377,7 +2377,7 @@
         <v>0.25</v>
       </c>
       <c r="P98">
-        <v>0.07692307692307693</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="99">
@@ -2388,7 +2388,7 @@
         <v>Chäli</v>
       </c>
       <c r="M99">
-        <v>0.38461538461538464</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="N99">
         <v>5</v>
@@ -2397,7 +2397,7 @@
         <v>0.2</v>
       </c>
       <c r="P99">
-        <v>0.07692307692307693</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="100">
@@ -2408,16 +2408,16 @@
         <v>Chäli</v>
       </c>
       <c r="M100">
-        <v>0.3076923076923077</v>
+        <v>0.25</v>
       </c>
       <c r="N100">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O100">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="P100">
-        <v>0.23076923076923078</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="110">
@@ -2442,7 +2442,7 @@
         <v>Chäli</v>
       </c>
       <c r="C111">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="112">
@@ -2453,7 +2453,7 @@
         <v>Küng</v>
       </c>
       <c r="C112">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="113">
@@ -2464,7 +2464,7 @@
         <v>Goonse</v>
       </c>
       <c r="C113">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
@@ -2520,9 +2520,6 @@
       <c r="M122">
         <v>12</v>
       </c>
-      <c r="N122">
-        <v>13</v>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -2564,9 +2561,6 @@
       <c r="M123">
         <v>1</v>
       </c>
-      <c r="N123">
-        <v>1</v>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -2608,9 +2602,6 @@
       <c r="M124">
         <v>-1</v>
       </c>
-      <c r="N124">
-        <v>1</v>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -2652,9 +2643,6 @@
       <c r="M125">
         <v>-1</v>
       </c>
-      <c r="N125">
-        <v>-1</v>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -2695,9 +2683,6 @@
       </c>
       <c r="M126">
         <v>1</v>
-      </c>
-      <c r="N126">
-        <v>-1</v>
       </c>
     </row>
     <row r="129">
@@ -2742,9 +2727,6 @@
       <c r="M131" t="str">
         <v>07.09.</v>
       </c>
-      <c r="N131" t="str">
-        <v>01.01.</v>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -2786,9 +2768,6 @@
       <c r="M132">
         <v>9</v>
       </c>
-      <c r="N132">
-        <v>13</v>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -2830,9 +2809,6 @@
       <c r="M133">
         <v>1</v>
       </c>
-      <c r="N133">
-        <v>1</v>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -2874,9 +2850,6 @@
       <c r="M134">
         <v>3</v>
       </c>
-      <c r="N134">
-        <v>2</v>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -2917,9 +2890,6 @@
       </c>
       <c r="M135">
         <v>25</v>
-      </c>
-      <c r="N135">
-        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Statistik_Jassen.xlsx
+++ b/Statistik_Jassen.xlsx
@@ -432,7 +432,7 @@
         <v>Chäli</v>
       </c>
       <c r="H8">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I8">
         <v>0.2619047619047619</v>
@@ -569,7 +569,7 @@
         <v>Küng</v>
       </c>
       <c r="C18">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F18">
         <v>2</v>
@@ -587,7 +587,7 @@
         <v>Küng</v>
       </c>
       <c r="M18">
-        <v>6.583333</v>
+        <v>6.666667</v>
       </c>
     </row>
     <row r="19">
@@ -598,7 +598,7 @@
         <v>Goonse</v>
       </c>
       <c r="C19">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F19">
         <v>3</v>
@@ -616,7 +616,7 @@
         <v>Goonse</v>
       </c>
       <c r="M19">
-        <v>5.166667</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="20">
@@ -729,7 +729,7 @@
         <v>Küng</v>
       </c>
       <c r="C24">
-        <v>2.323529</v>
+        <v>2.352941</v>
       </c>
       <c r="F24">
         <v>2</v>
@@ -758,7 +758,7 @@
         <v>Goonse</v>
       </c>
       <c r="C25">
-        <v>1.823529</v>
+        <v>1.852941</v>
       </c>
       <c r="F25">
         <v>2</v>
@@ -1027,7 +1027,7 @@
         <v>Küng</v>
       </c>
       <c r="C39">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -1039,7 +1039,7 @@
         <v>Küng</v>
       </c>
       <c r="H39">
-        <v>15420</v>
+        <v>15934</v>
       </c>
       <c r="I39">
         <v>1</v>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B40" t="str">
         <v>Chäli</v>
@@ -1067,9 +1067,6 @@
       <c r="C40">
         <v>20</v>
       </c>
-      <c r="D40">
-        <v>1</v>
-      </c>
       <c r="F40">
         <v>2</v>
       </c>
@@ -1100,7 +1097,7 @@
         <v>Goonse</v>
       </c>
       <c r="C41">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F41">
         <v>3</v>
@@ -1109,7 +1106,7 @@
         <v>Goonse</v>
       </c>
       <c r="H41">
-        <v>11308</v>
+        <v>11822</v>
       </c>
       <c r="K41">
         <v>3</v>
@@ -1196,7 +1193,7 @@
         <v>Küng</v>
       </c>
       <c r="C45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -1228,7 +1225,7 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B46" t="str">
         <v>Chäli</v>
@@ -1236,9 +1233,6 @@
       <c r="C46">
         <v>5</v>
       </c>
-      <c r="D46">
-        <v>1</v>
-      </c>
       <c r="F46">
         <v>2</v>
       </c>
@@ -1266,7 +1260,7 @@
         <v>Goonse</v>
       </c>
       <c r="C47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F47">
         <v>3</v>
@@ -2053,7 +2047,7 @@
         <v>Küng</v>
       </c>
       <c r="M80">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="81">
@@ -2085,7 +2079,7 @@
         <v>Goonse</v>
       </c>
       <c r="M81">
-        <v>360</v>
+        <v>350</v>
       </c>
     </row>
     <row r="82">
@@ -2204,7 +2198,7 @@
         <v>Küng</v>
       </c>
       <c r="C86">
-        <v>15.833333</v>
+        <v>15</v>
       </c>
       <c r="F86">
         <v>2</v>
@@ -2233,7 +2227,7 @@
         <v>Goonse</v>
       </c>
       <c r="C87">
-        <v>30</v>
+        <v>29.166667</v>
       </c>
       <c r="F87">
         <v>3</v>
@@ -2442,7 +2436,7 @@
         <v>Chäli</v>
       </c>
       <c r="C111">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="112">
@@ -2757,7 +2751,7 @@
         <v>19</v>
       </c>
       <c r="J132">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K132">
         <v>12</v>
@@ -2880,16 +2874,16 @@
         <v>13</v>
       </c>
       <c r="J135">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K135">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L135">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M135">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
